--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="119">
   <si>
     <t>date</t>
   </si>
@@ -371,18 +371,6 @@
   </si>
   <si>
     <t>udinese</t>
-  </si>
-  <si>
-    <t>6Le197C2</t>
-  </si>
-  <si>
-    <t>lazio</t>
-  </si>
-  <si>
-    <t>sassuolo</t>
-  </si>
-  <si>
-    <t>dif_prob_mod_bm &lt; 0.0</t>
   </si>
 </sst>
 </file>
@@ -408,7 +396,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -422,6 +410,13 @@
     </fill>
   </fills>
   <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -444,48 +439,41 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -807,7 +795,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -818,7 +806,7 @@
     <col min="6" max="6" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -861,7 +849,7 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -921,7 +909,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>26</v>
@@ -999,7 +987,7 @@
         <v>29</v>
       </c>
       <c r="B3" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>30</v>
@@ -1077,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="B4" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>33</v>
@@ -1155,7 +1143,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>36</v>
@@ -1233,7 +1221,7 @@
         <v>38</v>
       </c>
       <c r="B6" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>39</v>
@@ -1311,7 +1299,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>42</v>
@@ -1389,7 +1377,7 @@
         <v>44</v>
       </c>
       <c r="B8" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>45</v>
@@ -1467,7 +1455,7 @@
         <v>47</v>
       </c>
       <c r="B9" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>48</v>
@@ -1545,7 +1533,7 @@
         <v>50</v>
       </c>
       <c r="B10" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>51</v>
@@ -1623,7 +1611,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>54</v>
@@ -1701,7 +1689,7 @@
         <v>56</v>
       </c>
       <c r="B12" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>57</v>
@@ -1781,7 +1769,7 @@
         <v>59</v>
       </c>
       <c r="B13" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>60</v>
@@ -1861,7 +1849,7 @@
         <v>62</v>
       </c>
       <c r="B14" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>63</v>
@@ -1941,7 +1929,7 @@
         <v>65</v>
       </c>
       <c r="B15" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>66</v>
@@ -2021,7 +2009,7 @@
         <v>68</v>
       </c>
       <c r="B16" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>69</v>
@@ -2096,12 +2084,12 @@
         <v>32.22235954645397</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>72</v>
@@ -2176,12 +2164,12 @@
         <v>46.84798552903081</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="3" t="s">
         <v>74</v>
       </c>
       <c r="B18" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>75</v>
@@ -2256,12 +2244,12 @@
         <v>37.72802214730521</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B19" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>78</v>
@@ -2336,12 +2324,12 @@
         <v>30.63450749146325</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B20" s="6">
-        <v>25568.875525810185</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>81</v>
@@ -2416,12 +2404,12 @@
         <v>47.00267668299728</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="3" t="s">
         <v>83</v>
       </c>
       <c r="B21" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>84</v>
@@ -2494,12 +2482,12 @@
         <v>41.63542744859845</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="3" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>88</v>
@@ -2572,12 +2560,12 @@
         <v>32.5970636146569</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="3" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>92</v>
@@ -2650,12 +2638,12 @@
         <v>45.95661995158865</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="3" t="s">
         <v>94</v>
       </c>
       <c r="B24" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>95</v>
@@ -2728,12 +2716,12 @@
         <v>40.60981885249955</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="3" t="s">
         <v>97</v>
       </c>
       <c r="B25" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>98</v>
@@ -2806,12 +2794,12 @@
         <v>28.33236120813439</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="3" t="s">
         <v>100</v>
       </c>
       <c r="B26" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>101</v>
@@ -2884,12 +2872,12 @@
         <v>52.59185769314812</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="3" t="s">
         <v>103</v>
       </c>
       <c r="B27" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>104</v>
@@ -2962,12 +2950,12 @@
         <v>49.25088577807655</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B28" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>107</v>
@@ -3042,12 +3030,12 @@
         <v>34.31047145022888</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B29" s="6">
-        <v>25568.87552582176</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>110</v>
@@ -3120,12 +3108,12 @@
         <v>33.91267595189322</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="3" t="s">
         <v>112</v>
       </c>
       <c r="B30" s="6">
-        <v>25568.87552590278</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>113</v>
@@ -3198,12 +3186,12 @@
         <v>18.36260905959823</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="3" t="s">
         <v>116</v>
       </c>
       <c r="B31" s="6">
-        <v>25568.87552590278</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>117</v>
@@ -3274,84 +3262,6 @@
       </c>
       <c r="Z31" s="9">
         <v>21.30347681115242</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B32" s="6">
-        <v>25568.87552590278</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" s="8">
-        <v>77</v>
-      </c>
-      <c r="F32" s="8">
-        <v>771</v>
-      </c>
-      <c r="G32" s="9">
-        <v>1.29</v>
-      </c>
-      <c r="H32" s="9">
-        <v>5.75</v>
-      </c>
-      <c r="I32" s="8">
-        <v>9</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0.7311645650100667</v>
-      </c>
-      <c r="K32" s="9">
-        <v>0.1640351806718237</v>
-      </c>
-      <c r="L32" s="9">
-        <v>0.1048002543181096</v>
-      </c>
-      <c r="M32" s="9">
-        <v>0.06021795303898436</v>
-      </c>
-      <c r="N32" s="8">
-        <v>1</v>
-      </c>
-      <c r="O32" s="9">
-        <v>0.6433210241393781</v>
-      </c>
-      <c r="P32" s="9">
-        <v>0.2833053216314175</v>
-      </c>
-      <c r="Q32" s="9">
-        <v>0.07337365422920432</v>
-      </c>
-      <c r="R32" s="10"/>
-      <c r="S32" s="9">
-        <v>-0.08784354087068857</v>
-      </c>
-      <c r="T32" s="8">
-        <v>-1</v>
-      </c>
-      <c r="U32" s="9">
-        <v>0.08784354087068857</v>
-      </c>
-      <c r="V32" s="9">
-        <v>0.3566789758606219</v>
-      </c>
-      <c r="W32" s="9">
-        <v>3.508474576271186</v>
-      </c>
-      <c r="X32" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="Y32" s="9">
-        <v>17.83394879303109</v>
-      </c>
-      <c r="Z32" s="9">
-        <v>17.83394879303109</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="116">
   <si>
     <t>date</t>
   </si>
@@ -362,15 +362,6 @@
   </si>
   <si>
     <t>dif_prob_mod_bm &gt; 0.0</t>
-  </si>
-  <si>
-    <t>rN4paNle</t>
-  </si>
-  <si>
-    <t>frosinone</t>
-  </si>
-  <si>
-    <t>udinese</t>
   </si>
 </sst>
 </file>
@@ -380,19 +371,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -443,36 +428,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -489,9 +471,6 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,35 +774,35 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -891,7 +870,7 @@
       <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
       <c r="X1" s="3" t="s">
@@ -956,7 +935,7 @@
       <c r="Q2" s="9">
         <v>0.1235290487449972</v>
       </c>
-      <c r="R2" s="10"/>
+      <c r="R2" s="8"/>
       <c r="S2" s="9">
         <v>-0.209168931849007</v>
       </c>
@@ -1034,7 +1013,7 @@
       <c r="Q3" s="9">
         <v>0.3780506066699977</v>
       </c>
-      <c r="R3" s="10"/>
+      <c r="R3" s="8"/>
       <c r="S3" s="9">
         <v>-0.0655723138475624</v>
       </c>
@@ -1112,7 +1091,7 @@
       <c r="Q4" s="9">
         <v>0.3714009243666285</v>
       </c>
-      <c r="R4" s="10"/>
+      <c r="R4" s="8"/>
       <c r="S4" s="9">
         <v>0.22874994880352</v>
       </c>
@@ -1190,7 +1169,7 @@
       <c r="Q5" s="9">
         <v>0.3524695947708462</v>
       </c>
-      <c r="R5" s="10"/>
+      <c r="R5" s="8"/>
       <c r="S5" s="9">
         <v>0.1152977083117556</v>
       </c>
@@ -1268,7 +1247,7 @@
       <c r="Q6" s="9">
         <v>0.280137233227733</v>
       </c>
-      <c r="R6" s="10"/>
+      <c r="R6" s="8"/>
       <c r="S6" s="9">
         <v>-0.269836629001076</v>
       </c>
@@ -1346,7 +1325,7 @@
       <c r="Q7" s="9">
         <v>0.2903923938365265</v>
       </c>
-      <c r="R7" s="10"/>
+      <c r="R7" s="8"/>
       <c r="S7" s="9">
         <v>0.1762501084110619</v>
       </c>
@@ -1424,7 +1403,7 @@
       <c r="Q8" s="9">
         <v>0.2284780288823605</v>
       </c>
-      <c r="R8" s="10"/>
+      <c r="R8" s="8"/>
       <c r="S8" s="9">
         <v>-0.3740646654849183</v>
       </c>
@@ -1502,7 +1481,7 @@
       <c r="Q9" s="9">
         <v>0.3466372231665464</v>
       </c>
-      <c r="R9" s="10"/>
+      <c r="R9" s="8"/>
       <c r="S9" s="9">
         <v>0.1655972195130098</v>
       </c>
@@ -1580,7 +1559,7 @@
       <c r="Q10" s="9">
         <v>0.1649867725393549</v>
       </c>
-      <c r="R10" s="10"/>
+      <c r="R10" s="8"/>
       <c r="S10" s="9">
         <v>-0.355077979667156</v>
       </c>
@@ -1658,7 +1637,7 @@
       <c r="Q11" s="9">
         <v>0.5172218139414873</v>
       </c>
-      <c r="R11" s="10"/>
+      <c r="R11" s="8"/>
       <c r="S11" s="9">
         <v>-0.1863572622285953</v>
       </c>
@@ -2456,7 +2435,7 @@
       <c r="Q21" s="9">
         <v>0.5204428431074806</v>
       </c>
-      <c r="R21" s="10"/>
+      <c r="R21" s="8"/>
       <c r="S21" s="9">
         <v>-0.03717797473638562</v>
       </c>
@@ -2534,7 +2513,7 @@
       <c r="Q22" s="9">
         <v>0.1761166834736529</v>
       </c>
-      <c r="R22" s="10"/>
+      <c r="R22" s="8"/>
       <c r="S22" s="9">
         <v>-0.1176561771136446</v>
       </c>
@@ -2612,7 +2591,7 @@
       <c r="Q23" s="9">
         <v>0.290792124295596</v>
       </c>
-      <c r="R23" s="10"/>
+      <c r="R23" s="8"/>
       <c r="S23" s="9">
         <v>-0.2079298906652903</v>
       </c>
@@ -2690,7 +2669,7 @@
       <c r="Q24" s="9">
         <v>0.2131791053843112</v>
       </c>
-      <c r="R24" s="10"/>
+      <c r="R24" s="8"/>
       <c r="S24" s="9">
         <v>-0.09251578378458664</v>
       </c>
@@ -2768,7 +2747,7 @@
       <c r="Q25" s="9">
         <v>0.1135336887367399</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="R25" s="8"/>
       <c r="S25" s="9">
         <v>-0.07645719431963771</v>
       </c>
@@ -2846,7 +2825,7 @@
       <c r="Q26" s="9">
         <v>0.2788722651651065</v>
       </c>
-      <c r="R26" s="10"/>
+      <c r="R26" s="8"/>
       <c r="S26" s="9">
         <v>0.4573209712609139</v>
       </c>
@@ -2924,7 +2903,7 @@
       <c r="Q27" s="9">
         <v>0.133231047651172</v>
       </c>
-      <c r="R27" s="10"/>
+      <c r="R27" s="8"/>
       <c r="S27" s="9">
         <v>-0.02330444822013977</v>
       </c>
@@ -3082,7 +3061,7 @@
       <c r="Q29" s="9">
         <v>0.4239084493986652</v>
       </c>
-      <c r="R29" s="10"/>
+      <c r="R29" s="8"/>
       <c r="S29" s="9">
         <v>0.00820406140790314</v>
       </c>
@@ -3160,7 +3139,7 @@
       <c r="Q30" s="9">
         <v>0.3672521811919646</v>
       </c>
-      <c r="R30" s="10"/>
+      <c r="R30" s="8"/>
       <c r="S30" s="9">
         <v>0.06234608690296495</v>
       </c>
@@ -3184,84 +3163,6 @@
       </c>
       <c r="Z30" s="9">
         <v>18.36260905959823</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
-      <c r="A31" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="6">
-        <v>25568.875520833335</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="8">
-        <v>77</v>
-      </c>
-      <c r="F31" s="8">
-        <v>771</v>
-      </c>
-      <c r="G31" s="9">
-        <v>2.45</v>
-      </c>
-      <c r="H31" s="9">
-        <v>3.2</v>
-      </c>
-      <c r="I31" s="8">
-        <v>3</v>
-      </c>
-      <c r="J31" s="9">
-        <v>0.3872529245663574</v>
-      </c>
-      <c r="K31" s="9">
-        <v>0.2964905203711174</v>
-      </c>
-      <c r="L31" s="9">
-        <v>0.3162565550625252</v>
-      </c>
-      <c r="M31" s="9">
-        <v>0.05399659863945572</v>
-      </c>
-      <c r="N31" s="8">
-        <v>2</v>
-      </c>
-      <c r="O31" s="9">
-        <v>0.2256767281456628</v>
-      </c>
-      <c r="P31" s="9">
-        <v>0.348253735631289</v>
-      </c>
-      <c r="Q31" s="9">
-        <v>0.4260695362230483</v>
-      </c>
-      <c r="R31" s="10"/>
-      <c r="S31" s="9">
-        <v>0.1098129811605231</v>
-      </c>
-      <c r="T31" s="8">
-        <v>2</v>
-      </c>
-      <c r="U31" s="9">
-        <v>0.1098129811605231</v>
-      </c>
-      <c r="V31" s="9">
-        <v>0.4260695362230483</v>
-      </c>
-      <c r="W31" s="8">
-        <v>3</v>
-      </c>
-      <c r="X31" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y31" s="9">
-        <v>21.30347681115242</v>
-      </c>
-      <c r="Z31" s="9">
-        <v>21.30347681115242</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="112">
   <si>
     <t>date</t>
   </si>
@@ -350,18 +350,6 @@
   </si>
   <si>
     <t>brest</t>
-  </si>
-  <si>
-    <t>4W5t03Zl</t>
-  </si>
-  <si>
-    <t>empoli</t>
-  </si>
-  <si>
-    <t>as roma</t>
-  </si>
-  <si>
-    <t>dif_prob_mod_bm &gt; 0.0</t>
   </si>
 </sst>
 </file>
@@ -774,7 +762,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -785,7 +773,7 @@
     <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -799,7 +787,7 @@
     <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -828,7 +816,7 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -870,7 +858,7 @@
       <c r="V1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="5" t="s">
         <v>21</v>
       </c>
       <c r="X1" s="3" t="s">
@@ -1983,7 +1971,7 @@
         <v>39.64541637632485</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="3" t="s">
         <v>68</v>
       </c>
@@ -3085,84 +3073,6 @@
       </c>
       <c r="Z29" s="9">
         <v>33.91267595189322</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="6">
-        <v>25568.875520833335</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="8">
-        <v>77</v>
-      </c>
-      <c r="F30" s="8">
-        <v>771</v>
-      </c>
-      <c r="G30" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="H30" s="9">
-        <v>3.7</v>
-      </c>
-      <c r="I30" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="J30" s="9">
-        <v>0.439632042928325</v>
-      </c>
-      <c r="K30" s="9">
-        <v>0.2554618627826753</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0.3049060942889996</v>
-      </c>
-      <c r="M30" s="9">
-        <v>0.05796719450132803</v>
-      </c>
-      <c r="N30" s="8">
-        <v>2</v>
-      </c>
-      <c r="O30" s="9">
-        <v>0.2763914746914717</v>
-      </c>
-      <c r="P30" s="9">
-        <v>0.3563563441165634</v>
-      </c>
-      <c r="Q30" s="9">
-        <v>0.3672521811919646</v>
-      </c>
-      <c r="R30" s="8"/>
-      <c r="S30" s="9">
-        <v>0.06234608690296495</v>
-      </c>
-      <c r="T30" s="8">
-        <v>2</v>
-      </c>
-      <c r="U30" s="9">
-        <v>0.06234608690296495</v>
-      </c>
-      <c r="V30" s="9">
-        <v>0.3672521811919646</v>
-      </c>
-      <c r="W30" s="9">
-        <v>3.1</v>
-      </c>
-      <c r="X30" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y30" s="9">
-        <v>18.36260905959823</v>
-      </c>
-      <c r="Z30" s="9">
-        <v>18.36260905959823</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="109">
   <si>
     <t>date</t>
   </si>
@@ -341,15 +341,6 @@
   </si>
   <si>
     <t>rennes</t>
-  </si>
-  <si>
-    <t>C6diYbTh</t>
-  </si>
-  <si>
-    <t>toulouse</t>
-  </si>
-  <si>
-    <t>brest</t>
   </si>
 </sst>
 </file>
@@ -762,7 +753,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -2997,84 +2988,6 @@
         <v>34.31047145022888</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="6">
-        <v>25568.875520833335</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="8">
-        <v>55</v>
-      </c>
-      <c r="F29" s="8">
-        <v>551</v>
-      </c>
-      <c r="G29" s="8">
-        <v>3</v>
-      </c>
-      <c r="H29" s="9">
-        <v>3.6</v>
-      </c>
-      <c r="I29" s="9">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="9">
-        <v>0.3187066974595842</v>
-      </c>
-      <c r="K29" s="9">
-        <v>0.2655889145496536</v>
-      </c>
-      <c r="L29" s="9">
-        <v>0.4157043879907621</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0.04589371980676349</v>
-      </c>
-      <c r="N29" s="8">
-        <v>2</v>
-      </c>
-      <c r="O29" s="9">
-        <v>0.2634201695928</v>
-      </c>
-      <c r="P29" s="9">
-        <v>0.3126713810085349</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>0.4239084493986652</v>
-      </c>
-      <c r="R29" s="8"/>
-      <c r="S29" s="9">
-        <v>0.00820406140790314</v>
-      </c>
-      <c r="T29" s="8">
-        <v>2</v>
-      </c>
-      <c r="U29" s="9">
-        <v>0.00820406140790314</v>
-      </c>
-      <c r="V29" s="9">
-        <v>0.4239084493986652</v>
-      </c>
-      <c r="W29" s="9">
-        <v>2.3</v>
-      </c>
-      <c r="X29" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y29" s="9">
-        <v>33.91267595189322</v>
-      </c>
-      <c r="Z29" s="9">
-        <v>33.91267595189322</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
   <si>
     <t>date</t>
   </si>
@@ -332,15 +332,6 @@
   </si>
   <si>
     <t>nantes</t>
-  </si>
-  <si>
-    <t>fVodXIra</t>
-  </si>
-  <si>
-    <t>reims</t>
-  </si>
-  <si>
-    <t>rennes</t>
   </si>
 </sst>
 </file>
@@ -753,7 +744,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -2908,86 +2899,6 @@
         <v>49.25088577807655</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="6">
-        <v>25568.875520833335</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="8">
-        <v>55</v>
-      </c>
-      <c r="F28" s="8">
-        <v>551</v>
-      </c>
-      <c r="G28" s="8">
-        <v>3</v>
-      </c>
-      <c r="H28" s="9">
-        <v>3.4</v>
-      </c>
-      <c r="I28" s="9">
-        <v>2.38</v>
-      </c>
-      <c r="J28" s="9">
-        <v>0.3181818181818181</v>
-      </c>
-      <c r="K28" s="9">
-        <v>0.2807486631016043</v>
-      </c>
-      <c r="L28" s="9">
-        <v>0.4010695187165775</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0.04761904761904767</v>
-      </c>
-      <c r="N28" s="8">
-        <v>2</v>
-      </c>
-      <c r="O28" s="9">
-        <v>0.234329403268049</v>
-      </c>
-      <c r="P28" s="9">
-        <v>0.3367897036040899</v>
-      </c>
-      <c r="Q28" s="9">
-        <v>0.428880893127861</v>
-      </c>
-      <c r="R28" s="8">
-        <v>1</v>
-      </c>
-      <c r="S28" s="9">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="T28" s="8">
-        <v>2</v>
-      </c>
-      <c r="U28" s="9">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="V28" s="9">
-        <v>0.428880893127861</v>
-      </c>
-      <c r="W28" s="9">
-        <v>2.38</v>
-      </c>
-      <c r="X28" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y28" s="9">
-        <v>34.31047145022888</v>
-      </c>
-      <c r="Z28" s="9">
-        <v>34.31047145022888</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="103">
   <si>
     <t>date</t>
   </si>
@@ -323,15 +323,6 @@
   </si>
   <si>
     <t>psg</t>
-  </si>
-  <si>
-    <t>tnl8UGSH</t>
-  </si>
-  <si>
-    <t>monaco</t>
-  </si>
-  <si>
-    <t>nantes</t>
   </si>
 </sst>
 </file>
@@ -744,7 +735,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -2821,84 +2812,6 @@
         <v>52.59185769314812</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="6">
-        <v>25568.875520833335</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="8">
-        <v>55</v>
-      </c>
-      <c r="F27" s="8">
-        <v>551</v>
-      </c>
-      <c r="G27" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="H27" s="8">
-        <v>5</v>
-      </c>
-      <c r="I27" s="9">
-        <v>5.5</v>
-      </c>
-      <c r="J27" s="9">
-        <v>0.6389405204460966</v>
-      </c>
-      <c r="K27" s="9">
-        <v>0.1891263940520446</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0.1719330855018587</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0.05749385749385749</v>
-      </c>
-      <c r="N27" s="8">
-        <v>1</v>
-      </c>
-      <c r="O27" s="9">
-        <v>0.6156360722259568</v>
-      </c>
-      <c r="P27" s="9">
-        <v>0.251132880122871</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>0.133231047651172</v>
-      </c>
-      <c r="R27" s="8"/>
-      <c r="S27" s="9">
-        <v>-0.02330444822013977</v>
-      </c>
-      <c r="T27" s="8">
-        <v>1</v>
-      </c>
-      <c r="U27" s="9">
-        <v>-0.02330444822013977</v>
-      </c>
-      <c r="V27" s="9">
-        <v>0.6156360722259568</v>
-      </c>
-      <c r="W27" s="9">
-        <v>1.48</v>
-      </c>
-      <c r="X27" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y27" s="9">
-        <v>49.25088577807655</v>
-      </c>
-      <c r="Z27" s="9">
-        <v>49.25088577807655</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
   <si>
     <t>id_match</t>
   </si>
@@ -374,18 +374,6 @@
   </si>
   <si>
     <t>udinese</t>
-  </si>
-  <si>
-    <t>6Le197C2</t>
-  </si>
-  <si>
-    <t>lazio</t>
-  </si>
-  <si>
-    <t>sassuolo</t>
-  </si>
-  <si>
-    <t>dif_prob_mod_bm &lt; 0.0</t>
   </si>
 </sst>
 </file>
@@ -405,7 +393,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -472,20 +460,20 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -807,7 +795,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z32"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -818,7 +806,7 @@
     <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -838,7 +826,7 @@
     <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -863,7 +851,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -918,12 +906,12 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>27</v>
@@ -996,12 +984,12 @@
         <v>28.46215537952682</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>31</v>
@@ -1074,12 +1062,12 @@
         <v>18.90253033349989</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>34</v>
@@ -1152,12 +1140,12 @@
         <v>23.33863088145612</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B5" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>37</v>
@@ -1230,12 +1218,12 @@
         <v>18.47938501250129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>40</v>
@@ -1308,12 +1296,12 @@
         <v>19.89322222039439</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>43</v>
@@ -1386,12 +1374,12 @@
         <v>19.69907647661568</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>46</v>
@@ -1464,12 +1452,12 @@
         <v>23.18244346688417</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>49</v>
@@ -1542,12 +1530,12 @@
         <v>20.42299002018799</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>52</v>
@@ -1620,12 +1608,12 @@
         <v>26.7980358435261</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>55</v>
@@ -1698,12 +1686,12 @@
         <v>25.86109069707436</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>58</v>
@@ -1778,12 +1766,12 @@
         <v>60.40066288573521</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>61</v>
@@ -1858,12 +1846,12 @@
         <v>57.40947653436852</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>64</v>
@@ -1938,12 +1926,12 @@
         <v>33.83126953905438</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>67</v>
@@ -2018,12 +2006,12 @@
         <v>39.64541637632485</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>70</v>
@@ -2098,12 +2086,12 @@
         <v>32.22235954645397</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>73</v>
@@ -2178,12 +2166,12 @@
         <v>46.84798552903081</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>76</v>
@@ -2258,12 +2246,12 @@
         <v>37.72802214730521</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>79</v>
@@ -2338,12 +2326,12 @@
         <v>30.63450749146325</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>82</v>
@@ -2418,12 +2406,12 @@
         <v>47.00267668299728</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
         <v>84</v>
       </c>
       <c r="B21" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>85</v>
@@ -2501,7 +2489,7 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>89</v>
@@ -2579,7 +2567,7 @@
         <v>92</v>
       </c>
       <c r="B23" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>93</v>
@@ -2657,7 +2645,7 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>96</v>
@@ -2735,7 +2723,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>99</v>
@@ -2813,7 +2801,7 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>102</v>
@@ -2891,7 +2879,7 @@
         <v>104</v>
       </c>
       <c r="B27" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>105</v>
@@ -2969,7 +2957,7 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>108</v>
@@ -3049,7 +3037,7 @@
         <v>110</v>
       </c>
       <c r="B29" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>111</v>
@@ -3127,7 +3115,7 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>114</v>
@@ -3205,7 +3193,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>118</v>
@@ -3276,84 +3264,6 @@
       </c>
       <c r="Z31" s="8">
         <v>21.30347681115242</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B32" s="5">
-        <v>25568.875295925925</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E32" s="7">
-        <v>77</v>
-      </c>
-      <c r="F32" s="7">
-        <v>771</v>
-      </c>
-      <c r="G32" s="8">
-        <v>1.29</v>
-      </c>
-      <c r="H32" s="8">
-        <v>5.75</v>
-      </c>
-      <c r="I32" s="7">
-        <v>9</v>
-      </c>
-      <c r="J32" s="8">
-        <v>0.7311645650100667</v>
-      </c>
-      <c r="K32" s="8">
-        <v>0.1640351806718237</v>
-      </c>
-      <c r="L32" s="8">
-        <v>0.1048002543181096</v>
-      </c>
-      <c r="M32" s="8">
-        <v>0.06021795303898436</v>
-      </c>
-      <c r="N32" s="7">
-        <v>1</v>
-      </c>
-      <c r="O32" s="8">
-        <v>0.6433210241393781</v>
-      </c>
-      <c r="P32" s="8">
-        <v>0.2833053216314175</v>
-      </c>
-      <c r="Q32" s="8">
-        <v>0.07337365422920432</v>
-      </c>
-      <c r="R32" s="9"/>
-      <c r="S32" s="8">
-        <v>-0.08784354087068857</v>
-      </c>
-      <c r="T32" s="7">
-        <v>-1</v>
-      </c>
-      <c r="U32" s="8">
-        <v>0.08784354087068857</v>
-      </c>
-      <c r="V32" s="8">
-        <v>0.3566789758606219</v>
-      </c>
-      <c r="W32" s="8">
-        <v>3.508474576271186</v>
-      </c>
-      <c r="X32" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y32" s="8">
-        <v>17.83394879303109</v>
-      </c>
-      <c r="Z32" s="8">
-        <v>17.83394879303109</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="117">
   <si>
     <t>id_match</t>
   </si>
@@ -365,15 +365,6 @@
   </si>
   <si>
     <t>dif_prob_mod_bm &gt; 0.0</t>
-  </si>
-  <si>
-    <t>rN4paNle</t>
-  </si>
-  <si>
-    <t>frosinone</t>
-  </si>
-  <si>
-    <t>udinese</t>
   </si>
 </sst>
 </file>
@@ -383,7 +374,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,12 +385,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -446,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -472,9 +457,6 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -489,9 +471,6 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,35 +774,35 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z31"/>
+  <dimension ref="A1:Z30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -893,7 +872,7 @@
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
@@ -958,7 +937,7 @@
       <c r="Q2" s="8">
         <v>0.1235290487449972</v>
       </c>
-      <c r="R2" s="9"/>
+      <c r="R2" s="7"/>
       <c r="S2" s="8">
         <v>-0.209168931849007</v>
       </c>
@@ -1036,7 +1015,7 @@
       <c r="Q3" s="8">
         <v>0.3780506066699977</v>
       </c>
-      <c r="R3" s="9"/>
+      <c r="R3" s="7"/>
       <c r="S3" s="8">
         <v>-0.0655723138475624</v>
       </c>
@@ -1114,7 +1093,7 @@
       <c r="Q4" s="8">
         <v>0.3714009243666285</v>
       </c>
-      <c r="R4" s="9"/>
+      <c r="R4" s="7"/>
       <c r="S4" s="8">
         <v>0.22874994880352</v>
       </c>
@@ -1192,7 +1171,7 @@
       <c r="Q5" s="8">
         <v>0.3524695947708462</v>
       </c>
-      <c r="R5" s="9"/>
+      <c r="R5" s="7"/>
       <c r="S5" s="8">
         <v>0.1152977083117556</v>
       </c>
@@ -1270,7 +1249,7 @@
       <c r="Q6" s="8">
         <v>0.280137233227733</v>
       </c>
-      <c r="R6" s="9"/>
+      <c r="R6" s="7"/>
       <c r="S6" s="8">
         <v>-0.269836629001076</v>
       </c>
@@ -1348,7 +1327,7 @@
       <c r="Q7" s="8">
         <v>0.2903923938365265</v>
       </c>
-      <c r="R7" s="9"/>
+      <c r="R7" s="7"/>
       <c r="S7" s="8">
         <v>0.1762501084110619</v>
       </c>
@@ -1426,7 +1405,7 @@
       <c r="Q8" s="8">
         <v>0.2284780288823605</v>
       </c>
-      <c r="R8" s="9"/>
+      <c r="R8" s="7"/>
       <c r="S8" s="8">
         <v>-0.3740646654849183</v>
       </c>
@@ -1504,7 +1483,7 @@
       <c r="Q9" s="8">
         <v>0.3466372231665464</v>
       </c>
-      <c r="R9" s="9"/>
+      <c r="R9" s="7"/>
       <c r="S9" s="8">
         <v>0.1655972195130098</v>
       </c>
@@ -1582,7 +1561,7 @@
       <c r="Q10" s="8">
         <v>0.1649867725393549</v>
       </c>
-      <c r="R10" s="9"/>
+      <c r="R10" s="7"/>
       <c r="S10" s="8">
         <v>-0.355077979667156</v>
       </c>
@@ -1660,7 +1639,7 @@
       <c r="Q11" s="8">
         <v>0.5172218139414873</v>
       </c>
-      <c r="R11" s="9"/>
+      <c r="R11" s="7"/>
       <c r="S11" s="8">
         <v>-0.1863572622285953</v>
       </c>
@@ -2458,7 +2437,7 @@
       <c r="Q21" s="8">
         <v>0.5204428431074806</v>
       </c>
-      <c r="R21" s="9"/>
+      <c r="R21" s="7"/>
       <c r="S21" s="8">
         <v>-0.03717797473638562</v>
       </c>
@@ -2484,7 +2463,7 @@
         <v>41.63542744859845</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="1" t="s">
         <v>88</v>
       </c>
@@ -2536,7 +2515,7 @@
       <c r="Q22" s="8">
         <v>0.1761166834736529</v>
       </c>
-      <c r="R22" s="9"/>
+      <c r="R22" s="7"/>
       <c r="S22" s="8">
         <v>-0.1176561771136446</v>
       </c>
@@ -2562,7 +2541,7 @@
         <v>32.5970636146569</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="1" t="s">
         <v>92</v>
       </c>
@@ -2614,7 +2593,7 @@
       <c r="Q23" s="8">
         <v>0.290792124295596</v>
       </c>
-      <c r="R23" s="9"/>
+      <c r="R23" s="7"/>
       <c r="S23" s="8">
         <v>-0.2079298906652903</v>
       </c>
@@ -2640,7 +2619,7 @@
         <v>45.95661995158865</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
@@ -2692,7 +2671,7 @@
       <c r="Q24" s="8">
         <v>0.2131791053843112</v>
       </c>
-      <c r="R24" s="9"/>
+      <c r="R24" s="7"/>
       <c r="S24" s="8">
         <v>-0.09251578378458664</v>
       </c>
@@ -2718,7 +2697,7 @@
         <v>40.60981885249955</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="1" t="s">
         <v>98</v>
       </c>
@@ -2770,7 +2749,7 @@
       <c r="Q25" s="8">
         <v>0.1135336887367399</v>
       </c>
-      <c r="R25" s="9"/>
+      <c r="R25" s="7"/>
       <c r="S25" s="8">
         <v>-0.07645719431963771</v>
       </c>
@@ -2796,7 +2775,7 @@
         <v>28.33236120813439</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="1" t="s">
         <v>101</v>
       </c>
@@ -2848,7 +2827,7 @@
       <c r="Q26" s="8">
         <v>0.2788722651651065</v>
       </c>
-      <c r="R26" s="9"/>
+      <c r="R26" s="7"/>
       <c r="S26" s="8">
         <v>0.4573209712609139</v>
       </c>
@@ -2874,7 +2853,7 @@
         <v>52.59185769314812</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1" t="s">
         <v>104</v>
       </c>
@@ -2926,7 +2905,7 @@
       <c r="Q27" s="8">
         <v>0.133231047651172</v>
       </c>
-      <c r="R27" s="9"/>
+      <c r="R27" s="7"/>
       <c r="S27" s="8">
         <v>-0.02330444822013977</v>
       </c>
@@ -2952,7 +2931,7 @@
         <v>49.25088577807655</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="1" t="s">
         <v>107</v>
       </c>
@@ -3032,7 +3011,7 @@
         <v>34.31047145022888</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="1" t="s">
         <v>110</v>
       </c>
@@ -3084,7 +3063,7 @@
       <c r="Q29" s="8">
         <v>0.4239084493986652</v>
       </c>
-      <c r="R29" s="9"/>
+      <c r="R29" s="7"/>
       <c r="S29" s="8">
         <v>0.00820406140790314</v>
       </c>
@@ -3110,7 +3089,7 @@
         <v>33.91267595189322</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="1" t="s">
         <v>113</v>
       </c>
@@ -3162,7 +3141,7 @@
       <c r="Q30" s="8">
         <v>0.3672521811919646</v>
       </c>
-      <c r="R30" s="9"/>
+      <c r="R30" s="7"/>
       <c r="S30" s="8">
         <v>0.06234608690296495</v>
       </c>
@@ -3186,84 +3165,6 @@
       </c>
       <c r="Z30" s="8">
         <v>18.36260905959823</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="5">
-        <v>25568.875300925927</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" s="7">
-        <v>77</v>
-      </c>
-      <c r="F31" s="7">
-        <v>771</v>
-      </c>
-      <c r="G31" s="8">
-        <v>2.45</v>
-      </c>
-      <c r="H31" s="8">
-        <v>3.2</v>
-      </c>
-      <c r="I31" s="7">
-        <v>3</v>
-      </c>
-      <c r="J31" s="8">
-        <v>0.3872529245663574</v>
-      </c>
-      <c r="K31" s="8">
-        <v>0.2964905203711174</v>
-      </c>
-      <c r="L31" s="8">
-        <v>0.3162565550625252</v>
-      </c>
-      <c r="M31" s="8">
-        <v>0.05399659863945572</v>
-      </c>
-      <c r="N31" s="7">
-        <v>2</v>
-      </c>
-      <c r="O31" s="8">
-        <v>0.2256767281456628</v>
-      </c>
-      <c r="P31" s="8">
-        <v>0.348253735631289</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>0.4260695362230483</v>
-      </c>
-      <c r="R31" s="9"/>
-      <c r="S31" s="8">
-        <v>0.1098129811605231</v>
-      </c>
-      <c r="T31" s="7">
-        <v>2</v>
-      </c>
-      <c r="U31" s="8">
-        <v>0.1098129811605231</v>
-      </c>
-      <c r="V31" s="8">
-        <v>0.4260695362230483</v>
-      </c>
-      <c r="W31" s="7">
-        <v>3</v>
-      </c>
-      <c r="X31" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y31" s="8">
-        <v>21.30347681115242</v>
-      </c>
-      <c r="Z31" s="8">
-        <v>21.30347681115242</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
   <si>
     <t>id_match</t>
   </si>
@@ -353,18 +353,6 @@
   </si>
   <si>
     <t>brest</t>
-  </si>
-  <si>
-    <t>4W5t03Zl</t>
-  </si>
-  <si>
-    <t>empoli</t>
-  </si>
-  <si>
-    <t>as roma</t>
-  </si>
-  <si>
-    <t>dif_prob_mod_bm &gt; 0.0</t>
   </si>
 </sst>
 </file>
@@ -774,7 +762,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z30"/>
+  <dimension ref="A1:Z29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -785,7 +773,7 @@
     <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="12" max="12" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -799,7 +787,7 @@
     <col min="20" max="20" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="21" max="21" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="22" max="22" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="24" max="24" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -830,7 +818,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="4" t="s">
@@ -872,7 +860,7 @@
       <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
@@ -3087,84 +3075,6 @@
       </c>
       <c r="Z29" s="8">
         <v>33.91267595189322</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
-      <c r="A30" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="5">
-        <v>25568.875300925927</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" s="7">
-        <v>77</v>
-      </c>
-      <c r="F30" s="7">
-        <v>771</v>
-      </c>
-      <c r="G30" s="8">
-        <v>2.15</v>
-      </c>
-      <c r="H30" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="I30" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="J30" s="8">
-        <v>0.439632042928325</v>
-      </c>
-      <c r="K30" s="8">
-        <v>0.2554618627826753</v>
-      </c>
-      <c r="L30" s="8">
-        <v>0.3049060942889996</v>
-      </c>
-      <c r="M30" s="8">
-        <v>0.05796719450132803</v>
-      </c>
-      <c r="N30" s="7">
-        <v>2</v>
-      </c>
-      <c r="O30" s="8">
-        <v>0.2763914746914717</v>
-      </c>
-      <c r="P30" s="8">
-        <v>0.3563563441165634</v>
-      </c>
-      <c r="Q30" s="8">
-        <v>0.3672521811919646</v>
-      </c>
-      <c r="R30" s="7"/>
-      <c r="S30" s="8">
-        <v>0.06234608690296495</v>
-      </c>
-      <c r="T30" s="7">
-        <v>2</v>
-      </c>
-      <c r="U30" s="8">
-        <v>0.06234608690296495</v>
-      </c>
-      <c r="V30" s="8">
-        <v>0.3672521811919646</v>
-      </c>
-      <c r="W30" s="8">
-        <v>3.1</v>
-      </c>
-      <c r="X30" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="Y30" s="8">
-        <v>18.36260905959823</v>
-      </c>
-      <c r="Z30" s="8">
-        <v>18.36260905959823</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
   <si>
     <t>id_match</t>
   </si>
@@ -344,15 +344,6 @@
   </si>
   <si>
     <t>rennes</t>
-  </si>
-  <si>
-    <t>C6diYbTh</t>
-  </si>
-  <si>
-    <t>toulouse</t>
-  </si>
-  <si>
-    <t>brest</t>
   </si>
 </sst>
 </file>
@@ -762,7 +753,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -771,7 +762,7 @@
     <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -812,7 +803,7 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -2997,84 +2988,6 @@
       </c>
       <c r="Z28" s="8">
         <v>34.31047145022888</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
-      <c r="A29" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="5">
-        <v>25568.875300925927</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" s="7">
-        <v>55</v>
-      </c>
-      <c r="F29" s="7">
-        <v>551</v>
-      </c>
-      <c r="G29" s="7">
-        <v>3</v>
-      </c>
-      <c r="H29" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="I29" s="8">
-        <v>2.3</v>
-      </c>
-      <c r="J29" s="8">
-        <v>0.3187066974595842</v>
-      </c>
-      <c r="K29" s="8">
-        <v>0.2655889145496536</v>
-      </c>
-      <c r="L29" s="8">
-        <v>0.4157043879907621</v>
-      </c>
-      <c r="M29" s="8">
-        <v>0.04589371980676349</v>
-      </c>
-      <c r="N29" s="7">
-        <v>2</v>
-      </c>
-      <c r="O29" s="8">
-        <v>0.2634201695928</v>
-      </c>
-      <c r="P29" s="8">
-        <v>0.3126713810085349</v>
-      </c>
-      <c r="Q29" s="8">
-        <v>0.4239084493986652</v>
-      </c>
-      <c r="R29" s="7"/>
-      <c r="S29" s="8">
-        <v>0.00820406140790314</v>
-      </c>
-      <c r="T29" s="7">
-        <v>2</v>
-      </c>
-      <c r="U29" s="8">
-        <v>0.00820406140790314</v>
-      </c>
-      <c r="V29" s="8">
-        <v>0.4239084493986652</v>
-      </c>
-      <c r="W29" s="8">
-        <v>2.3</v>
-      </c>
-      <c r="X29" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y29" s="8">
-        <v>33.91267595189322</v>
-      </c>
-      <c r="Z29" s="8">
-        <v>33.91267595189322</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
   <si>
     <t>id_match</t>
   </si>
@@ -335,15 +335,6 @@
   </si>
   <si>
     <t>nantes</t>
-  </si>
-  <si>
-    <t>fVodXIra</t>
-  </si>
-  <si>
-    <t>reims</t>
-  </si>
-  <si>
-    <t>rennes</t>
   </si>
 </sst>
 </file>
@@ -753,7 +744,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -2910,86 +2901,6 @@
         <v>49.25088577807655</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
-      <c r="A28" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="5">
-        <v>25568.875300925927</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="7">
-        <v>55</v>
-      </c>
-      <c r="F28" s="7">
-        <v>551</v>
-      </c>
-      <c r="G28" s="7">
-        <v>3</v>
-      </c>
-      <c r="H28" s="8">
-        <v>3.4</v>
-      </c>
-      <c r="I28" s="8">
-        <v>2.38</v>
-      </c>
-      <c r="J28" s="8">
-        <v>0.3181818181818181</v>
-      </c>
-      <c r="K28" s="8">
-        <v>0.2807486631016043</v>
-      </c>
-      <c r="L28" s="8">
-        <v>0.4010695187165775</v>
-      </c>
-      <c r="M28" s="8">
-        <v>0.04761904761904767</v>
-      </c>
-      <c r="N28" s="7">
-        <v>2</v>
-      </c>
-      <c r="O28" s="8">
-        <v>0.234329403268049</v>
-      </c>
-      <c r="P28" s="8">
-        <v>0.3367897036040899</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>0.428880893127861</v>
-      </c>
-      <c r="R28" s="7">
-        <v>1</v>
-      </c>
-      <c r="S28" s="8">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="T28" s="7">
-        <v>2</v>
-      </c>
-      <c r="U28" s="8">
-        <v>0.02781137441128351</v>
-      </c>
-      <c r="V28" s="8">
-        <v>0.428880893127861</v>
-      </c>
-      <c r="W28" s="8">
-        <v>2.38</v>
-      </c>
-      <c r="X28" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y28" s="8">
-        <v>34.31047145022888</v>
-      </c>
-      <c r="Z28" s="8">
-        <v>34.31047145022888</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="104">
   <si>
     <t>id_match</t>
   </si>
@@ -326,15 +326,6 @@
   </si>
   <si>
     <t>psg</t>
-  </si>
-  <si>
-    <t>tnl8UGSH</t>
-  </si>
-  <si>
-    <t>monaco</t>
-  </si>
-  <si>
-    <t>nantes</t>
   </si>
 </sst>
 </file>
@@ -744,7 +735,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -753,8 +744,8 @@
     <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="10" max="10" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -794,10 +785,10 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="4" t="s">
@@ -2821,84 +2812,6 @@
       </c>
       <c r="Z26" s="8">
         <v>52.59185769314812</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="5">
-        <v>25568.875300925927</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E27" s="7">
-        <v>55</v>
-      </c>
-      <c r="F27" s="7">
-        <v>551</v>
-      </c>
-      <c r="G27" s="8">
-        <v>1.48</v>
-      </c>
-      <c r="H27" s="7">
-        <v>5</v>
-      </c>
-      <c r="I27" s="8">
-        <v>5.5</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0.6389405204460966</v>
-      </c>
-      <c r="K27" s="8">
-        <v>0.1891263940520446</v>
-      </c>
-      <c r="L27" s="8">
-        <v>0.1719330855018587</v>
-      </c>
-      <c r="M27" s="8">
-        <v>0.05749385749385749</v>
-      </c>
-      <c r="N27" s="7">
-        <v>1</v>
-      </c>
-      <c r="O27" s="8">
-        <v>0.6156360722259568</v>
-      </c>
-      <c r="P27" s="8">
-        <v>0.251132880122871</v>
-      </c>
-      <c r="Q27" s="8">
-        <v>0.133231047651172</v>
-      </c>
-      <c r="R27" s="7"/>
-      <c r="S27" s="8">
-        <v>-0.02330444822013977</v>
-      </c>
-      <c r="T27" s="7">
-        <v>1</v>
-      </c>
-      <c r="U27" s="8">
-        <v>-0.02330444822013977</v>
-      </c>
-      <c r="V27" s="8">
-        <v>0.6156360722259568</v>
-      </c>
-      <c r="W27" s="8">
-        <v>1.48</v>
-      </c>
-      <c r="X27" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y27" s="8">
-        <v>49.25088577807655</v>
-      </c>
-      <c r="Z27" s="8">
-        <v>49.25088577807655</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="130">
   <si>
     <t>id_match</t>
   </si>
@@ -386,6 +386,15 @@
   </si>
   <si>
     <t>dif_prob_mod_bm &lt; 0.0</t>
+  </si>
+  <si>
+    <t>prueba</t>
+  </si>
+  <si>
+    <t>Boca</t>
+  </si>
+  <si>
+    <t>River</t>
   </si>
   <si>
     <t>jPP565dL</t>
@@ -414,7 +423,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -467,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -481,20 +490,23 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -816,38 +828,38 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:Z33"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,12 +939,12 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>27</v>
@@ -1005,12 +1017,12 @@
         <v>28.46215537952682</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>31</v>
@@ -1083,12 +1095,12 @@
         <v>18.90253033349989</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B4" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>34</v>
@@ -1161,12 +1173,12 @@
         <v>23.33863088145612</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B5" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>37</v>
@@ -1239,12 +1251,12 @@
         <v>18.47938501250129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>40</v>
@@ -1317,12 +1329,12 @@
         <v>19.89322222039439</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B7" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>43</v>
@@ -1395,12 +1407,12 @@
         <v>19.69907647661568</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>46</v>
@@ -1473,12 +1485,12 @@
         <v>23.18244346688417</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>49</v>
@@ -1551,12 +1563,12 @@
         <v>20.42299002018799</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B10" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>52</v>
@@ -1629,12 +1641,12 @@
         <v>26.7980358435261</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>55</v>
@@ -1707,12 +1719,12 @@
         <v>25.86109069707436</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>58</v>
@@ -1787,12 +1799,12 @@
         <v>60.40066288573521</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B13" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>61</v>
@@ -1867,12 +1879,12 @@
         <v>57.40947653436852</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B14" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>64</v>
@@ -1947,12 +1959,12 @@
         <v>33.83126953905438</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>67</v>
@@ -2027,12 +2039,12 @@
         <v>39.64541637632485</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B16" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>70</v>
@@ -2107,12 +2119,12 @@
         <v>32.22235954645397</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B17" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>73</v>
@@ -2187,12 +2199,12 @@
         <v>46.84798552903081</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B18" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>76</v>
@@ -2267,12 +2279,12 @@
         <v>37.72802214730521</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>78</v>
       </c>
       <c r="B19" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>79</v>
@@ -2352,7 +2364,7 @@
         <v>81</v>
       </c>
       <c r="B20" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>82</v>
@@ -2432,7 +2444,7 @@
         <v>84</v>
       </c>
       <c r="B21" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>85</v>
@@ -2510,7 +2522,7 @@
         <v>88</v>
       </c>
       <c r="B22" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>89</v>
@@ -2588,7 +2600,7 @@
         <v>92</v>
       </c>
       <c r="B23" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>93</v>
@@ -2666,7 +2678,7 @@
         <v>95</v>
       </c>
       <c r="B24" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>96</v>
@@ -2744,7 +2756,7 @@
         <v>98</v>
       </c>
       <c r="B25" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>99</v>
@@ -2822,7 +2834,7 @@
         <v>101</v>
       </c>
       <c r="B26" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>102</v>
@@ -2900,7 +2912,7 @@
         <v>104</v>
       </c>
       <c r="B27" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>105</v>
@@ -2978,7 +2990,7 @@
         <v>107</v>
       </c>
       <c r="B28" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>108</v>
@@ -3058,7 +3070,7 @@
         <v>110</v>
       </c>
       <c r="B29" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>111</v>
@@ -3136,7 +3148,7 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>114</v>
@@ -3214,7 +3226,7 @@
         <v>117</v>
       </c>
       <c r="B31" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>118</v>
@@ -3292,7 +3304,7 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.875300925927</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>121</v>
@@ -3366,11 +3378,11 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="17.25">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B33" s="5">
-        <v>25568.875295925925</v>
+        <v>25568.375300925927</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>125</v>
@@ -3385,61 +3397,139 @@
         <v>771</v>
       </c>
       <c r="G33" s="8">
-        <v>6.25</v>
+        <v>1.29</v>
       </c>
       <c r="H33" s="8">
-        <v>4.75</v>
-      </c>
-      <c r="I33" s="8">
-        <v>1.44</v>
+        <v>5.75</v>
+      </c>
+      <c r="I33" s="7">
+        <v>9</v>
       </c>
       <c r="J33" s="8">
-        <v>0.1502388666190764</v>
+        <v>0.7311645650100667</v>
       </c>
       <c r="K33" s="8">
-        <v>0.1976827192356268</v>
+        <v>0.1640351806718237</v>
       </c>
       <c r="L33" s="8">
-        <v>0.6520784141452967</v>
+        <v>0.1048002543181096</v>
       </c>
       <c r="M33" s="8">
-        <v>0.06497076023391823</v>
+        <v>0.06021795303898436</v>
       </c>
       <c r="N33" s="7">
         <v>1</v>
       </c>
       <c r="O33" s="8">
-        <v>0.4266061492187417</v>
+        <v>0.6433210241393781</v>
       </c>
       <c r="P33" s="8">
-        <v>0.317368551131377</v>
+        <v>0.2833053216314175</v>
       </c>
       <c r="Q33" s="8">
-        <v>0.2560252996498812</v>
+        <v>0.07337365422920432</v>
       </c>
       <c r="R33" s="9"/>
       <c r="S33" s="8">
+        <v>-0.08784354087068857</v>
+      </c>
+      <c r="T33" s="7">
+        <v>-1</v>
+      </c>
+      <c r="U33" s="8">
+        <v>0.08784354087068857</v>
+      </c>
+      <c r="V33" s="8">
+        <v>0.3566789758606219</v>
+      </c>
+      <c r="W33" s="8">
+        <v>3.508474576271186</v>
+      </c>
+      <c r="X33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y33" s="8">
+        <v>17.83394879303109</v>
+      </c>
+      <c r="Z33" s="8">
+        <v>17.83394879303109</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+      <c r="A34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="5">
+        <v>25568.875300925927</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="7">
+        <v>77</v>
+      </c>
+      <c r="F34" s="7">
+        <v>771</v>
+      </c>
+      <c r="G34" s="8">
+        <v>6.25</v>
+      </c>
+      <c r="H34" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="I34" s="8">
+        <v>1.44</v>
+      </c>
+      <c r="J34" s="8">
+        <v>0.1502388666190764</v>
+      </c>
+      <c r="K34" s="8">
+        <v>0.1976827192356268</v>
+      </c>
+      <c r="L34" s="8">
+        <v>0.6520784141452967</v>
+      </c>
+      <c r="M34" s="8">
+        <v>0.06497076023391823</v>
+      </c>
+      <c r="N34" s="7">
+        <v>1</v>
+      </c>
+      <c r="O34" s="8">
+        <v>0.4266061492187417</v>
+      </c>
+      <c r="P34" s="8">
+        <v>0.317368551131377</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>0.2560252996498812</v>
+      </c>
+      <c r="R34" s="9"/>
+      <c r="S34" s="8">
         <v>0.2763672825996653</v>
       </c>
-      <c r="T33" s="7">
-        <v>1</v>
-      </c>
-      <c r="U33" s="8">
+      <c r="T34" s="7">
+        <v>1</v>
+      </c>
+      <c r="U34" s="8">
         <v>0.2763672825996653</v>
       </c>
-      <c r="V33" s="8">
+      <c r="V34" s="8">
         <v>0.4266061492187417</v>
       </c>
-      <c r="W33" s="8">
+      <c r="W34" s="8">
         <v>6.25</v>
       </c>
-      <c r="X33" s="6" t="s">
+      <c r="X34" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="Y33" s="8">
+      <c r="Y34" s="8">
         <v>21.33030746093709</v>
       </c>
-      <c r="Z33" s="8">
+      <c r="Z34" s="8">
         <v>21.33030746093709</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,227 +567,2377 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>80hEjzhl</t>
+          <t>hK8xvrmh</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45458.75</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>huracan</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ind  rivadavia</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>2.05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5696460056964601</v>
+        <v>0.2866854423618529</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2718025227180252</v>
+        <v>0.2588132465766728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1585514715855147</v>
+        <v>0.4545013110614742</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05118334759053322</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+        <v>0.07327496351886609</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2405712749555847</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3047180572764508</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4547106677679645</v>
+      </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0.0002093567064903601</v>
+      </c>
       <c r="T2" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0002093567064903601</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4547106677679645</v>
+      </c>
       <c r="W2" t="n">
-        <v>1.30638852672751</v>
+        <v>2.05</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>22.73553338839823</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22.73553338839823</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ChkVnhiD</t>
+          <t>rwisKhLu</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45458.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atl  tucuman</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>defensa y justicia</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>167</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
         <v>3.4</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J3" t="n">
-        <v>0.4931894569255263</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2770564302140457</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2297541128604281</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06158029550729749</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2991182851373308</v>
+        <v>0.2346391503667156</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3871825052785184</v>
+        <v>0.3932230744752567</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3136992095841509</v>
+        <v>0.3721377751580278</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1101260750644728</v>
+        <v>0.1310944546933838</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1101260750644728</v>
+        <v>0.1310944546933838</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3871825052785184</v>
+        <v>0.3932230744752567</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>19.35912526392592</v>
+        <v>19.66115372376283</v>
       </c>
       <c r="Z3" t="n">
-        <v>19.35912526392592</v>
+        <v>19.66115372376283</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UHaVQ4y2</t>
+          <t>2u7rIWkh</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45459.54166666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>river plate</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>talleres cordoba</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4792284866468843</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2459198813056379</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2748516320474777</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07009605461617863</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3055089573397518</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3831750237444987</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3113160189157493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1372551424388608</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1372551424388608</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3831750237444987</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>19.15875118722494</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>19.15875118722494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3461313584096667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2572597934125901</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3966088481777431</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05057330057330067</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4505947056993999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4045720753855079</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1448332189150922</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1044633472897332</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1044633472897332</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4505947056993999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>22.52973528496999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22.52973528496999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4276704769412693</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2688214426487978</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.303508080409933</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06284038542103043</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1818075392583132</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3904373506291662</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4277551101125207</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1242470297025876</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1242470297025876</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4277551101125207</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>21.38775550562603</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21.38775550562603</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.540711462450593</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2490118577075099</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2102766798418973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05680868838763553</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4488093302829228</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3709170360414691</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1802736336756081</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.09190213216767018</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.09190213216767018</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5511906697170772</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.060240963855422</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>27.55953348585386</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>27.55953348585386</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2690265486725664</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2353982300884956</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.495575221238938</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.06203007518796988</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1680032805977818</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2809564326988208</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5510402867033973</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.05546506546445928</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.05546506546445928</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5510402867033973</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>27.55201433516986</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27.55201433516986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4569015166058744</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2754847379535419</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2676137454405835</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06763681082188988</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.402282078998908</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3889374590923115</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2087804619087806</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.05461943760696641</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.05461943760696641</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.597717921001092</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.72463768115942</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>29.8858960500546</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29.8858960500546</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4365343242714649</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2607079992176805</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3027576765108547</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06547470200883554</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.400264628302527</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3118599895825174</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2878753821149555</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.03626969596893787</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.03626969596893787</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.400264628302527</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>20.01323141512635</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20.01323141512635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2765957446808511</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3617021276595744</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06334841628959276</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3412578240487837</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3137801616037382</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3449620143474781</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.01674011331209629</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.01674011331209629</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3449620143474781</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>17.24810071737391</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17.24810071737391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.479807336050389</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2528714338643941</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2673212300852167</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.06880506880506898</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5599963916364866</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3240456798708019</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1159579284927115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.08018905558609762</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.08018905558609762</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5599963916364866</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>27.99981958182433</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>27.99981958182433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4697535474234503</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2539208364451083</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2763256161314414</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06438791732909377</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3090900172899541</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1907008098653671</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.03045562542122837</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.03045562542122837</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4895104895104894</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2447552447552447</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2657342657342657</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.07518796992481214</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3923500084565287</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2800914764928201</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3275585150506511</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.09716048105396069</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09716048105396069</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6076499915434712</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.821917808219178</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>30.38249957717356</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>30.38249957717356</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6861848124428179</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.192131747483989</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1216834400731931</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.09573934837092724</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.408017959212156</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1150749705470585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3903891133319158</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2698277695088242</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3397831171592601</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0900199323228108</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3253819680529937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2513405081079281</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I17" t="n">
         <v>6</v>
       </c>
-      <c r="F4" t="n">
-        <v>66</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
+      <c r="J17" t="n">
+        <v>0.6544202066590127</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.1928817451205511</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1526980482204363</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0914786967418546</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4661798452488833</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3456482867954284</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1881718679556882</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1882403614101294</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1882403614101294</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5338201547511168</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.651162790697675</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6102841677943167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2232746955345061</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1664411366711773</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.09238728750923864</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4276350697450202</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1091702149334762</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5292352777002512</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2474532514652525</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2233114708344962</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.09220739137558542</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3199702133278545</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1623382209493025</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4992690880467783</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2537951197571123</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2469357921961093</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09449613547974201</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4304832510879221</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3686093631115925</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2009073858004855</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.06878583695885626</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.06878583695885626</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5695167489120779</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.824657534246575</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5102040816326531</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0888888888888888</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3435369954829963</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1897475671897203</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3906945681211042</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2764915405164737</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3328138913624221</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1128452867583303</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3135793977055996</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2079312910238517</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.4028577852796484</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.07065718925890503</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.5264850254614466</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="n">
-        <v>0.4735149745385534</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.1</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>23.67574872692767</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>23.67574872692767</v>
+      <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4585987261146497</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2547770700636943</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2866242038216561</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09027777777777768</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3774133555331881</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2384831538055338</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5523077419979976</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2427247181938568</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2049675398081457</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.08418251216864503</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3526258454087228</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2759251177172362</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1287243186801842</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1287243186801842</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5251641137855581</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2450765864332604</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2297592997811816</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.088095238095238</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1954301815841236</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3442148757946548</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7319778188539741</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.166358595194085</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1016635859519408</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.09292929292929308</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4793928065542001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3185566013592205</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2020505920865793</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2525850122997739</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2525850122997739</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5206071934457999</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4093023255813953</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3348837209302326</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.08585858585858586</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.368000075623453</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2239901570746398</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5508222068321281</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2555203015026817</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1936574916651903</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.08710648877683225</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.3538440300735814</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2301342302325673</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1605014381911697</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1605014381911697</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>20.80108698469257</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20.80108698469257</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2940,6 +2940,958 @@
         <v>20.80108698469257</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.1701231053420433</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4524952111662364</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3773816834917204</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5475047888337636</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4405375110051294</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4230894896430598</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1363729993518108</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.5594624889948705</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2140892175606832</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3874330693163754</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3984777131229413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.6015222868770587</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.3210142189221316</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.3448927681068193</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3340930129710492</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6551072318931808</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4397980876637556</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3661867226453867</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1940151896908577</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5602019123362445</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.200679443572579</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3376986280188904</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4616219284085306</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5383780715914694</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.3059494346527558</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.3623815163361492</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.331669049011095</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.6376184836638508</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1785087379952683</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3693367624283796</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4521544995763522</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5478455004236478</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.346936232859121</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4508880293372253</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2021757378036537</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.5491119706627747</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.6262315915243915</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3151672014569159</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.05860120701869274</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.3737684084756085</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5643607621403911</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3212043496563672</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1144348882032416</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.4356392378596089</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.2797014227648949</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.3293223024325962</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3909762748025089</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.609023725197491</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3166315062169586</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4592724251668016</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2240960686162398</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5407275748331984</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3911719378101357</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4172096518199451</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.1916184103699192</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5827903481800549</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>29.13951740900275</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>29.13951740900275</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -854,25 +854,25 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3461313584096667</v>
+        <v>0.3373753178173283</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2572597934125901</v>
+        <v>0.2519069039702718</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3966088481777431</v>
+        <v>0.4107177782123997</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05057330057330067</v>
+        <v>0.05859213250517614</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -890,19 +890,19 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1044633472897332</v>
+        <v>0.1132193878820715</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1044633472897332</v>
+        <v>0.1132193878820715</v>
       </c>
       <c r="V5" t="n">
         <v>0.4505947056993999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1670,28 +1670,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3923500084565287</v>
+        <v>0.3903375422424893</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2800914764928201</v>
+        <v>0.277533799235872</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3275585150506511</v>
+        <v>0.3321286585216386</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09716048105396069</v>
+        <v>-0.09917294726800008</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09716048105396069</v>
+        <v>0.09917294726800008</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6076499915434712</v>
+        <v>0.6096624577575107</v>
       </c>
       <c r="W14" t="n">
         <v>1.821917808219178</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.48312288787553</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.48312288787553</v>
       </c>
     </row>
     <row r="15">

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -590,7 +590,7 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
         <v>3.6</v>
@@ -599,16 +599,16 @@
         <v>2.05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2866854423618529</v>
+        <v>0.2898664571877455</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2588132465766728</v>
+        <v>0.2576590730557737</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4545013110614742</v>
+        <v>0.4524744697564808</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07327496351886609</v>
+        <v>0.07808265582655838</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -626,13 +626,13 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002093567064903601</v>
+        <v>0.002236198011483781</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002093567064903601</v>
+        <v>0.002236198011483781</v>
       </c>
       <c r="V2" t="n">
         <v>0.4547106677679645</v>
@@ -854,25 +854,25 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3373753178173283</v>
+        <v>0.3691141260973663</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2519069039702718</v>
+        <v>0.25438946528332</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4107177782123997</v>
+        <v>0.3764964086193136</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05859213250517614</v>
+        <v>0.06242713301536851</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -890,19 +890,19 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1132193878820715</v>
+        <v>0.08148057960203353</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1132193878820715</v>
+        <v>0.08148057960203353</v>
       </c>
       <c r="V5" t="n">
         <v>0.4505947056993999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -942,25 +942,25 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="H6" t="n">
         <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4276704769412693</v>
+        <v>0.4374145674672915</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2688214426487978</v>
+        <v>0.2686975200156219</v>
       </c>
       <c r="L6" t="n">
-        <v>0.303508080409933</v>
+        <v>0.2938879125170865</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06284038542103043</v>
+        <v>0.06333056478405319</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -978,19 +978,19 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1242470297025876</v>
+        <v>0.1338671975954341</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1242470297025876</v>
+        <v>0.1338671975954341</v>
       </c>
       <c r="V6" t="n">
         <v>0.4277551101125207</v>
       </c>
       <c r="W6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4569015166058744</v>
+        <v>0.4814305364511692</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2754847379535419</v>
+        <v>0.2682255845942228</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2676137454405835</v>
+        <v>0.250343878954608</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06763681082188988</v>
+        <v>0.06520146520146519</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1242,19 +1242,19 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.05461943760696641</v>
+        <v>-0.07914845745226123</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05461943760696641</v>
+        <v>0.07914845745226123</v>
       </c>
       <c r="V9" t="n">
         <v>0.597717921001092</v>
       </c>
       <c r="W9" t="n">
-        <v>1.72463768115942</v>
+        <v>1.810344827586207</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1382,25 +1382,25 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.3236831523924407</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.268194611982308</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3617021276595744</v>
+        <v>0.4081222356252514</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06334841628959276</v>
+        <v>0.06532448061683449</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1418,30 +1418,30 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.01674011331209629</v>
+        <v>-0.06316022127777321</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01674011331209629</v>
+        <v>0.06316022127777321</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3449620143474781</v>
+        <v>0.6550379856525219</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>1.5859375</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>17.24810071737391</v>
+        <v>32.7518992826261</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.24810071737391</v>
+        <v>32.7518992826261</v>
       </c>
     </row>
     <row r="12">
@@ -1558,25 +1558,25 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4697535474234503</v>
+        <v>0.4881988033623316</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2539208364451083</v>
+        <v>0.2453841353742245</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2763256161314414</v>
+        <v>0.2664170612634438</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06438791732909377</v>
+        <v>0.07243238987521172</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1594,19 +1594,19 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03045562542122837</v>
+        <v>0.01201036948234713</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.03045562542122837</v>
+        <v>0.01201036948234713</v>
       </c>
       <c r="V13" t="n">
         <v>0.5002091728446787</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1649,52 +1649,52 @@
         <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
         <v>3.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4895104895104894</v>
+        <v>0.492601948754962</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2447552447552447</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2657342657342657</v>
+        <v>0.2674124864669793</v>
       </c>
       <c r="M14" t="n">
-        <v>0.07518796992481214</v>
+        <v>0.06844033159822649</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3903375422424893</v>
+        <v>0.3923500084565287</v>
       </c>
       <c r="P14" t="n">
-        <v>0.277533799235872</v>
+        <v>0.2800914764928201</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3321286585216386</v>
+        <v>0.3275585150506511</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09917294726800008</v>
+        <v>-0.1002519402984333</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09917294726800008</v>
+        <v>0.1002519402984333</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6096624577575107</v>
+        <v>0.6076499915434712</v>
       </c>
       <c r="W14" t="n">
-        <v>1.821917808219178</v>
+        <v>1.844594594594594</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.48312288787553</v>
+        <v>30.38249957717356</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.48312288787553</v>
+        <v>30.38249957717356</v>
       </c>
     </row>
     <row r="15">

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45462.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45462.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45462.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45462.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45462.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45462.86458333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45462.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45462.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45462.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45462.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45462.89583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1530,182 +1530,6 @@
       </c>
       <c r="Z12" t="n">
         <v>27.99981958182433</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tflZ7nSp</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>167</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.4881988033623316</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2453841353742245</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.2664170612634438</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.07243238987521172</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.5002091728446787</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.3090900172899541</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1907008098653671</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.01201036948234713</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.01201036948234713</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.5002091728446787</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>25.01045864223394</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>25.01045864223394</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>raSHWV4o</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>167</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.492601948754962</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2399855647780585</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2674124864669793</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.06844033159822649</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.3923500084565287</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.2800914764928201</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3275585150506511</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.1002519402984333</v>
-      </c>
-      <c r="T14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1002519402984333</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.6076499915434712</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.844594594594594</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>30.38249957717356</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>30.38249957717356</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.85416666666</v>
+        <v>45462.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.86458333334</v>
+        <v>45462.98958333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45462.89583333334</v>
+        <v>45463.02083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,7 +590,7 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H2" t="n">
         <v>3.6</v>
@@ -599,16 +599,16 @@
         <v>2.05</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2898664571877455</v>
+        <v>0.2866854423618529</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2576590730557737</v>
+        <v>0.2588132465766728</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4524744697564808</v>
+        <v>0.4545013110614742</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07808265582655838</v>
+        <v>0.07327496351886609</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -626,13 +626,13 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002236198011483781</v>
+        <v>0.0002093567064903601</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.002236198011483781</v>
+        <v>0.0002093567064903601</v>
       </c>
       <c r="V2" t="n">
         <v>0.4547106677679645</v>
@@ -1530,6 +1530,182 @@
       </c>
       <c r="Z12" t="n">
         <v>27.99981958182433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4881988033623316</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2453841353742245</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2664170612634438</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.07243238987521172</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3090900172899541</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1907008098653671</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01201036948234713</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01201036948234713</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.492601948754962</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2399855647780585</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2674124864669793</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.06844033159822649</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3923500084565287</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2800914764928201</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3275585150506511</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1002519402984333</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1002519402984333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6076499915434712</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.844594594594594</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>30.38249957717356</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>30.38249957717356</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -1670,28 +1670,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3923500084565287</v>
+        <v>0.391679062020431</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2800914764928201</v>
+        <v>0.280281519357685</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3275585150506511</v>
+        <v>0.328039418621884</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1002519402984333</v>
+        <v>-0.100922886734531</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1002519402984333</v>
+        <v>0.100922886734531</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6076499915434712</v>
+        <v>0.608320937979569</v>
       </c>
       <c r="W14" t="n">
         <v>1.844594594594594</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.41604689897845</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.41604689897845</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,28 +1670,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.391679062020431</v>
+        <v>0.3908435178451044</v>
       </c>
       <c r="P14" t="n">
-        <v>0.280281519357685</v>
+        <v>0.2811927328105432</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.328039418621884</v>
+        <v>0.3279637493443524</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.100922886734531</v>
+        <v>-0.1017584309098576</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.100922886734531</v>
+        <v>0.1017584309098576</v>
       </c>
       <c r="V14" t="n">
-        <v>0.608320937979569</v>
+        <v>0.6091564821548956</v>
       </c>
       <c r="W14" t="n">
         <v>1.844594594594594</v>
@@ -1702,10 +1702,2194 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.41604689897845</v>
+        <v>30.45782410774478</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.41604689897845</v>
+        <v>30.45782410774478</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6861848124428179</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.192131747483989</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1216834400731931</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.09573934837092724</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.408017959212156</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1150749705470585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3903891133319158</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2698277695088242</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3397831171592601</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0900199323228108</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3253819680529937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2513405081079281</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.632183908045977</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2022988505747126</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1655172413793104</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0984848484848484</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4661798452488833</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3456482867954284</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1881718679556882</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1660040627970937</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1660040627970937</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5338201547511168</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6102841677943167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2232746955345061</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1664411366711773</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.09238728750923864</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4276350697450202</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1091702149334762</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5292352777002512</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2474532514652525</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2233114708344962</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.09220739137558542</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3199702133278545</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1623382209493025</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4992690880467783</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2537951197571123</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2469357921961093</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09449613547974201</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4304832510879221</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3686093631115925</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2009073858004855</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.06878583695885626</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.06878583695885626</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5695167489120779</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.824657534246575</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5102040816326531</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0888888888888888</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3435369954829963</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1897475671897203</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3906945681211042</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2764915405164737</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3328138913624221</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1128452867583303</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3135793977055996</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2079312910238517</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4585987261146497</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2547770700636943</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2866242038216561</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09027777777777768</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3774133555331881</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2384831538055338</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5523077419979976</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2427247181938568</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2049675398081457</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.08418251216864503</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3526258454087228</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2759251177172362</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1287243186801842</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1287243186801842</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5251641137855581</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2450765864332604</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2297592997811816</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.088095238095238</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1954301815841236</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3442148757946548</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7319778188539741</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.166358595194085</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1016635859519408</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.09292929292929308</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4793928065542001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3185566013592205</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2020505920865793</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2525850122997739</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2525850122997739</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5206071934457999</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4093023255813953</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3348837209302326</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.08585858585858586</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.368000075623453</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2239901570746398</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5694760820045558</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2460136674259681</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1845102505694761</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.08395061728395059</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.3538440300735814</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2301342302325673</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1700080722678833</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1700080722678833</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>20.80108698469257</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20.80108698469257</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.1701231053420433</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4524952111662364</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3773816834917204</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5475047888337636</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4405375110051294</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4230894896430598</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1363729993518108</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.5594624889948705</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2140892175606832</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3874330693163754</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3984777131229413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.6015222868770587</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.3210142189221316</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.3448927681068193</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3340930129710492</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6551072318931808</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4397980876637556</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3661867226453867</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1940151896908577</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5602019123362445</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.200679443572579</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3376986280188904</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4616219284085306</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5383780715914694</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.3059494346527558</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.3623815163361492</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.331669049011095</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.6376184836638508</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1785087379952683</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3693367624283796</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4521544995763522</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5478455004236478</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.346936232859121</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4508880293372253</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2021757378036537</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.5491119706627747</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.6262315915243915</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3151672014569159</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.05860120701869274</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.3737684084756085</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5643607621403911</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3212043496563672</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1144348882032416</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.4356392378596089</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.2797014227648949</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.3293223024325962</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3909762748025089</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.609023725197491</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3166315062169586</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4592724251668016</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2240960686162398</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5407275748331984</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3911719378101357</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4172096518199451</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.1916184103699192</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5827903481800549</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>29.13951740900275</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>29.13951740900275</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,14 +429,1283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>prob_home_bm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>prob_draw_bm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>prob_away_bm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>overround</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_result</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>copiado_formaciones</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>result_to_bet</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>odd_to_bet</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>id_match</t>
-        </is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2866854423618529</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2588132465766728</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4545013110614742</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.07327496351886609</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.2405712749555847</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3047180572764508</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4547106677679645</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.0002093567064903601</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0002093567064903601</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4547106677679645</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>22.73553338839823</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22.73553338839823</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>167</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2346391503667156</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3932230744752567</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.3721377751580278</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1310944546933838</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.1310944546933838</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.3932230744752567</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>19.66115372376283</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>19.66115372376283</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4792284866468843</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2459198813056379</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2748516320474777</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.07009605461617863</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3055089573397518</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.3831750237444987</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.3113160189157493</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1372551424388608</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1372551424388608</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.3831750237444987</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>19.15875118722494</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>19.15875118722494</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3691141260973663</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.25438946528332</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.3764964086193136</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06242713301536851</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4505947056993999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4045720753855079</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1448332189150922</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.08148057960203353</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.08148057960203353</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4505947056993999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>22.52973528496999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>22.52973528496999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4374145674672915</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2686975200156219</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2938879125170865</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06333056478405319</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1818075392583132</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.3904373506291662</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4277551101125207</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1338671975954341</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1338671975954341</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4277551101125207</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>21.38775550562603</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21.38775550562603</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.540711462450593</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2490118577075099</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2102766798418973</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05680868838763553</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4488093302829228</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.3709170360414691</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1802736336756081</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.09190213216767018</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.09190213216767018</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5511906697170772</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.060240963855422</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>27.55953348585386</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>27.55953348585386</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2690265486725664</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2353982300884956</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.495575221238938</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.06203007518796988</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1680032805977818</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.2809564326988208</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5510402867033973</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.05546506546445928</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.05546506546445928</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5510402867033973</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>27.55201433516986</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27.55201433516986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4640029460504511</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2717731541152641</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2642238998342846</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.05129694154084419</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.402282078998908</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3889374590923115</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2087804619087806</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.06172086705154306</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.06172086705154306</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.597717921001092</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.774647887323944</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>29.8858960500546</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>29.8858960500546</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4365343242714649</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2607079992176805</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3027576765108547</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06547470200883554</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.400264628302527</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3118599895825174</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2878753821149555</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0.03626969596893787</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.03626969596893787</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.400264628302527</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>20.01323141512635</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20.01323141512635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3480113636363636</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2684659090909091</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3835227272727272</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06424792139077851</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3412578240487837</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3137801616037382</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3449620143474781</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.0385607129252491</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.0385607129252491</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3449620143474781</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>17.24810071737391</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17.24810071737391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.479807336050389</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2528714338643941</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2673212300852167</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.06880506880506898</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5599963916364866</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3240456798708019</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1159579284927115</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.08018905558609762</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.08018905558609762</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5599963916364866</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>27.99981958182433</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>27.99981958182433</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4895104895104894</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2447552447552447</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2657342657342657</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.07518796992481214</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3090900172899541</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1907008098653671</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01069868333418927</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01069868333418927</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5002091728446787</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>25.01045864223394</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.492601948754962</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2399855647780585</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2674124864669793</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.06844033159822649</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3923500084565287</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.2800914764928201</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3275585150506511</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0.1002519402984333</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1002519402984333</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6076499915434712</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.844594594594594</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>30.38249957717356</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>30.38249957717356</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,19 +596,19 @@
         <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2866854423618529</v>
+        <v>0.2928767382461451</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2588132465766728</v>
+        <v>0.2644026109166588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4545013110614742</v>
+        <v>0.4427206508371961</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07327496351886609</v>
+        <v>0.05058636453985299</v>
       </c>
       <c r="N2" t="n">
         <v>2</v>
@@ -626,19 +626,19 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002093567064903601</v>
+        <v>0.01199001693076845</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002093567064903601</v>
+        <v>0.01199001693076845</v>
       </c>
       <c r="V2" t="n">
         <v>0.4547106677679645</v>
       </c>
       <c r="W2" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -678,25 +678,25 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2727272727272728</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2727272727272728</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.04761904761904745</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -714,19 +714,19 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1310944546933838</v>
+        <v>0.1204958017479839</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1310944546933838</v>
+        <v>0.1204958017479839</v>
       </c>
       <c r="V3" t="n">
         <v>0.3932230744752567</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
@@ -775,16 +775,16 @@
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4792284866468843</v>
+        <v>0.472913616398243</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2459198813056379</v>
+        <v>0.2489019033674963</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2748516320474777</v>
+        <v>0.2781844802342606</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07009605461617863</v>
+        <v>0.05727554179566563</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -802,13 +802,13 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1372551424388608</v>
+        <v>0.1342731203770024</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1372551424388608</v>
+        <v>0.1342731203770024</v>
       </c>
       <c r="V4" t="n">
         <v>0.3831750237444987</v>
@@ -854,25 +854,25 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3691141260973663</v>
+        <v>0.3291753291753292</v>
       </c>
       <c r="K5" t="n">
-        <v>0.25438946528332</v>
+        <v>0.2494802494802495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3764964086193136</v>
+        <v>0.4213444213444213</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06242713301536851</v>
+        <v>0.05482456140350878</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
@@ -890,19 +890,19 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08148057960203353</v>
+        <v>0.1214193765240707</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08148057960203353</v>
+        <v>0.1214193765240707</v>
       </c>
       <c r="V5" t="n">
         <v>0.4505947056993999</v>
       </c>
       <c r="W5" t="n">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -948,19 +948,19 @@
         <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4374145674672915</v>
+        <v>0.4413450515857852</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2686975200156219</v>
+        <v>0.2711119602598395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2938879125170865</v>
+        <v>0.2875429881543752</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06333056478405319</v>
+        <v>0.05386086781435617</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
@@ -978,19 +978,19 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1338671975954341</v>
+        <v>0.1402121219581454</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1338671975954341</v>
+        <v>0.1402121219581454</v>
       </c>
       <c r="V6" t="n">
         <v>0.4277551101125207</v>
       </c>
       <c r="W6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1030,25 +1030,25 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
         <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.540711462450593</v>
+        <v>0.5503745604647607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.238036997401009</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2102766798418973</v>
+        <v>0.2115884421342302</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05680868838763553</v>
+        <v>0.05025690430314711</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
@@ -1066,19 +1066,19 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.09190213216767018</v>
+        <v>-0.1015652301818379</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09190213216767018</v>
+        <v>0.1015652301818379</v>
       </c>
       <c r="V7" t="n">
         <v>0.5511906697170772</v>
       </c>
       <c r="W7" t="n">
-        <v>2.060240963855422</v>
+        <v>2.117647058823529</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1118,25 +1118,25 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2690265486725664</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2353982300884956</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="L8" t="n">
-        <v>0.495575221238938</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06203007518796988</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
@@ -1154,19 +1154,19 @@
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05546506546445928</v>
+        <v>0.05304609663561477</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.05546506546445928</v>
+        <v>0.05304609663561477</v>
       </c>
       <c r="V8" t="n">
         <v>0.5510402867033973</v>
       </c>
       <c r="W8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1206,25 +1206,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4640029460504511</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2717731541152641</v>
+        <v>0.2727272727272728</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2642238998342846</v>
+        <v>0.2727272727272728</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05129694154084419</v>
+        <v>0.04761904761904745</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1242,19 +1242,19 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.06172086705154306</v>
+        <v>-0.05226337554654659</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06172086705154306</v>
+        <v>0.05226337554654659</v>
       </c>
       <c r="V9" t="n">
         <v>0.597717921001092</v>
       </c>
       <c r="W9" t="n">
-        <v>1.774647887323944</v>
+        <v>1.75</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1294,25 +1294,25 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4365343242714649</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2607079992176805</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3027576765108547</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06547470200883554</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -1330,30 +1330,30 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.03626969596893787</v>
+        <v>-0.05094800565122365</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.03626969596893787</v>
+        <v>0.05094800565122365</v>
       </c>
       <c r="V10" t="n">
-        <v>0.400264628302527</v>
+        <v>0.5997353716974729</v>
       </c>
       <c r="W10" t="n">
-        <v>2.15</v>
+        <v>1.726618705035971</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>20.01323141512635</v>
+        <v>29.98676858487365</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.01323141512635</v>
+        <v>29.98676858487365</v>
       </c>
     </row>
     <row r="11">
@@ -1382,25 +1382,25 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="H11" t="n">
         <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3480113636363636</v>
+        <v>0.3465346534653466</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2684659090909091</v>
+        <v>0.2722772277227723</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3835227272727272</v>
+        <v>0.3811881188118812</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06424792139077851</v>
+        <v>0.04935064935064926</v>
       </c>
       <c r="N11" t="n">
         <v>2</v>
@@ -1418,19 +1418,19 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0385607129252491</v>
+        <v>-0.03622610446440311</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0385607129252491</v>
+        <v>-0.03622610446440311</v>
       </c>
       <c r="V11" t="n">
         <v>0.3449620143474781</v>
       </c>
       <c r="W11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1470,25 +1470,25 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.479807336050389</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2528714338643941</v>
+        <v>0.2374100719424461</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2673212300852167</v>
+        <v>0.2877697841726619</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06880506880506898</v>
+        <v>0.05303030303030298</v>
       </c>
       <c r="N12" t="n">
         <v>1</v>
@@ -1506,19 +1506,19 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.08018905558609762</v>
+        <v>0.08517624775159449</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08018905558609762</v>
+        <v>0.08517624775159449</v>
       </c>
       <c r="V12" t="n">
         <v>0.5599963916364866</v>
       </c>
       <c r="W12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1558,25 +1558,25 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4895104895104894</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2447552447552447</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2657342657342657</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="M13" t="n">
-        <v>0.07518796992481214</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1594,19 +1594,19 @@
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01069868333418927</v>
+        <v>0.002214982776896135</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01069868333418927</v>
+        <v>0.002214982776896135</v>
       </c>
       <c r="V13" t="n">
         <v>0.5002091728446787</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1646,55 +1646,55 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.492601948754962</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2674124864669793</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06844033159822649</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3923500084565287</v>
+        <v>0.3903375422424893</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2800914764928201</v>
+        <v>0.277533799235872</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3275585150506511</v>
+        <v>0.3321286585216386</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1002519402984333</v>
+        <v>-0.1076566478252932</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1002519402984333</v>
+        <v>0.1076566478252932</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6076499915434712</v>
+        <v>0.6096624577575107</v>
       </c>
       <c r="W14" t="n">
-        <v>1.844594594594594</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -1702,10 +1702,2806 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.48312288787553</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.38249957717356</v>
+        <v>30.48312288787553</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>z7pPU9Zc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6861848124428179</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.192131747483989</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1216834400731931</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.09573934837092724</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.408017959212156</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1150749705470585</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.2847753227567967</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4769070702407857</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23.84535351203928</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EcqTTTl4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3903891133319158</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2698277695088242</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3397831171592601</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0900199323228108</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3253819680529937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2513405081079281</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.03288841050716229</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4232775238390781</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>21.16387619195391</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>tpoLVkKi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.632183908045977</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.2022988505747126</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1655172413793104</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0984848484848484</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4661798452488833</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3456482867954284</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1881718679556882</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-0.1660040627970937</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.1660040627970937</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.5338201547511168</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.475</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>26.69100773755584</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ln2oxMH4</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6102841677943167</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2232746955345061</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.1664411366711773</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.09238728750923864</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4276350697450202</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1091702149334762</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.2399200197869973</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.4631947153215034</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>23.15973576607517</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WYwYSm4A</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5292352777002512</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2474532514652525</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2233114708344962</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.09220739137558542</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3199702133278545</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1623382209493025</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-0.01154371197740844</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5176915657228428</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>25.88457828614214</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>APxxS7JG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4992690880467783</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2537951197571123</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.2469357921961093</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.09449613547974201</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4304832510879221</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3686093631115925</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2009073858004855</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-0.06878583695885626</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.06878583695885626</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5695167489120779</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.824657534246575</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28.4758374456039</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>4nxtRRYM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5102040816326531</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2448979591836735</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0888888888888888</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3435369954829963</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1897475671897203</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2218174781436099</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.4667154373272834</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23.33577186636417</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IktpQolT</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3906945681211042</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2764915405164737</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3328138913624221</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.1128452867583303</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.3135793977055996</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2079312910238517</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.08779474314944435</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.4784893112705486</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23.92446556352743</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OWICL5dp</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45466.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4585987261146497</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2547770700636943</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2866242038216561</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.09027777777777768</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.3774133555331881</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2384831538055338</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1293264205975839</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.3841034906612782</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>19.20517453306391</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Sx1kytXA</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5959637003927942</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2339157524041718</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.170120547203034</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.06876085697741741</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.3526258454087228</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2759251177172362</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1375332844698692</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1375332844698692</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.371449036874041</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>18.57245184370205</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2NHGKPBj</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45466.0625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5251641137855581</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2450765864332604</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2297592997811816</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.088095238095238</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1954301815841236</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3442148757946548</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2305956428400399</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.4603549426212216</v>
+      </c>
+      <c r="W25" t="n">
+        <v>4</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>23.01774713106108</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>UT5bq9li</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.7319778188539741</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.166358595194085</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1016635859519408</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.09292929292929308</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4793928065542001</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3185566013592205</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2020505920865793</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2525850122997739</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2525850122997739</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5206071934457999</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.413793103448276</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>26.03035967228999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Ma0gz0nH</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.4093023255813953</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2558139534883721</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.3348837209302326</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.08585858585858586</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.368000075623453</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2239901570746398</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.001292558279488321</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.408009767301907</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20.40048836509535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45466.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5694760820045558</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2460136674259681</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1845102505694761</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.08395061728395059</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.3538440300735814</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2301342302325673</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1700080722678833</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1700080722678833</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.4160217396938514</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>20.80108698469257</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20.80108698469257</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.1701231053420433</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.4524952111662364</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3773816834917204</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5475047888337636</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>27.37523944168818</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4405375110051294</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.4230894896430598</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1363729993518108</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.5594624889948705</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>27.97312444974353</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.2140892175606832</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3874330693163754</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.3984777131229413</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.6015222868770587</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>30.07611434385293</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.3210142189221316</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.3448927681068193</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3340930129710492</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6551072318931808</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>32.75536159465904</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4397980876637556</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3661867226453867</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1940151896908577</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5602019123362445</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>28.01009561681223</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.200679443572579</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3376986280188904</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4616219284085306</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5383780715914694</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>26.91890357957347</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.3059494346527558</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.3623815163361492</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.331669049011095</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.6376184836638508</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>31.88092418319254</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1785087379952683</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3693367624283796</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4521544995763522</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5478455004236478</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>27.39227502118239</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.346936232859121</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4508880293372253</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2021757378036537</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.5491119706627747</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>27.45559853313874</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.6262315915243915</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3151672014569159</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.05860120701869274</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.3737684084756085</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>18.68842042378043</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5643607621403911</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3212043496563672</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.1144348882032416</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.4356392378596089</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>21.78196189298044</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.2797014227648949</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.3293223024325962</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3909762748025089</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.609023725197491</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>30.45118625987455</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3166315062169586</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4592724251668016</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.2240960686162398</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5407275748331984</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>27.03637874165992</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3911719378101357</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4172096518199451</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.1916184103699192</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5827903481800549</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>29.13951740900275</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>29.13951740900275</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.3354504606422241</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.4891739188341286</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.1753756205236473</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>0.5108260811658714</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y43" t="n">
+        <v>25.54130405829357</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>25.54130405829357</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.1255411351049629</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.3610571309718373</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.5134017339231999</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>0.4865982660768001</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y44" t="n">
+        <v>24.32991330384001</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>24.32991330384001</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.1541506161478319</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.3482407220684662</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.4976086617837018</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>0.5023913382162981</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y45" t="n">
+        <v>25.11956691081491</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>25.11956691081491</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>167</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.3367617654003327</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.4777469848732029</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.1854912497264643</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>0.5222530151267971</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y46" t="n">
+        <v>26.11265075633986</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>26.11265075633986</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>167</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.116818733845915</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.3357400823768987</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.5474411837771862</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="n">
+        <v>0.4525588162228138</v>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y47" t="n">
+        <v>22.62794081114069</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>22.62794081114069</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>167</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.3450030962939342</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.4169885269337558</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.2380083767723101</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>0.5830114730662442</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y48" t="n">
+        <v>29.15057365331221</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>29.15057365331221</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>167</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.3406766056910624</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.3793663272157939</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.2799570670931436</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>0.6206336727842061</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y49" t="n">
+        <v>31.03168363921031</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>31.03168363921031</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>167</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.2473735871688839</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.3924595120673585</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.3601669007637577</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>0.6075404879326416</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y50" t="n">
+        <v>30.37702439663208</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>30.37702439663208</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>167</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.3452194871455411</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.3145744625272366</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.3402060503272223</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>0.6547805128544588</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y51" t="n">
+        <v>32.73902564272294</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>32.73902564272294</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -1054,28 +1054,28 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.3163272478320253</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.1521363844333992</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="W7" t="n">
         <v>4.1</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
     </row>
     <row r="8">
@@ -1670,28 +1670,28 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3670770600203078</v>
+        <v>0.3522794075213345</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
+        <v>0.2484961914130281</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="W14" t="n">
         <v>4</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
       <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,11 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,14 +429,1283 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A2"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>odds_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>odds_draw</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>odds_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>prob_home_bm</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>prob_draw_bm</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>prob_away_bm</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>overround</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>predicted_result</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>prob_class_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>copiado_formaciones</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>result_to_bet</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>prob_result_to_bet</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>odd_to_bet</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>multiplier</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>id_match</t>
-        </is>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>167</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2928767382461451</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2644026109166588</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4427206508371961</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05058636453985299</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1782451111666511</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.3571235536153105</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.4646313352180383</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02191068438084226</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02191068438084226</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.4646313352180383</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>32.52419346526268</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>32.52419346526268</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>167</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.2571887055520775</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.3187289200171914</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.4240823744307311</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.146534424073454</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.146534424073454</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.4240823744307311</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>29.68576621015118</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29.68576621015118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4851944345344275</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2365322868355333</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2782732786300393</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05693815987933637</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.3069573833806068</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.432377296398577</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.2606653202208161</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1958450095630437</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1958450095630437</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.432377296398577</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>30.26641074790039</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30.26641074790039</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.313989239046887</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2478862413528055</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4381245196003075</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0616075071399429</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5402763867114466</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.2716252169503502</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1880983963382031</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2262871476645597</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.2262871476645597</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5402763867114466</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>37.81934706980126</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>37.81934706980126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45462.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4415584415584415</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05335157318741457</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.05171002128636167</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.5831063597486422</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3651836189649961</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.303885580527863</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.303885580527863</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5831063597486422</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>40.81744518240495</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40.81744518240495</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45462.98958333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5579074690051407</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.231327487148473</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2107650438463864</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05435995536425953</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3137173358551308</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.5378148515394482</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.148467812605421</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.3064873643909752</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.3064873643909752</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5378148515394482</v>
+      </c>
+      <c r="W7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>37.64703960776137</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>37.64703960776137</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.286028602860286</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.242024202420242</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4719471947194719</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05944055944055959</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.1248404827603851</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.4023580553124324</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.4728014619271825</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0008542672077105906</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0008542672077105906</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.4728014619271825</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>33.09610233490277</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>33.09610233490277</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4545454545454546</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2727272727272728</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.04761904761904745</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2898941193190928</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4422466191872576</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2678592614936495</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1695193464599848</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1695193464599848</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.4422466191872576</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>30.95726334310803</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>30.95726334310803</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4509283819628647</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2705570291777188</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2785145888594164</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05602240896358546</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4957383107137407</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.3722175717727494</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1320441175135099</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.04480992875087608</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04480992875087608</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4957383107137407</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>34.70168174996185</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>34.70168174996185</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3647199046483909</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2634088200238379</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3718712753277712</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05455002513826046</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.3471049403890203</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3545298080055802</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2983652516053995</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.09112098798174229</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.09112098798174229</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.3545298080055802</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>24.81708656039061</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>24.81708656039061</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45463.02083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4880098022054963</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2321022230001751</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2798879747943288</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05084059890372661</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4856464530380509</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.378293936563841</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1360596103981081</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.00236334916744535</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.00236334916744535</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4856464530380509</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>33.99525171266357</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>33.99525171266357</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4971246449109679</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2315873345804753</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2712880205085568</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0531769341627597</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.4721479090124855</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.3170924136355052</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2107596773520092</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.02497673589848237</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0.02497673589848237</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4721479090124855</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.05035363087399</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>33.05035363087399</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45463.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2909090909090909</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05769230769230771</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3670770600203078</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4077433881239975</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2251795518556948</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1713797517603611</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.1713797517603611</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4077433881239975</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>28.54203716867982</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>28.54203716867982</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,20 +567,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -590,85 +590,85 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2928767382461451</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2644026109166588</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4427206508371961</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05058636453985299</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1782451111666511</v>
+        <v>0.4436791468412691</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3571235536153105</v>
+        <v>0.3705221432445802</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.1857987099141508</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02191068438084226</v>
+        <v>-0.1950173445860046</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02191068438084226</v>
+        <v>0.1950173445860046</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.5563208531587309</v>
       </c>
       <c r="W2" t="n">
-        <v>2.15</v>
+        <v>2.616279069767442</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -678,85 +678,85 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.449677174325864</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2552221800227877</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2951006456513482</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05896074646074645</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2571887055520775</v>
+        <v>0.3319918150420612</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3187289200171914</v>
+        <v>0.2821118769142622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -766,85 +766,85 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4851944345344275</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2365322868355333</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2782732786300393</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05693815987933637</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3069573833806068</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="P4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.3535581894345241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2606653202208161</v>
+        <v>0.08590345004264675</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="V4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
       <c r="Z4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -854,85 +854,85 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.313989239046887</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2478862413528055</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4381245196003075</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0616075071399429</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4065117704358618</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2716252169503502</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1880983963382031</v>
+        <v>0.1753929965717735</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
       <c r="Z5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -942,85 +942,85 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05171002128636167</v>
+        <v>0.4336241512981687</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.3839572154861549</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3651836189649961</v>
+        <v>0.1824186332156764</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.303885580527863</v>
+        <v>-0.1122160234211114</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.303885580527863</v>
+        <v>0.1122160234211114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.5663758487018313</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>2.079231692677071</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1030,85 +1030,85 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5579074690051407</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.231327487148473</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2107650438463864</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05435995536425953</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.4538576876343147</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.3445537488859154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.20158856347977</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>-0.07245810183936946</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.07245810183936946</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5461423123656852</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>austin fc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1118,85 +1118,85 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.286028602860286</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.242024202420242</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4719471947194719</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05944055944055959</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1248404827603851</v>
+        <v>0.3797770002987284</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4023580553124324</v>
+        <v>0.2412557721298951</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.3789672275713766</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>-0.1595488423979008</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>0.1595488423979008</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.6202229997012716</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.048780487804879</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
       <c r="Z8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1206,85 +1206,85 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04761904761904745</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2898941193190928</v>
+        <v>0.3757201307377791</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.3500274915414723</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2678592614936495</v>
+        <v>0.2742523777207485</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1695193464599848</v>
+        <v>-0.0528512978336495</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1695193464599848</v>
+        <v>0.0528512978336495</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.6242798692622209</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1294,85 +1294,85 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4509283819628647</v>
+        <v>0.5129935875801552</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2372595342558218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.2497468781640229</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.2618796408719433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3722175717727494</v>
+        <v>0.3590715274375488</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1320441175135099</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
       <c r="Z10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1382,85 +1382,85 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3647199046483909</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2634088200238379</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3718712753277712</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05455002513826046</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3471049403890203</v>
+        <v>0.3086285968254135</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2983652516053995</v>
+        <v>0.1597543509322801</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1470,85 +1470,85 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4880098022054963</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2321022230001751</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2798879747943288</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05084059890372661</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.289341441372672</v>
       </c>
       <c r="P12" t="n">
-        <v>0.378293936563841</v>
+        <v>0.243865103015309</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1360596103981081</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="W12" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
       <c r="Z12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1558,85 +1558,85 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4971246449109679</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2315873345804753</v>
+        <v>0.1871559633027523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2712880205085568</v>
+        <v>0.1247706422018349</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0531769341627597</v>
+        <v>0.06862745098039214</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.6190558219313727</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3170924136355052</v>
+        <v>0.3026384164933133</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2107596773520092</v>
+        <v>0.07830576157531427</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>-0.06901757256404017</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>0.06901757256404017</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.3809441780686273</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
       <c r="Z13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1646,66 +1646,154 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4044264527514825</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07499815581492324</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4727272727272727</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2363636363636364</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2909090909090909</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05769230769230771</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.3670770600203078</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="O15" t="n">
+        <v>0.4209874955756275</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1422568859883006</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="T15" t="n">
         <v>0</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="U15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="W15" t="n">
         <v>4</v>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>28.54203716867982</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>30.57289329052502</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>30.57289329052502</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4436791468412691</v>
+        <v>0.4436791468412699</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3705221432445802</v>
+        <v>0.3705221432445809</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1857987099141508</v>
+        <v>0.1857987099141491</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1950173445860046</v>
+        <v>-0.1950173445860038</v>
       </c>
       <c r="T2" t="n">
         <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1950173445860046</v>
+        <v>0.1950173445860038</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5563208531587309</v>
+        <v>0.55632085315873</v>
       </c>
       <c r="W2" t="n">
         <v>2.616279069767442</v>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.94245972111116</v>
+        <v>38.9424597211111</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.94245972111116</v>
+        <v>38.9424597211111</v>
       </c>
     </row>
     <row r="3">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -702,28 +702,28 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3319918150420612</v>
+        <v>0.3319918150420605</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2821118769142622</v>
+        <v>0.282111876914261</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3858963080436765</v>
+        <v>0.3858963080436785</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09079566239232822</v>
+        <v>0.09079566239233022</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09079566239232822</v>
+        <v>0.09079566239233022</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3858963080436765</v>
+        <v>0.3858963080436785</v>
       </c>
       <c r="W3" t="n">
         <v>3.2</v>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>27.01274156305735</v>
+        <v>27.01274156305749</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.01274156305735</v>
+        <v>27.01274156305749</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -790,28 +790,28 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5605383605228289</v>
+        <v>0.5605383605228302</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3535581894345241</v>
+        <v>0.3535581894345236</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08590345004264675</v>
+        <v>0.08590345004264613</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04929736921866623</v>
+        <v>-0.0492973692186649</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04929736921866623</v>
+        <v>-0.0492973692186649</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5605383605228289</v>
+        <v>0.5605383605228302</v>
       </c>
       <c r="W4" t="n">
         <v>1.55</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.23768523659803</v>
+        <v>39.23768523659812</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.23768523659803</v>
+        <v>39.23768523659812</v>
       </c>
     </row>
     <row r="5">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -878,28 +878,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4065117704358618</v>
+        <v>0.4065117704358609</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4180952329923645</v>
+        <v>0.4180952329923648</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1753929965717735</v>
+        <v>0.1753929965717745</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1998843898261959</v>
+        <v>0.1998843898261963</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1998843898261959</v>
+        <v>0.1998843898261963</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4180952329923645</v>
+        <v>0.4180952329923648</v>
       </c>
       <c r="W5" t="n">
         <v>4.33</v>
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>29.26666630946551</v>
+        <v>29.26666630946553</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.26666630946551</v>
+        <v>29.26666630946553</v>
       </c>
     </row>
     <row r="6">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4336241512981687</v>
+        <v>0.4336241512981688</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3839572154861549</v>
+        <v>0.3839572154861547</v>
       </c>
       <c r="Q6" t="n">
         <v>0.1824186332156764</v>
@@ -978,16 +978,16 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1122160234211114</v>
+        <v>-0.1122160234211113</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1122160234211114</v>
+        <v>0.1122160234211113</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5663758487018313</v>
+        <v>0.5663758487018312</v>
       </c>
       <c r="W6" t="n">
         <v>2.079231692677071</v>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1054,28 +1054,28 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4538576876343147</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3445537488859154</v>
+        <v>0.361204355622729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.20158856347977</v>
+        <v>0.1869015769799884</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07245810183936946</v>
+        <v>-0.07442172207640124</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07245810183936946</v>
+        <v>0.07442172207640124</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5461423123656852</v>
+        <v>0.5481059326027171</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.22996186559796</v>
+        <v>38.3674152821902</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.22996186559796</v>
+        <v>38.3674152821902</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1118,66 +1118,66 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3797770002987284</v>
+        <v>0.3773370378645719</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2412557721298951</v>
+        <v>0.2414047650172821</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3789672275713766</v>
+        <v>0.3812581971181459</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1595488423979008</v>
+        <v>0.1631742474035144</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1595488423979008</v>
+        <v>0.1631742474035144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6202229997012716</v>
+        <v>0.3812581971181459</v>
       </c>
       <c r="W8" t="n">
-        <v>2.048780487804879</v>
+        <v>4.33</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>43.41560997908901</v>
+        <v>26.68807379827021</v>
       </c>
       <c r="Z8" t="n">
-        <v>43.41560997908901</v>
+        <v>26.68807379827021</v>
       </c>
     </row>
     <row r="9">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1230,28 +1230,28 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3757201307377791</v>
+        <v>0.3757201307377797</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3500274915414723</v>
+        <v>0.3500274915414737</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2742523777207485</v>
+        <v>0.2742523777207464</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0528512978336495</v>
+        <v>-0.05285129783364895</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0528512978336495</v>
+        <v>0.05285129783364895</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6242798692622209</v>
+        <v>0.6242798692622203</v>
       </c>
       <c r="W9" t="n">
         <v>1.65</v>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>43.69959084835546</v>
+        <v>43.69959084835543</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.69959084835546</v>
+        <v>43.69959084835543</v>
       </c>
     </row>
     <row r="10">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1315,45 +1315,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2618796408719433</v>
+        <v>0.3720081039411632</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375488</v>
+        <v>0.337583047308818</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905077</v>
+        <v>0.2904088487500189</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1293019535264847</v>
+        <v>-0.140985483638992</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1293019535264847</v>
+        <v>0.140985483638992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3790488316905077</v>
+        <v>0.6279918960588368</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833554</v>
+        <v>43.95943272411857</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833554</v>
+        <v>43.95943272411857</v>
       </c>
     </row>
     <row r="11">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1406,28 +1406,28 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3086285968254135</v>
+        <v>0.3086285968254163</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5316170522423062</v>
+        <v>0.5316170522423029</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1597543509322801</v>
+        <v>0.1597543509322807</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3210907364528325</v>
+        <v>0.3210907364528293</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3210907364528325</v>
+        <v>0.3210907364528293</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5316170522423062</v>
+        <v>0.5316170522423029</v>
       </c>
       <c r="W11" t="n">
         <v>4.5</v>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.21319365696143</v>
+        <v>37.2131936569612</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.21319365696143</v>
+        <v>37.2131936569612</v>
       </c>
     </row>
     <row r="12">
@@ -1451,7 +1451,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1494,28 +1494,28 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.289341441372672</v>
+        <v>0.2928339855178089</v>
       </c>
       <c r="P12" t="n">
-        <v>0.243865103015309</v>
+        <v>0.2472243808527774</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4667934556120188</v>
+        <v>0.4599416336294134</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2329698794867369</v>
+        <v>0.2261180575041315</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2329698794867369</v>
+        <v>0.2261180575041315</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4667934556120188</v>
+        <v>0.4599416336294134</v>
       </c>
       <c r="W12" t="n">
         <v>4</v>
@@ -1526,10 +1526,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>32.67554189284132</v>
+        <v>32.19591435405894</v>
       </c>
       <c r="Z12" t="n">
-        <v>32.67554189284132</v>
+        <v>32.19591435405894</v>
       </c>
     </row>
     <row r="13">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1582,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6190558219313727</v>
+        <v>0.6149171520084532</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3026384164933133</v>
+        <v>0.3027250780585539</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07830576157531427</v>
+        <v>0.0823577699329931</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06901757256404017</v>
+        <v>-0.07315624248695962</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06901757256404017</v>
+        <v>0.07315624248695962</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3809441780686273</v>
+        <v>0.3850828479915468</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.66609246480391</v>
+        <v>26.95579935940827</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.66609246480391</v>
+        <v>26.95579935940827</v>
       </c>
     </row>
     <row r="14">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1670,28 +1670,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5205753914335942</v>
+        <v>0.520575391433595</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4044264527514825</v>
+        <v>0.4044264527514819</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07499815581492324</v>
+        <v>0.07499815581492314</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09100882796610194</v>
+        <v>0.09100882796610271</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09100882796610194</v>
+        <v>0.09100882796610271</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5205753914335942</v>
+        <v>0.520575391433595</v>
       </c>
       <c r="W14" t="n">
         <v>2.2</v>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.4402774003516</v>
+        <v>36.44027740035165</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.4402774003516</v>
+        <v>36.44027740035165</v>
       </c>
     </row>
     <row r="15">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4209874955756275</v>
+        <v>0.420987495575627</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4367556184360717</v>
+        <v>0.4367556184360714</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1422568859883006</v>
+        <v>0.1422568859883015</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1994760214587418</v>
+        <v>0.1994760214587414</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1994760214587418</v>
+        <v>0.1994760214587414</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4367556184360717</v>
+        <v>0.4367556184360714</v>
       </c>
       <c r="W15" t="n">
         <v>4</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>30.57289329052502</v>
+        <v>30.572893290525</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.57289329052502</v>
+        <v>30.572893290525</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -1582,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6149171520084532</v>
+        <v>0.6125718165728418</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3027250780585539</v>
+        <v>0.3031664238939512</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0823577699329931</v>
+        <v>0.0842617595332071</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07315624248695962</v>
+        <v>-0.07550157792257106</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07315624248695962</v>
+        <v>0.07550157792257106</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3850828479915468</v>
+        <v>0.3874281834271582</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.95579935940827</v>
+        <v>27.11997283990108</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.95579935940827</v>
+        <v>27.11997283990108</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -1054,28 +1054,28 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4518940673972829</v>
+        <v>0.4536949757806798</v>
       </c>
       <c r="P7" t="n">
-        <v>0.361204355622729</v>
+        <v>0.3438612530005293</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1869015769799884</v>
+        <v>0.2024437712187911</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07442172207640124</v>
+        <v>-0.07262081369300438</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07442172207640124</v>
+        <v>0.07262081369300438</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5481059326027171</v>
+        <v>0.5463050242193201</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.3674152821902</v>
+        <v>38.24135169535241</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.3674152821902</v>
+        <v>38.24135169535241</v>
       </c>
     </row>
     <row r="8">
@@ -1315,45 +1315,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3720081039411632</v>
+        <v>0.261879640871944</v>
       </c>
       <c r="P10" t="n">
-        <v>0.337583047308818</v>
+        <v>0.3590715274375495</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2904088487500189</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6279918960588368</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.948717948717949</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
       <c r="Z10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
     </row>
     <row r="11">
@@ -1582,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6125718165728418</v>
+        <v>0.6144560676244835</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3031664238939512</v>
+        <v>0.3028120818651876</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0842617595332071</v>
+        <v>0.08273185051032889</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07550157792257106</v>
+        <v>-0.07361732687092937</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07550157792257106</v>
+        <v>0.07361732687092937</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3874281834271582</v>
+        <v>0.3855439323755165</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>27.11997283990108</v>
+        <v>26.98807526628616</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.11997283990108</v>
+        <v>26.98807526628616</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -854,66 +854,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.5888816959792844</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.2203206345234275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.1907976694972882</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.0482308328343739</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4065117704358609</v>
+        <v>0.4061314979160774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.3980054538324055</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1753929965717745</v>
+        <v>0.1958630482515173</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1998843898261963</v>
+        <v>-0.182750198063207</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1998843898261963</v>
+        <v>0.182750198063207</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.5938685020839225</v>
       </c>
       <c r="W5" t="n">
-        <v>4.33</v>
+        <v>2.320471596998928</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
     </row>
     <row r="6">
@@ -966,28 +966,28 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4336241512981688</v>
+        <v>0.4342780967767457</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3839572154861547</v>
+        <v>0.3880867595947963</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1824186332156764</v>
+        <v>0.1776351436284577</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1122160234211113</v>
+        <v>-0.1115620779425343</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1122160234211113</v>
+        <v>0.1115620779425343</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5663758487018312</v>
+        <v>0.5657219032232543</v>
       </c>
       <c r="W6" t="n">
         <v>2.079231692677071</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
     </row>
     <row r="7">
@@ -1030,66 +1030,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4998268098372012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2435053688950468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2566678212677519</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05299631615421085</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4536949757806798</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3438612530005293</v>
+        <v>0.361204355622729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2024437712187911</v>
+        <v>0.1869015769799884</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463050242193201</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
     </row>
     <row r="8">
@@ -1206,25 +1206,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06060606060606055</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1242,30 +1242,30 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6242798692622203</v>
+        <v>0.3757201307377797</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
     </row>
     <row r="10">
@@ -1315,45 +1315,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261879640871944</v>
+        <v>0.3720081039411632</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375495</v>
+        <v>0.337583047308818</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.2904088487500189</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1293019535264836</v>
+        <v>-0.140985483638992</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1293019535264836</v>
+        <v>0.140985483638992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.6279918960588368</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
     </row>
     <row r="11">
@@ -1382,25 +1382,25 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1418,19 +1418,19 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="V11" t="n">
         <v>0.5316170522423029</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1470,25 +1470,25 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
         <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.550173120294781</v>
+        <v>0.5362840799830516</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.2167429884458061</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.2469729315711422</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.06553334838250358</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1506,19 +1506,19 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="V12" t="n">
         <v>0.4599416336294134</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1561,19 +1561,19 @@
         <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1871559633027523</v>
+        <v>0.1782437745740498</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1247706422018349</v>
+        <v>0.1336828309305373</v>
       </c>
       <c r="M13" t="n">
         <v>0.06862745098039214</v>
@@ -1582,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6144560676244835</v>
+        <v>0.6171776308469605</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3028120818651876</v>
+        <v>0.3042189688659127</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08273185051032889</v>
+        <v>0.07860340028712649</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07361732687092937</v>
+        <v>-0.07089576364845229</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07361732687092937</v>
+        <v>0.07089576364845229</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3855439323755165</v>
+        <v>0.3828223691530395</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
     </row>
     <row r="14">
@@ -1734,25 +1734,25 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6045340050377834</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K15" t="n">
-        <v>0.23727959697733</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1581863979848867</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05360934182590227</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1770,19 +1770,19 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="V15" t="n">
         <v>0.4367556184360714</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1315,45 +1315,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3720081039411632</v>
+        <v>0.261879640871944</v>
       </c>
       <c r="P10" t="n">
-        <v>0.337583047308818</v>
+        <v>0.3590715274375495</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2904088487500189</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6279918960588368</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.948717948717949</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
       <c r="Z10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
     </row>
     <row r="11">
@@ -1582,28 +1582,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6171776308469605</v>
+        <v>0.6145717138326878</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3042189688659127</v>
+        <v>0.3027902689485072</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07860340028712649</v>
+        <v>0.08263801721880513</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07089576364845229</v>
+        <v>-0.073501680662725</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07089576364845229</v>
+        <v>0.073501680662725</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3828223691530395</v>
+        <v>0.3854282861673122</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
     </row>
     <row r="14">
@@ -1794,6 +1794,1842 @@
       </c>
       <c r="Z15" t="n">
         <v>30.572893290525</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2462720620015046</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4923339539454937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2613939840530014</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.5076660460545063</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4486050669888325</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4047008090404339</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1466941239707336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.5513949330111676</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3145692862666382</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4692743552439834</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2161563584893785</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.5307256447560167</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3395212219234734</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2837467714942478</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3767320065822789</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.6232679934177211</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.319004676081902</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4197691100698566</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2612262138482416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.5802308899301434</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3468466868897144</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3604566226280601</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2926966904822257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.6395433773719399</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.352099940595717</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4534281625400888</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.194471896864194</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.5465718374599111</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1884751250500326</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2882272408643515</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5232976340856157</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4767023659143843</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4491415382196292</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3649273122968265</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1859311494835444</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.5508584617803708</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5262868708033219</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3324678315859552</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1412452976107228</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.4737131291966781</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.603789322280942</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3291009915269105</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.06710968619214784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.396210677719058</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3410847389107385</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4719125839273521</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1870026771619094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.5280874160726479</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.458906160045076</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4271192785075237</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1139745614474004</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.5410938399549241</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4542204032452292</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3865699443481483</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1592096524066227</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5457795967547708</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5050016708574175</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.3849675921712908</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1100307369712915</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.4949983291425825</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.182866834220039</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2334437671118067</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5836893986681545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.4163106013318455</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2902861035528271</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.33017548571028</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3795384107368928</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6204615892631072</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4444862769605148</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3738661777520266</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1816475452874586</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5555137230394852</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.1556738986571048</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4360717482454501</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4082543530974453</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5639282517545499</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2291534607267637</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.361229768531829</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4096167707414073</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.5903832292585927</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4395550098211475</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4157662140662979</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.1446787761125546</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5604449901788525</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3588073437515735</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3478863234417136</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2933063328067126</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.6411926562484265</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4478269336701768</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3227439799731163</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2294290863567066</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.5521730663298232</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3640386993361091</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3611765105361796</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.2747847901277112</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.6359613006638909</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.3336436547157847</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4931748276163314</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1731815176678841</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.5068251723836686</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3032410599203441</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4777524411613178</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.219006498918338</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5222475588386822</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3204829122770161</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4160459857279659</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.2634711019950181</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5839540142720341</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.87678099904239</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>40.87678099904239</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -590,66 +590,66 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.442947785562681</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3696567110004065</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1873955034369123</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1957487058645927</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1957487058645927</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V2" t="n">
-        <v>0.557052214437319</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W2" t="n">
-        <v>2.616279069767442</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.99365501061233</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.99365501061233</v>
+        <v>33.32974830833433</v>
       </c>
     </row>
     <row r="3">
@@ -678,66 +678,66 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.449677174325864</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2552221800227877</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.330849415970903</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2884875394026187</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>26.64641312385347</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.64641312385347</v>
+        <v>30.02064457154486</v>
       </c>
     </row>
     <row r="4">
@@ -766,66 +766,66 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3421246695652593</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09566372313227506</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>4.5</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.8459538614815</v>
       </c>
     </row>
     <row r="5">
@@ -854,66 +854,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5888816959792844</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2203206345234275</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1907976694972882</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0482308328343739</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4064097840638316</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P5" t="n">
-        <v>0.406249628466087</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1873405874700815</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1824719119154528</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1824719119154528</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5935902159361683</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W5" t="n">
-        <v>2.320471596998928</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>41.55131511553179</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.55131511553179</v>
+        <v>34.70230953497961</v>
       </c>
     </row>
     <row r="6">
@@ -942,66 +942,66 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="J6" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.431972689407671</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3757237719572734</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1923035386350555</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.113867485311609</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113867485311609</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V6" t="n">
-        <v>0.568027310592329</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W6" t="n">
-        <v>2.079231692677071</v>
+        <v>4.2</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.76191174146303</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.76191174146303</v>
+        <v>30.42791295614444</v>
       </c>
     </row>
     <row r="7">
@@ -1030,66 +1030,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4998268098372012</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2435053688950468</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2566678212677519</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05299631615421085</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4352110096174183</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4322347323892172</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325542579933644</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06461580021978297</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06461580021978297</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5647889903825818</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W7" t="n">
-        <v>1.898684210526316</v>
+        <v>2.9</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>39.53522932678072</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z7" t="n">
-        <v>39.53522932678072</v>
+        <v>33.07514882490723</v>
       </c>
     </row>
     <row r="8">
@@ -1139,45 +1139,45 @@
         <v>0.05898156429801493</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4585357639156413</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3362499079698303</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2052143281145281</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08730441080363877</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08730441080363877</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5414642360843587</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W8" t="n">
-        <v>2.079231692677071</v>
+        <v>4.33</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.30030244418116</v>
       </c>
     </row>
     <row r="9">
@@ -1206,66 +1206,66 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3362450625534014</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2874736771444432</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>26.33968822115087</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.33968822115087</v>
+        <v>29.87489690278373</v>
       </c>
     </row>
     <row r="10">
@@ -1294,506 +1294,66 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2433648073553128</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3403588267448442</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>29.13934561298902</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.13934561298902</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>167</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6543046357615894</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1997350993377483</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1459602649006622</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.05402764204942079</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.3128952493758644</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.5361372692209605</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.150967481403175</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.3364021698832122</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.3364021698832122</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.5361372692209605</v>
-      </c>
-      <c r="W11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y11" t="n">
-        <v>37.52960884546724</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>37.52960884546724</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.05898156429801493</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.2957512568246276</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.2512322781440824</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.4530164650312902</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2169405894652016</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.2169405894652016</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.4530164650312902</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
-        <v>31.71115255219031</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>31.71115255219031</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>167</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6880733944954128</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.1782437745740498</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1336828309305373</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.06862745098039214</v>
-      </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.6288124535672187</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.3013673527911105</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.06982019364167102</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.05926094092819412</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.05926094092819412</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.3711875464327813</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>25.98312825029469</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>25.98312825029469</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>167</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.439632042928325</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2554618627826753</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3049060942889996</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05796719450132803</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.5201066341798269</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.4046451603515387</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.07524820546863475</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.08047459125150191</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.08047459125150191</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.5201066341798269</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>36.40746439258788</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>36.40746439258788</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>167</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6538661131292164</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.210690192008303</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1354436948624805</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.05473453749315826</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.3745130758574692</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.4403573203792</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.1851296037633309</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.229667128370897</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.229667128370897</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.4403573203792</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y15" t="n">
-        <v>30.825012426544</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>30.825012426544</v>
+        <v>40.18452838575731</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,20 +567,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -590,55 +590,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.7083825265643447</v>
       </c>
       <c r="K2" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1570247933884298</v>
       </c>
       <c r="L2" t="n">
-        <v>0.126027397260274</v>
+        <v>0.1345926800472255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.06140350877192979</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.3869700516647428</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3071275721315585</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.1690590533739638</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>6</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -646,29 +646,29 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>33.32974830833433</v>
+        <v>31.07796264729053</v>
       </c>
       <c r="Z2" t="n">
-        <v>33.32974830833433</v>
+        <v>31.07796264729053</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -678,55 +678,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.315015479876161</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1700536136842038</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4010800352937268</v>
+        <v>0.2900694571601281</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3457655266429275</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1138508711459084</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1138508711459084</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -734,29 +734,29 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>30.02064457154486</v>
+        <v>25.49155113378612</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.02064457154486</v>
+        <v>25.49155113378612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -766,55 +766,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5968169761273209</v>
+        <v>0.6102722850464338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2122015915119363</v>
+        <v>0.2252195337671363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.16450818118643</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.05716957189607941</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.2443995218260647</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.2882032729522528</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="W4" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -822,538 +822,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>33.8459538614815</v>
+        <v>32.71780436551778</v>
       </c>
       <c r="Z4" t="n">
-        <v>33.8459538614815</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>new york red bulls</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>167</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6018171661844011</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2182108431661685</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1799719906494304</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.05836574785251614</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.4957472790711372</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2448591035222365</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.2593936174066264</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.4957472790711372</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>34.70230953497961</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34.70230953497961</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>167</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5746381507885073</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.225750702095485</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.1996111471160078</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.05468215994531778</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.2064575634094828</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.4346844708020633</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3588579657884538</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2089337687065784</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2089337687065784</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.4346844708020633</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>30.42791295614444</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>30.42791295614444</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>167</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4194683346364347</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2550820953870211</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3254495699765442</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.05954230092161117</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1470755222311179</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3804223516987789</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.4725021260701033</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1470525560935591</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1470525560935591</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.4725021260701033</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>33.07514882490723</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>33.07514882490723</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>167</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.05898156429801493</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.3723226691402557</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1948158673714422</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4328614634883022</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.4328614634883022</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>30.30030244418116</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>167</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3619297617627173</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2719643638388418</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3661058743984409</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.05055780721179959</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3328004140349778</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.426784241468339</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.2404153444966831</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1548198776294972</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1548198776294972</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.426784241468339</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29.87489690278373</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>167</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5180518051805181</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2257225722572257</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2562256225622562</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.05481359579720224</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2032595674696957</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2226757413052</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5740646912251044</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3178390686628482</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.3178390686628482</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.5740646912251044</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40.18452838575731</v>
+        <v>32.71780436551778</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -590,55 +590,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7083825265643447</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1570247933884298</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1345926800472255</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06140350877192979</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3869700516647428</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1690590533739638</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z2" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
     </row>
     <row r="3">
@@ -699,34 +699,34 @@
         <v>0.05796719450132803</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2900694571601281</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3457655266429275</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W3" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
     </row>
     <row r="4">
@@ -790,28 +790,28 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2443995218260647</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2882032729522528</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="W4" t="n">
         <v>5.75</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z4" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -766,25 +766,25 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6102722850464338</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2252195337671363</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.16450818118643</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05716957189607941</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -802,13 +802,13 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="V4" t="n">
         <v>0.5503379081592003</v>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,20 +567,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45471.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -590,55 +590,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7239382239382238</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1505791505791506</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06256410256410261</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.1642468697849789</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.3239081110463583</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.280873440818991</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2427329799458556</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2427329799458556</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="W2" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -646,29 +646,29 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>26.88892750690754</v>
+        <v>35.8291513418064</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.88892750690754</v>
+        <v>35.8291513418064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -678,55 +678,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.439632042928325</v>
+        <v>0.542180339508165</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2344929968372814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.2233266636545537</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.06612992017616293</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3153639087876114</v>
+        <v>0.5495201590542395</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2454734549405155</v>
+        <v>0.2376684911701525</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.2128113497756081</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.007339819546074433</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.007339819546074433</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.5495201590542395</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -734,98 +734,2902 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>30.74138453903112</v>
+        <v>38.46641113379676</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.74138453903112</v>
+        <v>38.46641113379676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1112666056438713</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4213897107776879</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1991490715961327</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1991490715961327</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>32.71405785049085</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>32.71405785049085</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3223762376237624</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2526732673267326</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4249504950495049</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06964331102262133</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2885538219241844</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2798882682614742</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1788846424876088</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1788846424876088</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>30.2090536870039</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>30.2090536870039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5546995377503853</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2357473035439137</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2095531587057011</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06045751633986929</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2696524984710746</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.325890968492706</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1687092294923057</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1687092294923057</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>28.31195731253536</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28.31195731253536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3567060741948635</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2680391357521402</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3752547900529964</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.06594242259641492</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1056844427493848</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4070576290052907</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4872579282453244</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.112003138192328</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.112003138192328</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.4872579282453244</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>34.10805497717271</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>34.10805497717271</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2019387812030422</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.289818025706767</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2912450014084549</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2912450014084549</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>35.57702351631336</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>35.57702351631336</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0761032136620981</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3219959001578103</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2747980824417739</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2747980824417739</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>42.13306203260642</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42.13306203260642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06261588931678785</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3408279566753958</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1450477685978707</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2845940733844515</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2845940733844515</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>35.98869923087134</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>35.98869923087134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06280193236714959</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3177878431154366</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.227368782789396</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.17242935317756</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.17242935317756</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>31.83903618666172</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>31.83903618666172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2465753424657534</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2602739726027397</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.06725146198830423</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.359396816040525</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1767278559818356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>32.47127295843476</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32.47127295843476</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2615384615384615</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06209150326797408</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2337930636330741</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2864780022701863</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1104981648659705</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1104981648659705</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.58102538677178</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>33.58102538677178</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>seattle sounders</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05776014109347427</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2292248832373925</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3239337003004357</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2667663851991455</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2667663851991455</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>31.27889915235203</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>31.27889915235203</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5152153240048907</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2548227143051216</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2299619616899878</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.06062079672635434</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1096026689551528</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6508783927570068</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2395189382878405</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3960556784518852</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.3960556784518852</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6508783927570068</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>45.56148749299047</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>45.56148749299047</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2910801910715639</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3187300557940925</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3901897531343437</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.6098102468656563</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>42.68671728059594</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42.68671728059594</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.11859282169494</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2891652246559143</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5922419536491457</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.4077580463508543</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>28.5430632445598</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28.5430632445598</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1300286073032101</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2959344201278853</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5740369725689046</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.4259630274310954</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>29.81741192017668</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>29.81741192017668</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3021367112651189</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3118254466460983</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3860378420887828</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.6139621579112171</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>42.9773510537852</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42.9773510537852</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1137181767269389</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.347281232600631</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5390005906724301</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.4609994093275699</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>32.26995865292989</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>32.26995865292989</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3377610251048948</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.2629343508692568</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3993046240258485</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.6006953759741516</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>42.04867631819061</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>42.04867631819061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2102050138660907</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4460485145786615</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3437464715552478</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.5539514854213385</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.7766039794937</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>38.7766039794937</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2039683792691152</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2195417309854106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5764898897454743</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4235101102545257</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>29.6457077178168</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29.6457077178168</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.165730761755151</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3643945447399982</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.4698746935048509</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.530125306495149</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>37.10877145466043</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>37.10877145466043</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1804427270102636</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3316364199201491</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4879208530695873</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.5120791469304127</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>35.84554028512889</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>35.84554028512889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>167</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6038755619308649</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2312401542027946</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1648842838663405</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.05475815766188674</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1555948135238605</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.460780950832072</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.3836242356440675</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.539219049167928</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>37.74533344175496</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>37.74533344175496</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2464572160737567</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4197114665611633</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.33383131736508</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.5802885334388367</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>40.62019734071857</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40.62019734071857</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1912627821864503</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5240250406309664</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2847121771825833</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.4759749593690336</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.31824715583235</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>33.31824715583235</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.2068043869608158</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.242857704879984</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="O29" t="n">
+        <v>0.1339057857071087</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3791454438510249</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.4869487704418664</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5130512295581335</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>35.91358606906935</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>35.91358606906935</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.6970129084589971</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1478901277561028</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1550969637849001</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.3029870915410029</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.2090964078702</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>21.2090964078702</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38.52365357114402</v>
+      <c r="O31" t="n">
+        <v>0.1032657155921802</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3638537276127817</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5328805567950382</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.4671194432049618</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>32.69836102434733</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>32.69836102434733</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2186122003093852</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.4397178547663033</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3416699449243116</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.5602821452336968</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>39.21975016635878</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>39.21975016635878</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.1753271859574902</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3795316382043792</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4451411758381306</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5548588241618694</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>38.84011769133085</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38.84011769133085</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45480.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.3635616090733832</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3758222204173031</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.2606161705093137</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.6241777795826969</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>43.69244457078879</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>43.69244457078879</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45480.0625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2170576406952672</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.215256431144031</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.5676859281607018</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.4323140718392982</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>30.26198502875087</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>30.26198502875087</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45480.10416666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1862907893755237</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3809950351800475</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4327141754444288</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5672858245555712</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.71000771888998</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>39.71000771888998</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1172133659454251</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3491915500948359</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.533595083959739</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.466404916040261</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>32.64834412281827</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>32.64834412281827</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.2519730838065383</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.1717278774908062</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.5762990387026554</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.4237009612973446</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>29.65906729081412</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>29.65906729081412</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45481.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.1053620075900685</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.584721392714579</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3099165996953525</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.415278607285421</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.06950250997947</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>29.06950250997947</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4173085263408691</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4131424591513406</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1695490145077903</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.5826914736591309</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.78840315613916</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>40.78840315613916</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.1942455617650128</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.3935222465769074</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.4122321916580799</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5877678083419201</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>41.14374658393441</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>41.14374658393441</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45481.83333333334</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.2753350332114494</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.3677670757637634</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3568978910247871</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.6322329242362366</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>44.25630469653656</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>44.25630469653656</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,15 +429,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_match</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
@@ -561,6 +556,21 @@
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
         </is>
       </c>
     </row>
@@ -651,6 +661,19 @@
       <c r="Z2" t="n">
         <v>38.99365501061233</v>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -739,6 +762,19 @@
       <c r="Z3" t="n">
         <v>26.64641312385347</v>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -827,6 +863,19 @@
       <c r="Z4" t="n">
         <v>39.3548125111726</v>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -915,6 +964,19 @@
       <c r="Z5" t="n">
         <v>41.55131511553179</v>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1003,6 +1065,19 @@
       <c r="Z6" t="n">
         <v>39.76191174146303</v>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1091,6 +1166,19 @@
       <c r="Z7" t="n">
         <v>39.53522932678072</v>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1179,6 +1267,19 @@
       <c r="Z8" t="n">
         <v>37.90249652590511</v>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1267,6 +1368,19 @@
       <c r="Z9" t="n">
         <v>26.33968822115087</v>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1355,6 +1469,19 @@
       <c r="Z10" t="n">
         <v>29.13934561298902</v>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1443,6 +1570,19 @@
       <c r="Z11" t="n">
         <v>37.52960884546724</v>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1531,6 +1671,19 @@
       <c r="Z12" t="n">
         <v>31.71115255219031</v>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1619,6 +1772,19 @@
       <c r="Z13" t="n">
         <v>25.98312825029469</v>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1707,6 +1873,19 @@
       <c r="Z14" t="n">
         <v>36.40746439258788</v>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1794,6 +1973,19 @@
       </c>
       <c r="Z15" t="n">
         <v>30.825012426544</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -600,66 +600,66 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.442947785562681</v>
+        <v>0.3128952493758644</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3696567110004065</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1873955034369123</v>
+        <v>0.150967481403175</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="V2" t="n">
-        <v>0.557052214437319</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="W2" t="n">
-        <v>2.616279069767442</v>
+        <v>4.75</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC2" t="n">
@@ -678,20 +678,20 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,55 +701,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.449677174325864</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2552221800227877</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.330849415970903</v>
+        <v>0.2957512568246276</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2884875394026187</v>
+        <v>0.2512322781440824</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AC3" t="n">
@@ -779,7 +779,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -802,85 +802,85 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3421246695652593</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09566372313227506</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -888,12 +888,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -903,85 +903,85 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5888816959792844</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2203206345234275</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1907976694972882</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0482308328343739</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4064097840638316</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P5" t="n">
-        <v>0.406249628466087</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1873405874700815</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1824719119154528</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1824719119154528</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5935902159361683</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W5" t="n">
-        <v>2.320471596998928</v>
+        <v>3</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>41.55131511553179</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.55131511553179</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -989,12 +989,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1004,70 +1004,70 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.431972689407671</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3757237719572734</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1923035386350555</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.113867485311609</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113867485311609</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V6" t="n">
-        <v>0.568027310592329</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W6" t="n">
-        <v>2.079231692677071</v>
+        <v>4.5</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,98 +1105,98 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4998268098372012</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2435053688950468</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2566678212677519</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05299631615421085</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4352110096174183</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4322347323892172</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325542579933644</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06461580021978297</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06461580021978297</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5647889903825818</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W7" t="n">
-        <v>1.898684210526316</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>39.53522932678072</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z7" t="n">
-        <v>39.53522932678072</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1206,98 +1206,98 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4585357639156413</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3362499079698303</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2052143281145281</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08730441080363877</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08730441080363877</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5414642360843587</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W8" t="n">
-        <v>2.079231692677071</v>
+        <v>4.2</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1310,82 +1310,82 @@
         <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3362450625534014</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2874736771444432</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>26.33968822115087</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.33968822115087</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1408,98 +1408,98 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2433648073553128</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3403588267448442</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>29.13934561298902</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.13934561298902</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1509,75 +1509,75 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>2.63</v>
       </c>
       <c r="H11" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.150967481403175</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W11" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC11" t="n">
@@ -1587,20 +1587,20 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1610,70 +1610,70 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>31.71115255219031</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z12" t="n">
-        <v>31.71115255219031</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1711,66 +1711,66 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6288124535672187</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3013673527911105</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06982019364167102</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.05926094092819412</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05926094092819412</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3711875464327813</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>25.98312825029469</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.98312825029469</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1833,45 +1833,45 @@
         <v>0.05796719450132803</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4046451603515387</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07524820546863475</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W14" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.40746439258788</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.40746439258788</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1913,66 +1913,66 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K15" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3745130758574692</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4403573203792</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1851296037633309</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4403573203792</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>30.825012426544</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.825012426544</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -433,6 +433,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -575,6 +575,16 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>result</t>
         </is>
       </c>
@@ -676,7 +686,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -777,7 +797,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -878,7 +908,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -979,7 +1019,17 @@
           <t>4</t>
         </is>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1080,7 +1130,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1181,7 +1241,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1282,7 +1352,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1383,7 +1463,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1484,7 +1574,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1585,7 +1685,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1686,7 +1796,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1787,7 +1907,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1888,7 +2018,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1989,7 +2129,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,10 +429,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_match</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>date</t>
@@ -570,27 +575,42 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
           <t>result</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>acerte</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -600,66 +620,66 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.442947785562681</v>
+        <v>0.3128952493758644</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3696567110004065</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1873955034369123</v>
+        <v>0.150967481403175</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1957487058645927</v>
+        <v>0.3364021698832122</v>
       </c>
       <c r="V2" t="n">
-        <v>0.557052214437319</v>
+        <v>0.5361372692209605</v>
       </c>
       <c r="W2" t="n">
-        <v>2.616279069767442</v>
+        <v>4.75</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.99365501061233</v>
+        <v>37.52960884546724</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -668,30 +688,43 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.0625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -701,55 +734,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.449677174325864</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2552221800227877</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.330849415970903</v>
+        <v>0.2957512568246276</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2884875394026187</v>
+        <v>0.2512322781440824</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.2169405894652016</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4530164650312902</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -757,29 +790,42 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.64641312385347</v>
+        <v>31.71115255219031</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
         <v>2</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -787,12 +833,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -802,85 +848,98 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3421246695652593</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09566372313227506</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.3548125111726</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>2</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -888,12 +947,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -903,85 +962,98 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5888816959792844</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2203206345234275</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1907976694972882</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0482308328343739</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4064097840638316</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P5" t="n">
-        <v>0.406249628466087</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1873405874700815</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1824719119154528</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1824719119154528</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5935902159361683</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W5" t="n">
-        <v>2.320471596998928</v>
+        <v>3</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>41.55131511553179</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.55131511553179</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -989,12 +1061,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1004,70 +1076,70 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.431972689407671</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3757237719572734</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1923035386350555</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.113867485311609</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113867485311609</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V6" t="n">
-        <v>0.568027310592329</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W6" t="n">
-        <v>2.079231692677071</v>
+        <v>4.5</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1075,14 +1147,27 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="n">
-        <v>1</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1090,12 +1175,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,98 +1190,111 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4998268098372012</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2435053688950468</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2566678212677519</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05299631615421085</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4352110096174183</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4322347323892172</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325542579933644</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06461580021978297</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06461580021978297</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5647889903825818</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W7" t="n">
-        <v>1.898684210526316</v>
+        <v>1.57</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>39.53522932678072</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z7" t="n">
-        <v>39.53522932678072</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>2</v>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1206,98 +1304,111 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4585357639156413</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3362499079698303</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2052143281145281</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08730441080363877</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08730441080363877</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5414642360843587</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W8" t="n">
-        <v>2.079231692677071</v>
+        <v>4.2</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>2</v>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1310,82 +1421,95 @@
         <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3362450625534014</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2874736771444432</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>26.33968822115087</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.33968822115087</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1393,12 +1517,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1408,98 +1532,111 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2433648073553128</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3403588267448442</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>29.13934561298902</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.13934561298902</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1509,98 +1646,111 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>2.63</v>
       </c>
       <c r="H11" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.150967481403175</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W11" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>1</v>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1610,70 +1760,70 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="H12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.54584017471928</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>31.71115255219031</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z12" t="n">
-        <v>31.71115255219031</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -1681,8 +1831,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AC12" t="n">
-        <v>2</v>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1711,66 +1874,66 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6288124535672187</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3013673527911105</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06982019364167102</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.05926094092819412</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05926094092819412</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3711875464327813</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>6.25</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>25.98312825029469</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.98312825029469</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1782,8 +1945,21 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AC13" t="n">
-        <v>1</v>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1833,45 +2009,45 @@
         <v>0.05796719450132803</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4046451603515387</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07524820546863475</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08047459125150191</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W14" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.40746439258788</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.40746439258788</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -1883,8 +2059,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AC14" t="n">
-        <v>1</v>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1913,79 +2102,92 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K15" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.2068043869608158</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.242857704879984</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="W15" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.3745130758574692</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.4403573203792</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.1851296037633309</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.229667128370897</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.229667128370897</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.4403573203792</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
-      </c>
-      <c r="Y15" t="n">
-        <v>30.825012426544</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>30.825012426544</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC15" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,147 +465,132 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>goals_home</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>goals_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>competition</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -614,109 +599,96 @@
       <c r="F2" t="n">
         <v>1671</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.75</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6543046357615894</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1997350993377483</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.06685633001422464</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5361372692209605</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.150967481403175</v>
+        <v>0.1585296251078339</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0.3603816340318831</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.4810887408602829</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2344220741936162</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5361372692209605</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>0.2344220741936162</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.4810887408602829</v>
       </c>
       <c r="Y2" t="n">
-        <v>37.52960884546724</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>37.52960884546724</v>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
+        <v>3.8</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>19.05443704301414</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>19.05443704301414</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -725,109 +697,96 @@
       <c r="F3" t="n">
         <v>1671</v>
       </c>
-      <c r="G3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.33</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.54584017471928</v>
-      </c>
       <c r="K3" t="n">
-        <v>0.2180839497146315</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2512322781440824</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.600582874090608</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.2593121032056201</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.1401050227037719</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.06125703139397876</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4530164650312902</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
-        </is>
+        <v>0.06125703139397876</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.600582874090608</v>
       </c>
       <c r="Y3" t="n">
-        <v>31.71115255219031</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>31.71115255219031</v>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
+        <v>1.75</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>25.0291437045304</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25.0291437045304</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -836,109 +795,96 @@
       <c r="F4" t="n">
         <v>1671</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6849315068493151</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.189041095890411</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.126027397260274</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3071275721315585</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.1011077281055308</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0.2294654363350203</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.6694268355594488</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.3074312971291102</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4761392615476333</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.3074312971291102</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.6694268355594488</v>
       </c>
       <c r="Y4" t="n">
-        <v>33.32974830833433</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>33.32974830833433</v>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
-        <v>1</v>
+        <v>2.6</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>28.47134177797244</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>28.47134177797244</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -947,109 +893,96 @@
       <c r="F5" t="n">
         <v>1671</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.7</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4295665634674923</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2554179566563468</v>
+        <v>2.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.315015479876161</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="N5" t="n">
+        <v>0.4366812227074235</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.06511627906976747</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.1700536136842038</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.4010800352937268</v>
-      </c>
       <c r="Q5" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3174985794909022</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0.2631537432633123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1138508711459084</v>
+        <v>0.4193476772457856</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1138508711459084</v>
+        <v>-0.01733354546163796</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4288663510220694</v>
+        <v>-2</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.01733354546163796</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.5806523227542144</v>
       </c>
       <c r="Y5" t="n">
-        <v>30.02064457154486</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>30.02064457154486</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>24.03261613771072</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.03261613771072</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1058,109 +991,96 @@
       <c r="F6" t="n">
         <v>1671</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>4.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5968169761273209</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.2122015915119363</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4835136265925929</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.5113280515068027</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0.2294201897299064</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.2592517587632908</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2713120350806566</v>
+        <v>-0.1202508958616183</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4835136265925929</v>
+        <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.1202508958616183</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4886719484931973</v>
       </c>
       <c r="Y6" t="n">
-        <v>33.8459538614815</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>33.8459538614815</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.571428571428571</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>19.43359742465987</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>19.43359742465987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1169,109 +1089,96 @@
       <c r="F7" t="n">
         <v>1671</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.33</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>5.25</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6018171661844011</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2182108431661685</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2448591035222365</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2593936174066264</v>
+        <v>0.1461905207264745</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0.2006163205883511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.6531931586851744</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.3052602892623336</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4957472790711372</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.3052602892623336</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.6531931586851744</v>
       </c>
       <c r="Y7" t="n">
-        <v>34.70230953497961</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>34.70230953497961</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
+        <v>2.7</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>27.65965793425872</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>27.65965793425872</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1280,109 +1187,96 @@
       <c r="F8" t="n">
         <v>1671</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.2</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>4.75</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5746381507885073</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0.225750702095485</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2064575634094828</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4346844708020633</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3588579657884538</v>
+        <v>0.2770150961145689</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0.3381121763154563</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.3848727275699747</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.1774653201625673</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4346844708020633</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.1774653201625673</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.3848727275699747</v>
       </c>
       <c r="Y8" t="n">
-        <v>30.42791295614444</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>30.42791295614444</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
+        <v>4.5</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA8" t="n">
+        <v>14.24363637849873</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>14.24363637849873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1391,104 +1285,91 @@
       <c r="F9" t="n">
         <v>1671</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.7</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4194683346364347</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2550820953870211</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3254495699765442</v>
+        <v>0.4983388704318937</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05954230092161117</v>
+        <v>0.2491694352159468</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0.2524916943521595</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1470755222311179</v>
+        <v>0.05614035087719293</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3804223516987789</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.1822897025916111</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>0.4115121503485941</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1470525560935591</v>
+        <v>0.4061981470597947</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1470525560935591</v>
+        <v>0.1623427151326473</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4725021260701033</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.1623427151326473</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4115121503485941</v>
       </c>
       <c r="Y9" t="n">
-        <v>33.07514882490723</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>33.07514882490723</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>2</v>
+        <v>3.8</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA9" t="n">
+        <v>15.57560751742971</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>15.57560751742971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1502,109 +1383,96 @@
       <c r="F10" t="n">
         <v>1671</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I10" t="n">
-        <v>4.33</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.54584017471928</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2360758755660886</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.5228187919463088</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="N10" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06261588931678785</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.3723226691402557</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.1948158673714422</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.2562809039497406</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0.343238534749213</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2147775137736708</v>
+        <v>0.4004805613010465</v>
       </c>
       <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.1709503599587646</v>
+      </c>
+      <c r="V10" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.4328614634883022</v>
-      </c>
       <c r="W10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.1709503599587646</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.4004805613010465</v>
       </c>
       <c r="Y10" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
+        <v>4.1</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="n">
+        <v>15.02402806505232</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>15.02402806505232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1613,109 +1481,96 @@
       <c r="F11" t="n">
         <v>1671</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.5</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3619297617627173</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2719643638388418</v>
+        <v>5.75</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3661058743984409</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05055780721179959</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3328004140349778</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="P11" t="n">
-        <v>0.426784241468339</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2404153444966831</v>
+        <v>0.6842793279755205</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0.2583691465609907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1548198776294972</v>
+        <v>0.05735152546348866</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1548198776294972</v>
+        <v>0.05700660070279318</v>
       </c>
       <c r="V11" t="n">
-        <v>0.426784241468339</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.05700660070279318</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6842793279755205</v>
       </c>
       <c r="Y11" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE11" t="n">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="n">
+        <v>29.21396639877602</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>29.21396639877602</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1724,109 +1579,96 @@
       <c r="F12" t="n">
         <v>1671</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.2</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5180518051805181</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2257225722572257</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.5082095387021109</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.2410737555381809</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0.2507167057597081</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2032595674696957</v>
+        <v>0.06361746361746357</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2226757413052</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.6556394530658596</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0.1749962637134689</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.1693642832206717</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.1474299143637486</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5740646912251044</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.1474299143637486</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.6556394530658596</v>
       </c>
       <c r="Y12" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA12" t="n">
+        <v>27.78197265329298</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>27.78197265329298</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1835,109 +1677,96 @@
       <c r="F13" t="n">
         <v>1671</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6.25</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7239382239382238</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1505791505791506</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.3646038628301144</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06256410256410261</v>
+        <v>0.2562081198265668</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.379188017343319</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.05488565488565467</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3841275358129648</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.280873440818991</v>
+        <v>0.2392310608947727</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0.3227469299461854</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.4380220091590419</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.05883399181572296</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3841275358129648</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.05883399181572296</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4380220091590419</v>
       </c>
       <c r="Y13" t="n">
-        <v>26.88892750690754</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>26.88892750690754</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
+        <v>2.5</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA13" t="n">
+        <v>16.9011004579521</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>16.9011004579521</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1946,109 +1775,96 @@
       <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.7</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="J14" t="n">
-        <v>0.439632042928325</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2554618627826753</v>
+        <v>5.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.5835764902042518</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.236348478532722</v>
       </c>
       <c r="N14" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05776014109347427</v>
+      </c>
+      <c r="P14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.3153639087876114</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.2454734549405155</v>
-      </c>
       <c r="Q14" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.1104422495607779</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0.3755765015243285</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.5139812489148935</v>
       </c>
       <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3339062176518672</v>
+      </c>
+      <c r="V14" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1342565419828735</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.4391626362718731</v>
-      </c>
       <c r="W14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
+        <v>0.3339062176518672</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.5139812489148935</v>
       </c>
       <c r="Y14" t="n">
-        <v>30.74138453903112</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>30.74138453903112</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE14" t="n">
-        <v>1</v>
+        <v>5.25</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>20.69906244574468</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20.69906244574468</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2057,91 +1873,2714 @@
       <c r="F15" t="n">
         <v>1671</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5221774193548387</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2540322580645161</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2237903225806452</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06392106392106389</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3511615882647987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2676215560887525</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3812168556464487</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1574265330658036</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1574265330658036</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3812168556464487</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>14.06084278232244</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.06084278232244</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.09506172839506166</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2986195152733523</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2383247333879759</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4630557513386717</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2804176453634744</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.2804176453634744</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4630557513386717</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>18.15278756693358</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18.15278756693358</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4343286698684485</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2806431405303822</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2850281896011694</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.09638278388278376</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1836536507829496</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3266724605478561</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4896738886691943</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2046456990680249</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.2046456990680249</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.4896738886691943</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.48369443345971</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>19.48369443345971</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3521126760563379</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3661971830985915</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.09230769230769242</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1553928911572484</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3170210187805046</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.527586090062247</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1613889069636555</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1613889069636555</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.527586090062247</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>21.37930450311235</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>21.37930450311235</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>1.57</v>
       </c>
-      <c r="H15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6038755619308649</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.2312401542027946</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1648842838663405</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.05475815766188674</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5811960717106538</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2433274220228604</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1754765062664858</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.09591703413359465</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.303257120057161</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4890266717119621</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2077162082308768</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2456992496891018</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2456992496891018</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.4890266717119621</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>19.45133358559811</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>19.45133358559811</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P20" t="n">
         <v>2</v>
       </c>
-      <c r="O15" t="n">
-        <v>0.2068043869608158</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.242857704879984</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="Q20" t="n">
+        <v>0.09331688082328962</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2367728396021617</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6699102795745489</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.3555631543730443</v>
+      </c>
+      <c r="V20" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="W15" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y15" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AE15" t="n">
-        <v>1</v>
-      </c>
+      <c r="W20" t="n">
+        <v>0.3555631543730443</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6699102795745489</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>28.49551397872744</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>28.49551397872744</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3927384873205019</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2829980502106852</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3242634624688129</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.01242002960588179</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.01242002960588179</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.6072615126794981</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.532520325203252</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>25.3630756339749</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25.3630756339749</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.332706312209954</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2913184969117958</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3759751908782502</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.06162806567674561</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.06162806567674561</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.3759751908782502</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>13.79875954391251</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.79875954391251</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2399367110755938</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4607248436047824</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2993384453196239</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1802304857326706</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1802304857326706</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.4607248436047824</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>18.03624218023912</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>18.03624218023912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5639990501068629</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2436475896461648</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1923533602469722</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.09447693307342431</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3015832438805195</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3189591270404248</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3794576290790557</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1871042688320835</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.1871042688320835</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3794576290790557</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>13.97288145395278</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13.97288145395278</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5280322219860701</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2609987840102575</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2109689940036723</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.09469585001230074</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3384884511422985</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3447227435307231</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3167888053269785</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.08372395952046557</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.08372395952046557</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3447227435307231</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>12.23613717653615</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.23613717653615</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.09539969834087492</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.1165722926010396</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2643952151519466</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6190324922470138</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2679137314896989</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2679137314896989</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6190324922470138</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>25.95162461235069</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>25.95162461235069</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.09506172839506166</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3553081675807302</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3166251980902031</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.3280666343290666</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2083896903674095</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2083896903674095</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.6446918324192698</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.093023255813954</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>27.23459162096349</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>27.23459162096349</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.09539969834087492</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1577702476860585</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3783477455351054</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4638820067788361</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1127632460215212</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1127632460215212</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4638820067788361</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>18.19410033894181</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18.19410033894181</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2198767360298228</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3762799186433601</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.4038433453268171</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="n">
+        <v>0.5961566546731829</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>24.80783273365915</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>24.80783273365915</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.6517450933228697</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2462058230352516</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1020490836418788</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>0.3482549066771303</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>12.41274533385652</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.41274533385652</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2340252767550797</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.4533277151477706</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.3126470080971495</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>0.5466722848522294</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>22.33361424261147</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>22.33361424261147</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.4879230264703818</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.2880531314804122</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.224023842049206</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>0.5120769735296182</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>20.60384867648091</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>20.60384867648091</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.3248000313835386</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.4291690095653991</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2460309590510623</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>0.5708309904346009</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>23.54154952173005</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>23.54154952173005</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45479.89583333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.2992059919222956</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.2498873569671831</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.4509066511105214</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="n">
+        <v>0.5490933488894787</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>22.45466744447393</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>22.45466744447393</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3212718705413699</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.390346703945361</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2883814255132691</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="n">
+        <v>0.609653296054639</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>25.48266480273195</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>25.48266480273195</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.225668000183265</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.4145494309309021</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.3597825688858328</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="n">
+        <v>0.5854505690690979</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>24.27252845345489</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>24.27252845345489</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.1112410798441106</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.266165823801843</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.6225930963540462</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="n">
+        <v>0.3774069036459538</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>13.87034518229769</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>13.87034518229769</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2392316636670534</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.3479242645368</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.4128440717961466</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="n">
+        <v>0.5871559282038534</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>24.35779641019267</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>24.35779641019267</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.2027394013853659</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.3507673632106973</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.4464932354039368</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>0.5535067645960632</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>22.67533822980316</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>22.67533822980316</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1832356348957332</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.2403955547468579</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.5763688103574088</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
+        <v>0.4236311896425912</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>16.18155948212956</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>16.18155948212956</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.4443843597147053</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.3332789578993695</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.2223366823859252</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="n">
+        <v>0.5556156402852948</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>22.78078201426474</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>22.78078201426474</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3771408747564578</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.2843206683708714</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.3385384568726707</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="n">
+        <v>0.6228591252435423</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>26.14295626217711</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>26.14295626217711</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>indy eleven</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sacramento republic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.1866426214177104</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.333167626535192</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.4801897520470976</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
+        <v>0.5198102479529023</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>20.99051239764512</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>20.99051239764512</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>new mexico</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>167</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -265,7 +265,7 @@
     <t>seattle sounders</t>
   </si>
   <si>
-    <t xml:space="preserve">fc dallas </t>
+    <t xml:space="preserve">fc dallas  </t>
   </si>
 </sst>
 </file>
@@ -275,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,13 +285,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -352,16 +346,16 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -821,7 +815,7 @@
         <v>32</v>
       </c>
       <c r="B2" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>33</v>
@@ -919,7 +913,7 @@
         <v>40</v>
       </c>
       <c r="B3" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>41</v>
@@ -1017,7 +1011,7 @@
         <v>44</v>
       </c>
       <c r="B4" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>45</v>
@@ -1115,7 +1109,7 @@
         <v>48</v>
       </c>
       <c r="B5" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>49</v>
@@ -1213,7 +1207,7 @@
         <v>51</v>
       </c>
       <c r="B6" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>52</v>
@@ -1311,7 +1305,7 @@
         <v>55</v>
       </c>
       <c r="B7" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>56</v>
@@ -1409,7 +1403,7 @@
         <v>59</v>
       </c>
       <c r="B8" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>60</v>
@@ -1507,7 +1501,7 @@
         <v>62</v>
       </c>
       <c r="B9" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>63</v>
@@ -1605,7 +1599,7 @@
         <v>65</v>
       </c>
       <c r="B10" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>66</v>
@@ -1703,7 +1697,7 @@
         <v>68</v>
       </c>
       <c r="B11" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>69</v>
@@ -1801,7 +1795,7 @@
         <v>71</v>
       </c>
       <c r="B12" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>72</v>
@@ -1899,7 +1893,7 @@
         <v>74</v>
       </c>
       <c r="B13" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>75</v>
@@ -1997,7 +1991,7 @@
         <v>78</v>
       </c>
       <c r="B14" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>79</v>
@@ -2090,12 +2084,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
       <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B15" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>82</v>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -265,7 +265,7 @@
     <t>seattle sounders</t>
   </si>
   <si>
-    <t xml:space="preserve">fc dallas  </t>
+    <t xml:space="preserve">fc dallas   </t>
   </si>
 </sst>
 </file>
@@ -712,7 +712,7 @@
     <col min="32" max="32" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
@@ -908,7 +908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>40</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>48</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>51</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>55</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>62</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>68</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>71</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>74</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="89">
   <si>
     <t>id_match</t>
   </si>
@@ -257,6 +257,21 @@
   </si>
   <si>
     <t>vancouver whitecaps</t>
+  </si>
+  <si>
+    <t>aefejfasdfn</t>
+  </si>
+  <si>
+    <t>equipo1</t>
+  </si>
+  <si>
+    <t>equipo2</t>
+  </si>
+  <si>
+    <t>dsfivdfdiskv</t>
+  </si>
+  <si>
+    <t>AOKSDGA</t>
   </si>
   <si>
     <t>8K42rT3c</t>
@@ -332,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -357,6 +372,9 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -675,41 +693,41 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF15"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -2084,12 +2102,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
       <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B15" s="5">
-        <v>25568.875520833335</v>
+        <v>25568.375520833335</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>82</v>
@@ -2107,67 +2125,67 @@
         <v>1.57</v>
       </c>
       <c r="H15" s="8">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="I15" s="8">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="J15" s="8">
-        <v>0.6038755619308649</v>
+        <v>3</v>
       </c>
       <c r="K15" s="8">
-        <v>0.2312401542027946</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L15" s="8">
-        <v>0.1648842838663405</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M15" s="8">
-        <v>0.05475815766188674</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N15" s="7">
         <v>2</v>
       </c>
       <c r="O15" s="8">
-        <v>0.2068043869608158</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P15" s="8">
-        <v>0.242857704879984</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q15" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R15" s="7">
         <v>1</v>
       </c>
       <c r="S15" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T15" s="7">
         <v>2</v>
       </c>
       <c r="U15" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V15" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W15" s="8">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X15" s="6" t="s">
         <v>47</v>
       </c>
       <c r="Y15" s="8">
-        <v>38.52365357114402</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z15" s="8">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB15" s="6" t="s">
-        <v>54</v>
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
       </c>
       <c r="AC15" s="6" t="s">
         <v>38</v>
@@ -2179,6 +2197,300 @@
         <v>1</v>
       </c>
       <c r="AF15" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+      <c r="A16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="5">
+        <v>25568.375520833335</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="7">
+        <v>167</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8">
+        <v>2</v>
+      </c>
+      <c r="J16" s="8">
+        <v>3</v>
+      </c>
+      <c r="K16" s="8">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M16" s="8">
+        <v>0.05796719450132803</v>
+      </c>
+      <c r="N16" s="7">
+        <v>2</v>
+      </c>
+      <c r="O16" s="8">
+        <v>0.3153639087876114</v>
+      </c>
+      <c r="P16" s="8">
+        <v>0.2454734549405155</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="R16" s="7">
+        <v>1</v>
+      </c>
+      <c r="S16" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="T16" s="7">
+        <v>2</v>
+      </c>
+      <c r="U16" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="V16" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W16" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="X16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y16" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="Z16" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA16" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE16" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+      <c r="A17" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="5">
+        <v>25568.375520833335</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="7">
+        <v>167</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
+      </c>
+      <c r="I17" s="8">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0.05796719450132803</v>
+      </c>
+      <c r="N17" s="7">
+        <v>2</v>
+      </c>
+      <c r="O17" s="8">
+        <v>0.3153639087876114</v>
+      </c>
+      <c r="P17" s="8">
+        <v>0.2454734549405155</v>
+      </c>
+      <c r="Q17" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="R17" s="7">
+        <v>1</v>
+      </c>
+      <c r="S17" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="T17" s="7">
+        <v>2</v>
+      </c>
+      <c r="U17" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="V17" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W17" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="X17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y17" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="Z17" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA17" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE17" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
+      <c r="A18" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="5">
+        <v>25568.875520833335</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="7">
+        <v>167</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G18" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H18" s="8">
+        <v>4.1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0.6038755619308649</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0.2312401542027946</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.1648842838663405</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0.05475815766188674</v>
+      </c>
+      <c r="N18" s="7">
+        <v>2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0.2068043869608158</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.242857704879984</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="T18" s="7">
+        <v>2</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="V18" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="W18" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="X18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="Z18" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="AA18" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="7">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
   <si>
     <t>id_match</t>
   </si>
@@ -124,12 +124,6 @@
     <t>dif_prob_mod_bm &gt; -0.05</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
     <t>los angeles galaxy</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>z7pPU9Zc</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
     <t>new england revolution</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>ln2oxMH4</t>
   </si>
   <si>
@@ -190,9 +178,6 @@
     <t>toronto fc</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>WYwYSm4A</t>
   </si>
   <si>
@@ -247,9 +232,6 @@
     <t>san jose earthquakes</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>Ma0gz0nH</t>
   </si>
   <si>
@@ -272,6 +254,24 @@
   </si>
   <si>
     <t>AOKSDGA</t>
+  </si>
+  <si>
+    <t>AAAAAAAAA</t>
+  </si>
+  <si>
+    <t>jasdngdsagn</t>
+  </si>
+  <si>
+    <t>ejiq</t>
+  </si>
+  <si>
+    <t>BBBBBBBBBB</t>
+  </si>
+  <si>
+    <t>neoqirg</t>
+  </si>
+  <si>
+    <t>sjdnfsaj</t>
   </si>
   <si>
     <t>8K42rT3c</t>
@@ -290,7 +290,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +301,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -347,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -376,6 +382,12 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -390,6 +402,9 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,41 +708,41 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF18"/>
+  <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="17" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="17" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
@@ -809,10 +824,10 @@
       <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
@@ -907,17 +922,17 @@
       <c r="Z2" s="8">
         <v>37.52960884546724</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AA2" s="9">
+        <v>4</v>
+      </c>
+      <c r="AB2" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AD2" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AC2" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD2" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE2" s="7">
         <v>1</v>
@@ -928,16 +943,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="7">
         <v>167</v>
@@ -1005,17 +1020,17 @@
       <c r="Z3" s="8">
         <v>31.71115255219031</v>
       </c>
-      <c r="AA3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AA3" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD3" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AC3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD3" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE3" s="7">
         <v>2</v>
@@ -1026,16 +1041,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" s="7">
         <v>167</v>
@@ -1095,7 +1110,7 @@
         <v>1.38</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y4" s="8">
         <v>33.32974830833433</v>
@@ -1103,17 +1118,17 @@
       <c r="Z4" s="8">
         <v>33.32974830833433</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AA4" s="9">
+        <v>4</v>
+      </c>
+      <c r="AB4" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AB4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC4" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="AD4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE4" s="7">
         <v>1</v>
@@ -1124,16 +1139,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B5" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" s="7">
         <v>167</v>
@@ -1193,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="X5" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y5" s="8">
         <v>30.02064457154486</v>
@@ -1201,17 +1216,17 @@
       <c r="Z5" s="8">
         <v>30.02064457154486</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AA5" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD5" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AB5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC5" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE5" s="7">
         <v>2</v>
@@ -1222,16 +1237,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B6" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E6" s="7">
         <v>167</v>
@@ -1291,7 +1306,7 @@
         <v>4.5</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y6" s="8">
         <v>33.8459538614815</v>
@@ -1299,17 +1314,17 @@
       <c r="Z6" s="8">
         <v>33.8459538614815</v>
       </c>
-      <c r="AA6" s="6" t="s">
+      <c r="AA6" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD6" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AB6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD6" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE6" s="7">
         <v>2</v>
@@ -1320,16 +1335,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B7" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E7" s="7">
         <v>167</v>
@@ -1389,7 +1404,7 @@
         <v>1.57</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y7" s="8">
         <v>34.70230953497961</v>
@@ -1397,17 +1412,17 @@
       <c r="Z7" s="8">
         <v>34.70230953497961</v>
       </c>
-      <c r="AA7" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB7" s="6" t="s">
-        <v>43</v>
+      <c r="AA7" s="9">
+        <v>3</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE7" s="7">
         <v>1</v>
@@ -1418,16 +1433,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B8" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E8" s="7">
         <v>167</v>
@@ -1487,7 +1502,7 @@
         <v>4.2</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y8" s="8">
         <v>30.42791295614444</v>
@@ -1495,17 +1510,17 @@
       <c r="Z8" s="8">
         <v>30.42791295614444</v>
       </c>
-      <c r="AA8" s="6" t="s">
+      <c r="AA8" s="9">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AB8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC8" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="AD8" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE8" s="7">
         <v>1</v>
@@ -1516,16 +1531,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B9" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E9" s="7">
         <v>167</v>
@@ -1585,7 +1600,7 @@
         <v>2.9</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y9" s="8">
         <v>33.07514882490723</v>
@@ -1593,17 +1608,17 @@
       <c r="Z9" s="8">
         <v>33.07514882490723</v>
       </c>
-      <c r="AA9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB9" s="6" t="s">
-        <v>54</v>
+      <c r="AA9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>2</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD9" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE9" s="7">
         <v>2</v>
@@ -1614,16 +1629,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B10" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E10" s="7">
         <v>167</v>
@@ -1683,7 +1698,7 @@
         <v>4.33</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y10" s="8">
         <v>30.30030244418116</v>
@@ -1691,17 +1706,17 @@
       <c r="Z10" s="8">
         <v>30.30030244418116</v>
       </c>
-      <c r="AA10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB10" s="6" t="s">
+      <c r="AA10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD10" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AC10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE10" s="7">
         <v>2</v>
@@ -1712,16 +1727,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B11" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E11" s="7">
         <v>167</v>
@@ -1781,7 +1796,7 @@
         <v>3.5</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y11" s="8">
         <v>29.87489690278373</v>
@@ -1789,17 +1804,17 @@
       <c r="Z11" s="8">
         <v>29.87489690278373</v>
       </c>
-      <c r="AA11" s="6" t="s">
+      <c r="AA11" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD11" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AB11" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC11" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD11" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE11" s="7">
         <v>1</v>
@@ -1810,16 +1825,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B12" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E12" s="7">
         <v>167</v>
@@ -1879,7 +1894,7 @@
         <v>3.7</v>
       </c>
       <c r="X12" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y12" s="8">
         <v>40.18452838575731</v>
@@ -1887,17 +1902,17 @@
       <c r="Z12" s="8">
         <v>40.18452838575731</v>
       </c>
-      <c r="AA12" s="6" t="s">
+      <c r="AA12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD12" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD12" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="AE12" s="7">
         <v>0</v>
@@ -1908,16 +1923,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B13" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E13" s="7">
         <v>167</v>
@@ -1977,7 +1992,7 @@
         <v>6.25</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y13" s="8">
         <v>26.88892750690754</v>
@@ -1985,17 +2000,17 @@
       <c r="Z13" s="8">
         <v>26.88892750690754</v>
       </c>
-      <c r="AA13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="AB13" s="6" t="s">
-        <v>54</v>
+      <c r="AA13" s="9">
+        <v>6</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>2</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD13" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE13" s="7">
         <v>1</v>
@@ -2006,16 +2021,16 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B14" s="5">
         <v>25568.875520833335</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E14" s="7">
         <v>167</v>
@@ -2075,7 +2090,7 @@
         <v>3.1</v>
       </c>
       <c r="X14" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y14" s="8">
         <v>30.74138453903112</v>
@@ -2083,17 +2098,17 @@
       <c r="Z14" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB14" s="6" t="s">
-        <v>43</v>
+      <c r="AA14" s="9">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD14" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE14" s="7">
         <v>1</v>
@@ -2102,18 +2117,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B15" s="5">
         <v>25568.375520833335</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E15" s="7">
         <v>167</v>
@@ -2173,7 +2188,7 @@
         <v>3.1</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y15" s="8">
         <v>30.74138453903112</v>
@@ -2181,17 +2196,17 @@
       <c r="Z15" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA15" s="9">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="9">
+      <c r="AA15" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="10">
         <v>0</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE15" s="7">
         <v>1</v>
@@ -2200,18 +2215,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B16" s="5">
         <v>25568.375520833335</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E16" s="7">
         <v>167</v>
@@ -2271,7 +2286,7 @@
         <v>3.1</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y16" s="8">
         <v>30.74138453903112</v>
@@ -2279,17 +2294,17 @@
       <c r="Z16" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA16" s="9">
-        <v>2</v>
-      </c>
-      <c r="AB16" s="9">
+      <c r="AA16" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="10">
         <v>0</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD16" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE16" s="7">
         <v>1</v>
@@ -2298,18 +2313,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="17.25">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B17" s="5">
         <v>25568.375520833335</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E17" s="7">
         <v>167</v>
@@ -2369,7 +2384,7 @@
         <v>3.1</v>
       </c>
       <c r="X17" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Y17" s="8">
         <v>30.74138453903112</v>
@@ -2377,17 +2392,17 @@
       <c r="Z17" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA17" s="9">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="9">
+      <c r="AA17" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="10">
         <v>0</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AD17" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AE17" s="7">
         <v>1</v>
@@ -2396,18 +2411,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="20.25">
-      <c r="A18" s="1" t="s">
-        <v>86</v>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
+      <c r="A18" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="B18" s="5">
-        <v>25568.875520833335</v>
+        <v>25568.375520833335</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E18" s="7">
         <v>167</v>
@@ -2419,78 +2434,274 @@
         <v>1.57</v>
       </c>
       <c r="H18" s="8">
+        <v>1</v>
+      </c>
+      <c r="I18" s="8">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>3</v>
+      </c>
+      <c r="K18" s="8">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M18" s="8">
+        <v>0.05796719450132803</v>
+      </c>
+      <c r="N18" s="7">
+        <v>2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>0.3153639087876114</v>
+      </c>
+      <c r="P18" s="8">
+        <v>0.2454734549405155</v>
+      </c>
+      <c r="Q18" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1</v>
+      </c>
+      <c r="S18" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="T18" s="7">
+        <v>2</v>
+      </c>
+      <c r="U18" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="V18" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W18" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="X18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y18" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="Z18" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA18" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE18" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
+      <c r="A19" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="5">
+        <v>25568.375520833335</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="7">
+        <v>167</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G19" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H19" s="8">
+        <v>1</v>
+      </c>
+      <c r="I19" s="8">
+        <v>2</v>
+      </c>
+      <c r="J19" s="8">
+        <v>3</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0.05796719450132803</v>
+      </c>
+      <c r="N19" s="7">
+        <v>2</v>
+      </c>
+      <c r="O19" s="8">
+        <v>0.3153639087876114</v>
+      </c>
+      <c r="P19" s="8">
+        <v>0.2454734549405155</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="R19" s="7">
+        <v>1</v>
+      </c>
+      <c r="S19" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="T19" s="7">
+        <v>2</v>
+      </c>
+      <c r="U19" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="V19" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W19" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y19" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="Z19" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA19" s="10">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE19" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25">
+      <c r="A20" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="5">
+        <v>25568.875520833335</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="7">
+        <v>167</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G20" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H20" s="8">
         <v>4.1</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I20" s="8">
         <v>5.75</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J20" s="8">
         <v>0.6038755619308649</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K20" s="8">
         <v>0.2312401542027946</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L20" s="8">
         <v>0.1648842838663405</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M20" s="8">
         <v>0.05475815766188674</v>
       </c>
-      <c r="N18" s="7">
-        <v>2</v>
-      </c>
-      <c r="O18" s="8">
+      <c r="N20" s="7">
+        <v>2</v>
+      </c>
+      <c r="O20" s="8">
         <v>0.2068043869608158</v>
       </c>
-      <c r="P18" s="8">
+      <c r="P20" s="8">
         <v>0.242857704879984</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q20" s="8">
         <v>0.5503379081592003</v>
       </c>
-      <c r="R18" s="7">
-        <v>1</v>
-      </c>
-      <c r="S18" s="8">
+      <c r="R20" s="7">
+        <v>1</v>
+      </c>
+      <c r="S20" s="8">
         <v>0.3854536242928598</v>
       </c>
-      <c r="T18" s="7">
-        <v>2</v>
-      </c>
-      <c r="U18" s="8">
+      <c r="T20" s="7">
+        <v>2</v>
+      </c>
+      <c r="U20" s="8">
         <v>0.3854536242928598</v>
       </c>
-      <c r="V18" s="8">
+      <c r="V20" s="8">
         <v>0.5503379081592003</v>
       </c>
-      <c r="W18" s="8">
+      <c r="W20" s="8">
         <v>5.75</v>
       </c>
-      <c r="X18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y18" s="8">
+      <c r="X20" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y20" s="8">
         <v>38.52365357114402</v>
       </c>
-      <c r="Z18" s="8">
+      <c r="Z20" s="8">
         <v>38.52365357114402</v>
       </c>
-      <c r="AA18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="AD18" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE18" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="7">
+      <c r="AA20" s="9">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE20" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="7">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="90">
   <si>
     <t>id_match</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>sjdnfsaj</t>
+  </si>
+  <si>
+    <t>ZZZZZZZZ</t>
   </si>
   <si>
     <t>8K42rT3c</t>
@@ -353,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,11 +382,11 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -402,9 +405,6 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +708,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -737,8 +737,8 @@
     <col min="24" max="24" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="25" max="25" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="26" max="26" style="16" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="17" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="17" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="29" max="29" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="30" max="30" style="14" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="31" max="31" style="15" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -2196,10 +2196,10 @@
       <c r="Z15" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA15" s="10">
-        <v>2</v>
-      </c>
-      <c r="AB15" s="10">
+      <c r="AA15" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB15" s="7">
         <v>0</v>
       </c>
       <c r="AC15" s="6" t="s">
@@ -2294,10 +2294,10 @@
       <c r="Z16" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA16" s="10">
-        <v>2</v>
-      </c>
-      <c r="AB16" s="10">
+      <c r="AA16" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB16" s="7">
         <v>0</v>
       </c>
       <c r="AC16" s="6" t="s">
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="20.25">
       <c r="A17" s="1" t="s">
         <v>79</v>
       </c>
@@ -2392,10 +2392,10 @@
       <c r="Z17" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA17" s="10">
-        <v>2</v>
-      </c>
-      <c r="AB17" s="10">
+      <c r="AA17" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="7">
         <v>0</v>
       </c>
       <c r="AC17" s="6" t="s">
@@ -2411,8 +2411,8 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="17.25">
-      <c r="A18" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B18" s="5">
@@ -2490,10 +2490,10 @@
       <c r="Z18" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA18" s="10">
-        <v>2</v>
-      </c>
-      <c r="AB18" s="10">
+      <c r="AA18" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="7">
         <v>0</v>
       </c>
       <c r="AC18" s="6" t="s">
@@ -2509,8 +2509,8 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="17.25">
-      <c r="A19" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="10" t="s">
         <v>83</v>
       </c>
       <c r="B19" s="5">
@@ -2588,10 +2588,10 @@
       <c r="Z19" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA19" s="10">
-        <v>2</v>
-      </c>
-      <c r="AB19" s="10">
+      <c r="AA19" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB19" s="7">
         <v>0</v>
       </c>
       <c r="AC19" s="6" t="s">
@@ -2607,18 +2607,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="20.25">
-      <c r="A20" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
+      <c r="A20" s="11" t="s">
         <v>86</v>
       </c>
       <c r="B20" s="5">
-        <v>25568.875520833335</v>
+        <v>25568.375520833335</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E20" s="7">
         <v>167</v>
@@ -2630,67 +2630,67 @@
         <v>1.57</v>
       </c>
       <c r="H20" s="8">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="I20" s="8">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="J20" s="8">
-        <v>0.6038755619308649</v>
+        <v>3</v>
       </c>
       <c r="K20" s="8">
-        <v>0.2312401542027946</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L20" s="8">
-        <v>0.1648842838663405</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M20" s="8">
-        <v>0.05475815766188674</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N20" s="7">
         <v>2</v>
       </c>
       <c r="O20" s="8">
-        <v>0.2068043869608158</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P20" s="8">
-        <v>0.242857704879984</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q20" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R20" s="7">
         <v>1</v>
       </c>
       <c r="S20" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T20" s="7">
         <v>2</v>
       </c>
       <c r="U20" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V20" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W20" s="8">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X20" s="6" t="s">
         <v>44</v>
       </c>
       <c r="Y20" s="8">
-        <v>38.52365357114402</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z20" s="8">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA20" s="9">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="9">
-        <v>2</v>
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA20" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>0</v>
       </c>
       <c r="AC20" s="6" t="s">
         <v>36</v>
@@ -2702,6 +2702,104 @@
         <v>1</v>
       </c>
       <c r="AF20" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25">
+      <c r="A21" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="5">
+        <v>25568.875520833335</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="7">
+        <v>167</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G21" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H21" s="8">
+        <v>4.1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0.6038755619308649</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0.2312401542027946</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0.1648842838663405</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0.05475815766188674</v>
+      </c>
+      <c r="N21" s="7">
+        <v>2</v>
+      </c>
+      <c r="O21" s="8">
+        <v>0.2068043869608158</v>
+      </c>
+      <c r="P21" s="8">
+        <v>0.242857704879984</v>
+      </c>
+      <c r="Q21" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="R21" s="7">
+        <v>1</v>
+      </c>
+      <c r="S21" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="T21" s="7">
+        <v>2</v>
+      </c>
+      <c r="U21" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="V21" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="W21" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="X21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y21" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="Z21" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="AA21" s="9">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC21" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE21" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="7">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>id_match</t>
   </si>
@@ -274,7 +274,13 @@
     <t>sjdnfsaj</t>
   </si>
   <si>
+    <t>XXXXXXXXXX</t>
+  </si>
+  <si>
     <t>ZZZZZZZZ</t>
+  </si>
+  <si>
+    <t>nueva_fila</t>
   </si>
   <si>
     <t>8K42rT3c</t>
@@ -382,13 +388,13 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -708,7 +714,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
@@ -922,10 +928,10 @@
       <c r="Z2" s="8">
         <v>37.52960884546724</v>
       </c>
-      <c r="AA2" s="9">
+      <c r="AA2" s="7">
         <v>4</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AB2" s="7">
         <v>1</v>
       </c>
       <c r="AC2" s="6" t="s">
@@ -1020,10 +1026,10 @@
       <c r="Z3" s="8">
         <v>31.71115255219031</v>
       </c>
-      <c r="AA3" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="9">
+      <c r="AA3" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="7">
         <v>1</v>
       </c>
       <c r="AC3" s="6" t="s">
@@ -1118,10 +1124,10 @@
       <c r="Z4" s="8">
         <v>33.32974830833433</v>
       </c>
-      <c r="AA4" s="9">
+      <c r="AA4" s="7">
         <v>4</v>
       </c>
-      <c r="AB4" s="9">
+      <c r="AB4" s="7">
         <v>0</v>
       </c>
       <c r="AC4" s="6" t="s">
@@ -1216,10 +1222,10 @@
       <c r="Z5" s="8">
         <v>30.02064457154486</v>
       </c>
-      <c r="AA5" s="9">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="9">
+      <c r="AA5" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="7">
         <v>4</v>
       </c>
       <c r="AC5" s="6" t="s">
@@ -1314,10 +1320,10 @@
       <c r="Z6" s="8">
         <v>33.8459538614815</v>
       </c>
-      <c r="AA6" s="9">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="9">
+      <c r="AA6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="7">
         <v>2</v>
       </c>
       <c r="AC6" s="6" t="s">
@@ -1412,10 +1418,10 @@
       <c r="Z7" s="8">
         <v>34.70230953497961</v>
       </c>
-      <c r="AA7" s="9">
+      <c r="AA7" s="7">
         <v>3</v>
       </c>
-      <c r="AB7" s="9">
+      <c r="AB7" s="7">
         <v>0</v>
       </c>
       <c r="AC7" s="6" t="s">
@@ -1510,10 +1516,10 @@
       <c r="Z8" s="8">
         <v>30.42791295614444</v>
       </c>
-      <c r="AA8" s="9">
+      <c r="AA8" s="7">
         <v>4</v>
       </c>
-      <c r="AB8" s="9">
+      <c r="AB8" s="7">
         <v>2</v>
       </c>
       <c r="AC8" s="6" t="s">
@@ -1608,10 +1614,10 @@
       <c r="Z9" s="8">
         <v>33.07514882490723</v>
       </c>
-      <c r="AA9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="9">
+      <c r="AA9" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7">
         <v>2</v>
       </c>
       <c r="AC9" s="6" t="s">
@@ -1706,10 +1712,10 @@
       <c r="Z10" s="8">
         <v>30.30030244418116</v>
       </c>
-      <c r="AA10" s="9">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="9">
+      <c r="AA10" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="7">
         <v>1</v>
       </c>
       <c r="AC10" s="6" t="s">
@@ -1804,10 +1810,10 @@
       <c r="Z11" s="8">
         <v>29.87489690278373</v>
       </c>
-      <c r="AA11" s="9">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="9">
+      <c r="AA11" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="7">
         <v>0</v>
       </c>
       <c r="AC11" s="6" t="s">
@@ -1902,10 +1908,10 @@
       <c r="Z12" s="8">
         <v>40.18452838575731</v>
       </c>
-      <c r="AA12" s="9">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="9">
+      <c r="AA12" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="7">
         <v>1</v>
       </c>
       <c r="AC12" s="6" t="s">
@@ -2000,10 +2006,10 @@
       <c r="Z13" s="8">
         <v>26.88892750690754</v>
       </c>
-      <c r="AA13" s="9">
+      <c r="AA13" s="7">
         <v>6</v>
       </c>
-      <c r="AB13" s="9">
+      <c r="AB13" s="7">
         <v>2</v>
       </c>
       <c r="AC13" s="6" t="s">
@@ -2098,10 +2104,10 @@
       <c r="Z14" s="8">
         <v>30.74138453903112</v>
       </c>
-      <c r="AA14" s="9">
-        <v>2</v>
-      </c>
-      <c r="AB14" s="9">
+      <c r="AA14" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB14" s="7">
         <v>0</v>
       </c>
       <c r="AC14" s="6" t="s">
@@ -2412,7 +2418,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="B18" s="5">
@@ -2510,7 +2516,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>83</v>
       </c>
       <c r="B19" s="5">
@@ -2608,7 +2614,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="17.25">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>86</v>
       </c>
       <c r="B20" s="5">
@@ -2705,18 +2711,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="20.25">
-      <c r="A21" s="1" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="11" t="s">
         <v>87</v>
       </c>
       <c r="B21" s="5">
-        <v>25568.875520833335</v>
+        <v>25568.375520833335</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E21" s="7">
         <v>167</v>
@@ -2728,67 +2734,67 @@
         <v>1.57</v>
       </c>
       <c r="H21" s="8">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="I21" s="8">
-        <v>5.75</v>
+        <v>2</v>
       </c>
       <c r="J21" s="8">
-        <v>0.6038755619308649</v>
+        <v>3</v>
       </c>
       <c r="K21" s="8">
-        <v>0.2312401542027946</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L21" s="8">
-        <v>0.1648842838663405</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M21" s="8">
-        <v>0.05475815766188674</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N21" s="7">
         <v>2</v>
       </c>
       <c r="O21" s="8">
-        <v>0.2068043869608158</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P21" s="8">
-        <v>0.242857704879984</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q21" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R21" s="7">
         <v>1</v>
       </c>
       <c r="S21" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T21" s="7">
         <v>2</v>
       </c>
       <c r="U21" s="8">
-        <v>0.3854536242928598</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V21" s="8">
-        <v>0.5503379081592003</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W21" s="8">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="X21" s="6" t="s">
         <v>44</v>
       </c>
       <c r="Y21" s="8">
-        <v>38.52365357114402</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z21" s="8">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA21" s="9">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="9">
-        <v>2</v>
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA21" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="7">
+        <v>0</v>
       </c>
       <c r="AC21" s="6" t="s">
         <v>36</v>
@@ -2800,6 +2806,202 @@
         <v>1</v>
       </c>
       <c r="AF21" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="17.25">
+      <c r="A22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="5">
+        <v>25568.375520833335</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="7">
+        <v>167</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8">
+        <v>2</v>
+      </c>
+      <c r="J22" s="8">
+        <v>3</v>
+      </c>
+      <c r="K22" s="8">
+        <v>0.2554618627826753</v>
+      </c>
+      <c r="L22" s="8">
+        <v>0.3049060942889996</v>
+      </c>
+      <c r="M22" s="8">
+        <v>0.05796719450132803</v>
+      </c>
+      <c r="N22" s="7">
+        <v>2</v>
+      </c>
+      <c r="O22" s="8">
+        <v>0.3153639087876114</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0.2454734549405155</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="R22" s="7">
+        <v>1</v>
+      </c>
+      <c r="S22" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="T22" s="7">
+        <v>2</v>
+      </c>
+      <c r="U22" s="8">
+        <v>0.1342565419828735</v>
+      </c>
+      <c r="V22" s="8">
+        <v>0.4391626362718731</v>
+      </c>
+      <c r="W22" s="8">
+        <v>3.1</v>
+      </c>
+      <c r="X22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y22" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="Z22" s="8">
+        <v>30.74138453903112</v>
+      </c>
+      <c r="AA22" s="7">
+        <v>2</v>
+      </c>
+      <c r="AB22" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE22" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="20.25">
+      <c r="A23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="5">
+        <v>25568.875520833335</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="7">
+        <v>167</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1671</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1.57</v>
+      </c>
+      <c r="H23" s="8">
+        <v>4.1</v>
+      </c>
+      <c r="I23" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0.6038755619308649</v>
+      </c>
+      <c r="K23" s="8">
+        <v>0.2312401542027946</v>
+      </c>
+      <c r="L23" s="8">
+        <v>0.1648842838663405</v>
+      </c>
+      <c r="M23" s="8">
+        <v>0.05475815766188674</v>
+      </c>
+      <c r="N23" s="7">
+        <v>2</v>
+      </c>
+      <c r="O23" s="8">
+        <v>0.2068043869608158</v>
+      </c>
+      <c r="P23" s="8">
+        <v>0.242857704879984</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="R23" s="7">
+        <v>1</v>
+      </c>
+      <c r="S23" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="T23" s="7">
+        <v>2</v>
+      </c>
+      <c r="U23" s="8">
+        <v>0.3854536242928598</v>
+      </c>
+      <c r="V23" s="8">
+        <v>0.5503379081592003</v>
+      </c>
+      <c r="W23" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="X23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y23" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="Z23" s="8">
+        <v>38.52365357114402</v>
+      </c>
+      <c r="AA23" s="7">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="7">
+        <v>2</v>
+      </c>
+      <c r="AC23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE23" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="7">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,6 +2225,130 @@
         <v>1</v>
       </c>
       <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.85416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.510925955038516</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2397421789026883</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2493318660587958</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.06952501050861692</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.1600414027325715</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3548428194046342</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4851157778627943</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2357839118039984</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2357839118039984</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.4851157778627943</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.425578889313971</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.425578889313971</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>MLS</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH16"/>
+  <dimension ref="A1:AF16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -585,20 +585,10 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>country</t>
+          <t>result</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>competition</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>acerte</t>
         </is>
@@ -703,20 +693,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,20 +799,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AE3" t="n">
         <v>2</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AF3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -935,20 +905,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
+      <c r="AE4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1051,20 +1011,10 @@
           <t>4</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AE5" t="n">
         <v>2</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AF5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1167,20 +1117,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
+      <c r="AE6" t="n">
         <v>2</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AF6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1283,20 +1223,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1399,20 +1329,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1515,20 +1435,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AF9" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1631,20 +1541,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AE10" t="n">
         <v>2</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AF10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1747,20 +1647,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1863,20 +1753,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AE12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AF12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1979,20 +1859,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2095,20 +1965,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2211,20 +2071,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2335,20 +2185,10 @@
           <t>2</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>MLS</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH16" t="n">
+      <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF16"/>
+  <dimension ref="A1:AF18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,20 +597,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -620,77 +620,77 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.150967481403175</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W2" t="n">
-        <v>4.75</v>
+        <v>6.25</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>37.52960884546724</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z2" t="n">
-        <v>37.52960884546724</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="n">
@@ -703,20 +703,20 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -726,103 +726,103 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="H3" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.54584017471928</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W3" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>31.71115255219031</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z3" t="n">
-        <v>31.71115255219031</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -832,55 +832,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>7.5</v>
+        <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K4" t="n">
-        <v>0.189041095890411</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.126027397260274</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3071275721315585</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>5.75</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -888,47 +888,47 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>33.32974830833433</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z4" t="n">
-        <v>33.32974830833433</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -938,103 +938,111 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.510925955038516</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.2397421789026883</v>
       </c>
       <c r="L5" t="n">
-        <v>0.315015479876161</v>
+        <v>0.2493318660587958</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.06952501050861692</v>
       </c>
       <c r="N5" t="n">
         <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1700536136842038</v>
+        <v>0.1600414027325715</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4010800352937268</v>
+        <v>0.3548428194046342</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1138508711459084</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1138508711459084</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>30.02064457154486</v>
+        <v>2.425578889313971</v>
       </c>
       <c r="Z5" t="n">
-        <v>30.02064457154486</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+        <v>2.425578889313971</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1044,103 +1052,111 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5968169761273209</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2122015915119363</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M6" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.2825583427564414</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.1038652110113047</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="W6" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>33.8459538614815</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.8459538614815</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+        <v>3.067882231161269</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1150,103 +1166,111 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="H7" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.0706619627663416</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2448591035222365</v>
+        <v>0.2511722045198468</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2593936174066264</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1060698871132638</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4957472790711372</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="W7" t="n">
-        <v>1.57</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>34.70230953497961</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="Z7" t="n">
-        <v>34.70230953497961</v>
-      </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+        <v>3.390829163569058</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1256,81 +1280,89 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>4.75</v>
+        <v>2.15</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5746381507885073</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="K8" t="n">
-        <v>0.225750702095485</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1996111471160078</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05468215994531778</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2064575634094828</v>
+        <v>0.1964722326397506</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4346844708020633</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3588579657884538</v>
+        <v>0.3909365342429724</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2089337687065784</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4346844708020633</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>30.42791295614444</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="Z8" t="n">
-        <v>30.42791295614444</v>
-      </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+        <v>2.062956165586385</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1339,20 +1371,20 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1362,72 +1394,80 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4194683346364347</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2550820953870211</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3254495699765442</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05954230092161117</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1470755222311179</v>
+        <v>0.4489400143010975</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3804223516987789</v>
+        <v>0.3040135939367658</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.2470463917621368</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1470525560935591</v>
+        <v>-0.1826389330673235</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1470525560935591</v>
+        <v>0.1826389330673235</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4725021260701033</v>
+        <v>0.5510599856989025</v>
       </c>
       <c r="W9" t="n">
-        <v>2.9</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>33.07514882490723</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="Z9" t="n">
-        <v>33.07514882490723</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+        <v>2.755299928494512</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1436,7 +1476,7 @@
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>1</v>
@@ -1445,20 +1485,20 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1468,69 +1508,77 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.73</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="J10" t="n">
-        <v>0.54584017471928</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3723226691402557</v>
+        <v>0.1285853626482153</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1948158673714422</v>
+        <v>0.2521890736131565</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2147775137736708</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2147775137736708</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="W10" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>30.30030244418116</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="Z10" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+        <v>3.096127818693141</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>0</t>
@@ -1551,20 +1599,20 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1574,69 +1622,77 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3619297617627173</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2719643638388418</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3661058743984409</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05055780721179959</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3328004140349778</v>
+        <v>0.2868517150384613</v>
       </c>
       <c r="P11" t="n">
-        <v>0.426784241468339</v>
+        <v>0.3390256513186948</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2404153444966831</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1548198776294972</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1548198776294972</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="V11" t="n">
-        <v>0.426784241468339</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>29.87489690278373</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="Z11" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+        <v>1.870613168214219</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>1</t>
@@ -1657,20 +1713,20 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1680,69 +1736,77 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
         <v>3.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2032595674696957</v>
+        <v>0.07899396123747764</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2226757413052</v>
+        <v>0.2628148092904548</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3178390686628482</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="W12" t="n">
         <v>3.7</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>40.18452838575731</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="Z12" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+        <v>3.290956147360338</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1750,33 +1814,33 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1786,77 +1850,85 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7239382239382238</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1505791505791506</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06256410256410261</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.2519603951479352</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.3332635017594314</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.280873440818991</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="W13" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.88892750690754</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.88892750690754</v>
-      </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+        <v>2.073880515463168</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="n">
@@ -1869,20 +1941,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1892,72 +1964,80 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>2.15</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="J14" t="n">
-        <v>0.439632042928325</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3153639087876114</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2454734549405155</v>
+        <v>0.2779189034356739</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.07194914847262197</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>30.74138453903112</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="Z14" t="n">
-        <v>30.74138453903112</v>
-      </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+        <v>3.25065974045852</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -1969,26 +2049,26 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1998,69 +2078,77 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6038755619308649</v>
+        <v>0.5082095387021109</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2312401542027946</v>
+        <v>0.2410737555381809</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1648842838663405</v>
+        <v>0.2507167057597081</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05475815766188674</v>
+        <v>0.06361746361746357</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2068043869608158</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="P15" t="n">
-        <v>0.242857704879984</v>
+        <v>0.1566867042163429</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.5503379081592003</v>
+        <v>0.1544764098783133</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3854536242928598</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3854536242928598</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5503379081592003</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="W15" t="n">
-        <v>5.75</v>
+        <v>1.85</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>38.52365357114402</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="Z15" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+        <v>3.44418442952672</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>3</t>
@@ -2075,26 +2163,26 @@
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45471.85416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2104,55 +2192,55 @@
         <v>1671</v>
       </c>
       <c r="G16" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.510925955038516</v>
+        <v>0.3646038628301144</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2397421789026883</v>
+        <v>0.2562081198265668</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2493318660587958</v>
+        <v>0.379188017343319</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06952501050861692</v>
+        <v>0.05488565488565467</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1600414027325715</v>
+        <v>0.2111363599934632</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3548428194046342</v>
+        <v>0.2528128853098374</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="W16" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2160,10 +2248,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>2.425578889313971</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.425578889313971</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2177,18 +2265,246 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05776014109347427</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1101391702825879</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.3923018476563575</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4975589820610545</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3174839507980283</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.3174839507980283</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4975589820610545</v>
+      </c>
+      <c r="W17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.487794910305273</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.487794910305273</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5221774193548387</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2540322580645161</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2237903225806452</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.06392106392106389</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3419055891466642</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2647645273290432</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3933298835242927</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1695395609436476</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1695395609436476</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3933298835242927</v>
+      </c>
+      <c r="W18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.966649417621464</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.966649417621464</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF18"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,20 +597,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -620,72 +620,80 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7239382239382238</v>
+        <v>0.510925955038516</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1505791505791506</v>
+        <v>0.2397421789026883</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.2493318660587958</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06256410256410261</v>
+        <v>0.06952501050861692</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.1600414027325715</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.3548428194046342</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.280873440818991</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="W2" t="n">
-        <v>6.25</v>
+        <v>3.75</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>26.88892750690754</v>
+        <v>2.425578889313971</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.88892750690754</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>2.425578889313971</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -703,20 +711,20 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -726,69 +734,77 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.439632042928325</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3153639087876114</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2454734549405155</v>
+        <v>0.2825583427564414</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.1038652110113047</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>1.75</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>30.74138453903112</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.74138453903112</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>3.067882231161269</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2</t>
@@ -796,33 +812,33 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -832,72 +848,80 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6038755619308649</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2312401542027946</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1648842838663405</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05475815766188674</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2068043869608158</v>
+        <v>0.0706619627663416</v>
       </c>
       <c r="P4" t="n">
-        <v>0.242857704879984</v>
+        <v>0.2511722045198468</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5503379081592003</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3854536242928598</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3854536242928598</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5503379081592003</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="W4" t="n">
-        <v>5.75</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>38.52365357114402</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="Z4" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+        <v>3.390829163569058</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -915,20 +939,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45471.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -938,52 +962,52 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>2.15</v>
       </c>
       <c r="J5" t="n">
-        <v>0.510925955038516</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2397421789026883</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2493318660587958</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06952501050861692</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1600414027325715</v>
+        <v>0.1964722326397506</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3548428194046342</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.3909365342429724</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="W5" t="n">
         <v>3.75</v>
@@ -994,10 +1018,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>2.425578889313971</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.425578889313971</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1011,16 +1035,16 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1029,7 +1053,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1037,12 +1061,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1052,66 +1076,66 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.4489400143010975</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2825583427564414</v>
+        <v>0.3040135939367658</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1038652110113047</v>
+        <v>0.2470463917621368</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07425060353562463</v>
+        <v>-0.1826389330673235</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.07425060353562463</v>
+        <v>0.1826389330673235</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.5510599856989025</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>3.067882231161269</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.067882231161269</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1130,11 +1154,11 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
@@ -1143,20 +1167,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1166,22 +1190,22 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
-        <v>0.369093490164267</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="K7" t="n">
         <v>0.2689109714053944</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M7" t="n">
         <v>0.06248653307476837</v>
@@ -1190,31 +1214,31 @@
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0706619627663416</v>
+        <v>0.1285853626482153</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2511722045198468</v>
+        <v>0.2521890736131565</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.316170294283473</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.316170294283473</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1222,10 +1246,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>3.390829163569058</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.390829163569058</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1239,38 +1263,38 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1280,55 +1304,55 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3129548762736535</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2503639010189229</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4366812227074235</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06511627906976747</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1964722326397506</v>
+        <v>0.2868517150384613</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4125912331172771</v>
+        <v>0.3390256513186948</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3909365342429724</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1622273320983542</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1622273320983542</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4125912331172771</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="W8" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1336,10 +1360,10 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>2.062956165586385</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.062956165586385</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1358,11 +1382,11 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1371,20 +1395,20 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1394,66 +1418,66 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.631578947368421</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4489400143010975</v>
+        <v>0.07899396123747764</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3040135939367658</v>
+        <v>0.2628148092904548</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2470463917621368</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1826389330673235</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1826389330673235</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5510599856989025</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="W9" t="n">
-        <v>2.571428571428571</v>
+        <v>3.7</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>2.755299928494512</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.755299928494512</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1467,16 +1491,16 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>1</v>
@@ -1485,7 +1509,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -1493,12 +1517,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1508,55 +1532,55 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2689109714053944</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L10" t="n">
-        <v>0.369093490164267</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06248653307476837</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1285853626482153</v>
+        <v>0.2519603951479352</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2521890736131565</v>
+        <v>0.3332635017594314</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="W10" t="n">
-        <v>2.55</v>
+        <v>4.2</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1564,10 +1588,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>3.096127818693141</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.096127818693141</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1581,38 +1605,38 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1622,55 +1646,55 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2074074074074074</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2868517150384613</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3390256513186948</v>
+        <v>0.2779189034356739</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.07194914847262197</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1667152262354365</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1667152262354365</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1678,10 +1702,10 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>1.870613168214219</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.870613168214219</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1695,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1707,26 +1731,26 @@
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1736,55 +1760,55 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4953320415712524</v>
+        <v>0.5082095387021109</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2489695261581821</v>
+        <v>0.2410737555381809</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2556984322705654</v>
+        <v>0.2507167057597081</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05698837443119609</v>
+        <v>0.06361746361746357</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07899396123747764</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2628148092904548</v>
+        <v>0.1566867042163429</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.1544764098783133</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="W12" t="n">
-        <v>3.7</v>
+        <v>1.85</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1792,10 +1816,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>3.290956147360338</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.290956147360338</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1809,7 +1833,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1818,7 +1842,7 @@
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>1</v>
@@ -1827,20 +1851,20 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1850,55 +1874,55 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.3646038628301144</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2562081198265668</v>
       </c>
       <c r="L13" t="n">
-        <v>0.225296442687747</v>
+        <v>0.379188017343319</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.05488565488565467</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2519603951479352</v>
+        <v>0.2111363599934632</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3332635017594314</v>
+        <v>0.2528128853098374</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4147761030926335</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1894796604048865</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1894796604048865</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4147761030926335</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="W13" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1906,10 +1930,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>2.073880515463168</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.073880515463168</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1923,25 +1947,25 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1949,12 +1973,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1964,55 +1988,55 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6272727272727273</v>
+        <v>0.5835764902042518</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2090909090909091</v>
+        <v>0.236348478532722</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1636363636363637</v>
+        <v>0.1800750312630263</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06280193236714959</v>
+        <v>0.05776014109347427</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.650131948091704</v>
+        <v>0.1101391702825879</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2779189034356739</v>
+        <v>0.3923018476563575</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07194914847262197</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="V14" t="n">
-        <v>0.650131948091704</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2020,10 +2044,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>3.25065974045852</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25065974045852</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2037,25 +2061,25 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -2063,12 +2087,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2078,55 +2102,55 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5082095387021109</v>
+        <v>0.5221774193548387</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2410737555381809</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2507167057597081</v>
+        <v>0.2237903225806452</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06361746361746357</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.688836885905344</v>
+        <v>0.3419055891466642</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1566867042163429</v>
+        <v>0.2647645273290432</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1544764098783133</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.180627347203233</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.180627347203233</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="V15" t="n">
-        <v>0.688836885905344</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="W15" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2134,10 +2158,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>3.44418442952672</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.44418442952672</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2151,38 +2175,38 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.8125</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2192,55 +2216,55 @@
         <v>1671</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3646038628301144</v>
+        <v>0.5636978579481398</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2562081198265668</v>
+        <v>0.2536640360766629</v>
       </c>
       <c r="L16" t="n">
-        <v>0.379188017343319</v>
+        <v>0.1826381059751973</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05488565488565467</v>
+        <v>0.09506172839506166</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2111363599934632</v>
+        <v>0.2968325553819417</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2528128853098374</v>
+        <v>0.2265005769057136</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2248,10 +2272,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>2.680253773483497</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.680253773483497</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2265,38 +2289,38 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2306,55 +2330,55 @@
         <v>1671</v>
       </c>
       <c r="G17" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5835764902042518</v>
+        <v>0.4343286698684485</v>
       </c>
       <c r="K17" t="n">
-        <v>0.236348478532722</v>
+        <v>0.2806431405303822</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1800750312630263</v>
+        <v>0.2850281896011694</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05776014109347427</v>
+        <v>0.09638278388278376</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1101391702825879</v>
+        <v>0.1839455355924454</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3923018476563575</v>
+        <v>0.3280930314040816</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3174839507980283</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3174839507980283</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="W17" t="n">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2362,10 +2386,10 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>2.487794910305273</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.487794910305273</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2379,38 +2403,38 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2420,55 +2444,55 @@
         <v>1671</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5221774193548387</v>
+        <v>0.3521126760563379</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2237903225806452</v>
+        <v>0.3661971830985915</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06392106392106389</v>
+        <v>0.09230769230769242</v>
       </c>
       <c r="N18" t="n">
         <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3419055891466642</v>
+        <v>0.1546325039321441</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2647645273290432</v>
+        <v>0.3258389601561393</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="W18" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2476,10 +2500,10 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>1.966649417621464</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.966649417621464</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2493,18 +2517,1142 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6359043646830759</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.211478587792986</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1526170475239382</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.09205799332820108</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.2962823561221066</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.4856871051415895</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2180305387363038</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2742085173486035</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2742085173486035</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.4856871051415895</v>
+      </c>
+      <c r="W19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.428435525707947</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.428435525707947</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.09582627098066902</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.2336393823796127</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.6705343466397182</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3561872214382136</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.3561872214382136</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.6705343466397182</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.352671733198591</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.352671733198591</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4043701639172806</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.2780547405980152</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3175750954847041</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.0007883530091030155</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.0007883530091030155</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5956298360827194</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.532520325203252</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.978149180413597</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.978149180413597</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.3439326658646624</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.2927412809917307</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3633260531436069</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.04897892794210235</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.04897892794210235</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.3633260531436069</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.816630265718035</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.816630265718035</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr">
+      <c r="AD22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2448931430703108</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.4556050920427626</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2995017648869266</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1751107341706508</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1751107341706508</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.4556050920427626</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.278025460213813</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.278025460213813</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5639990501068629</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.2436475896461648</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.1923533602469722</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.09447693307342431</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.2985644244914996</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3169153134554451</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3845202620530553</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1921669018060831</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1921669018060831</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.3845202620530553</v>
+      </c>
+      <c r="W24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.922601310265276</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.922601310265276</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5280322219860701</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.2609987840102575</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2109689940036723</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.09469585001230074</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.3422502016557549</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3415599378636597</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3161898604805853</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1857820203303152</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1857820203303152</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6577497983442451</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.935504469987229</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>3.288748991721225</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.288748991721225</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4329004329004328</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3246753246753247</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1161871972015239</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.2590926084503565</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.6247201943481197</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.300044869672795</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.300044869672795</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.6247201943481197</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>3.123600971740598</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.123600971740598</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5949500412764382</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.2395456745139343</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1655042842096274</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.0985708477968541</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3708726163433075</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.3150255188123561</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3141018648443366</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2240774249331308</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.2240774249331308</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6291273836566925</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.247311827956989</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.145636918283463</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.145636918283463</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.41797976447172</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.2627301376679383</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.3192900978603417</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.08748196248196249</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1630457610990916</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.3785328609147655</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4584213779861428</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1391312801258011</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1391312801258011</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.4584213779861428</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.292106889930714</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.292106889930714</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF28"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,20 +597,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>jqf7smJ3</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45471.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -620,55 +620,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.510925955038516</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2397421789026883</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2493318660587958</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06952501050861692</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1600414027325715</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3548428194046342</v>
+        <v>0.2825583427564414</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.1038652110113047</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2357839118039984</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4851157778627943</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="W2" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>2.425578889313971</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.425578889313971</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -693,25 +693,25 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -719,12 +719,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -734,55 +734,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>2.55</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.0706619627663416</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2825583427564414</v>
+        <v>0.2511722045198468</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1038652110113047</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.07425060353562463</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07425060353562463</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="W3" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>3.067882231161269</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.067882231161269</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -807,25 +807,25 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -848,55 +848,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="J4" t="n">
-        <v>0.369093490164267</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2689109714053944</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06248653307476837</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0706619627663416</v>
+        <v>0.1964722326397506</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2511722045198468</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.3909365342429724</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.316170294283473</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.316170294283473</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>3.390829163569058</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.390829163569058</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -921,16 +921,16 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -939,7 +939,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -947,12 +947,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -962,111 +962,111 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3129548762736535</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2503639010189229</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4366812227074235</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M5" t="n">
-        <v>0.06511627906976747</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4489400143010975</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.3040135939367658</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2470463917621368</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1826389330673235</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1826389330673235</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5510599856989025</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.755299928494512</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.755299928494512</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.1964722326397506</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.4125912331172771</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.3909365342429724</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.1622273320983542</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1622273320983542</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.4125912331172771</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.062956165586385</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.062956165586385</v>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>2</v>
-      </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1076,66 +1076,66 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="J6" t="n">
-        <v>0.631578947368421</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4489400143010975</v>
+        <v>0.1285853626482153</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3040135939367658</v>
+        <v>0.2521890736131565</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2470463917621368</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1826389330673235</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1826389330673235</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5510599856989025</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="W6" t="n">
-        <v>2.571428571428571</v>
+        <v>2.55</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>2.755299928494512</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.755299928494512</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1149,16 +1149,16 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
@@ -1167,7 +1167,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1190,55 +1190,55 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2689109714053944</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="L7" t="n">
-        <v>0.369093490164267</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="M7" t="n">
-        <v>0.06248653307476837</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="N7" t="n">
         <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1285853626482153</v>
+        <v>0.2868517150384613</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2521890736131565</v>
+        <v>0.3390256513186948</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="W7" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>3.096127818693141</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.096127818693141</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1263,25 +1263,25 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1304,55 +1304,55 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2074074074074074</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2868517150384613</v>
+        <v>0.07899396123747764</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3390256513186948</v>
+        <v>0.2628148092904548</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1667152262354365</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1667152262354365</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="W8" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>1.870613168214219</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.870613168214219</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1382,20 +1382,20 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1418,55 +1418,55 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
         <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4953320415712524</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2489695261581821</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2556984322705654</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05698837443119609</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="N9" t="n">
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07899396123747764</v>
+        <v>0.2519603951479352</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2628148092904548</v>
+        <v>0.3332635017594314</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="W9" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>3.290956147360338</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.290956147360338</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1491,38 +1491,38 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1532,55 +1532,55 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="L10" t="n">
-        <v>0.225296442687747</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2519603951479352</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3332635017594314</v>
+        <v>0.2779189034356739</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4147761030926335</v>
+        <v>0.07194914847262197</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1894796604048865</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1894796604048865</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4147761030926335</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="W10" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>2.073880515463168</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.073880515463168</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1617,13 +1617,13 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1646,55 +1646,55 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6272727272727273</v>
+        <v>0.5082095387021109</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2090909090909091</v>
+        <v>0.2410737555381809</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1636363636363637</v>
+        <v>0.2507167057597081</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06280193236714959</v>
+        <v>0.06361746361746357</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.650131948091704</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2779189034356739</v>
+        <v>0.1566867042163429</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07194914847262197</v>
+        <v>0.1544764098783133</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="V11" t="n">
-        <v>0.650131948091704</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>3.25065974045852</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25065974045852</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="n">
@@ -1737,7 +1737,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1760,55 +1760,55 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5082095387021109</v>
+        <v>0.3646038628301144</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2410737555381809</v>
+        <v>0.2562081198265668</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2507167057597081</v>
+        <v>0.379188017343319</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06361746361746357</v>
+        <v>0.05488565488565467</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.688836885905344</v>
+        <v>0.2111363599934632</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1566867042163429</v>
+        <v>0.2528128853098374</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1544764098783133</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.180627347203233</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.180627347203233</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="V12" t="n">
-        <v>0.688836885905344</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="W12" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>3.44418442952672</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.44418442952672</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1833,16 +1833,16 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>1</v>
@@ -1851,7 +1851,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1874,55 +1874,55 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3646038628301144</v>
+        <v>0.5835764902042518</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2562081198265668</v>
+        <v>0.236348478532722</v>
       </c>
       <c r="L13" t="n">
-        <v>0.379188017343319</v>
+        <v>0.1800750312630263</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05488565488565467</v>
+        <v>0.05776014109347427</v>
       </c>
       <c r="N13" t="n">
         <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2111363599934632</v>
+        <v>0.1101391702825879</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2528128853098374</v>
+        <v>0.3923018476563575</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="W13" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>2.680253773483497</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.680253773483497</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1947,25 +1947,25 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1988,55 +1988,55 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5835764902042518</v>
+        <v>0.5221774193548387</v>
       </c>
       <c r="K14" t="n">
-        <v>0.236348478532722</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1800750312630263</v>
+        <v>0.2237903225806452</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05776014109347427</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1101391702825879</v>
+        <v>0.3419055891466642</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3923018476563575</v>
+        <v>0.2647645273290432</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3174839507980283</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3174839507980283</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="W14" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>2.487794910305273</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.487794910305273</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="n">
@@ -2079,20 +2079,20 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.8125</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2102,55 +2102,55 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5221774193548387</v>
+        <v>0.5636978579481398</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2536640360766629</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2237903225806452</v>
+        <v>0.1826381059751973</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06392106392106389</v>
+        <v>0.09506172839506166</v>
       </c>
       <c r="N15" t="n">
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3419055891466642</v>
+        <v>0.2968325553819417</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2647645273290432</v>
+        <v>0.2265005769057136</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>1.966649417621464</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.966649417621464</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="n">
@@ -2193,20 +2193,20 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45476.8125</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2216,55 +2216,55 @@
         <v>1671</v>
       </c>
       <c r="G16" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5636978579481398</v>
+        <v>0.4343286698684485</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2536640360766629</v>
+        <v>0.2806431405303822</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1826381059751973</v>
+        <v>0.2850281896011694</v>
       </c>
       <c r="M16" t="n">
-        <v>0.09506172839506166</v>
+        <v>0.09638278388278376</v>
       </c>
       <c r="N16" t="n">
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2968325553819417</v>
+        <v>0.1839455355924454</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2265005769057136</v>
+        <v>0.3280930314040816</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4766668677123448</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2940287617371475</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="T16" t="n">
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2940287617371475</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4766668677123448</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>2.383334338561724</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.383334338561724</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2289,25 +2289,25 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -2315,12 +2315,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2330,55 +2330,55 @@
         <v>1671</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="H17" t="n">
         <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4343286698684485</v>
+        <v>0.3521126760563379</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2806431405303822</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2850281896011694</v>
+        <v>0.3661971830985915</v>
       </c>
       <c r="M17" t="n">
-        <v>0.09638278388278376</v>
+        <v>0.09230769230769242</v>
       </c>
       <c r="N17" t="n">
         <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1839455355924454</v>
+        <v>0.1546325039321441</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3280930314040816</v>
+        <v>0.3258389601561393</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4879614330034731</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2029332434023037</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="T17" t="n">
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2029332434023037</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4879614330034731</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>2.439807165017365</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.439807165017365</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="n">
@@ -2421,7 +2421,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2444,55 +2444,55 @@
         <v>1671</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3521126760563379</v>
+        <v>0.6359043646830759</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2816901408450704</v>
+        <v>0.211478587792986</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3661971830985915</v>
+        <v>0.1526170475239382</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09230769230769242</v>
+        <v>0.09205799332820108</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1546325039321441</v>
+        <v>0.2962823561221066</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3258389601561393</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5195285359117165</v>
+        <v>0.2180305387363038</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.153331352813125</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.153331352813125</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5195285359117165</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>2.597642679558583</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.597642679558583</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2522,20 +2522,20 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2558,55 +2558,55 @@
         <v>1671</v>
       </c>
       <c r="G19" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="H19" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6359043646830759</v>
+        <v>0.4051585169263837</v>
       </c>
       <c r="K19" t="n">
-        <v>0.211478587792986</v>
+        <v>0.2804943578721118</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1526170475239382</v>
+        <v>0.3143471252015046</v>
       </c>
       <c r="M19" t="n">
-        <v>0.09205799332820108</v>
+        <v>0.0969643383436487</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2962823561221066</v>
+        <v>0.09582627098066902</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4856871051415895</v>
+        <v>0.2336393823796127</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2180305387363038</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2742085173486035</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2742085173486035</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4856871051415895</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="W19" t="n">
-        <v>4.33</v>
+        <v>2.9</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>2.428435525707947</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.428435525707947</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2631,38 +2631,38 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AE19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45476.86458333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2693,45 +2693,45 @@
         <v>0.0969643383436487</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.09582627098066902</v>
+        <v>0.4043701639172806</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2336393823796127</v>
+        <v>0.2780547405980152</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.6705343466397182</v>
+        <v>0.3175750954847041</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3561872214382136</v>
+        <v>-0.0007883530091030155</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3561872214382136</v>
+        <v>0.0007883530091030155</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6705343466397182</v>
+        <v>0.5956298360827194</v>
       </c>
       <c r="W20" t="n">
-        <v>2.9</v>
+        <v>1.532520325203252</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>3.352671733198591</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.352671733198591</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2745,38 +2745,38 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45476.86458333334</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2807,45 +2807,45 @@
         <v>0.0969643383436487</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4043701639172806</v>
+        <v>0.3439326658646624</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2780547405980152</v>
+        <v>0.2927412809917307</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3175750954847041</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0007883530091030155</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="T21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0007883530091030155</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5956298360827194</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="W21" t="n">
-        <v>1.532520325203252</v>
+        <v>2.9</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>2.978149180413597</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.978149180413597</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2859,12 +2859,12 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="n">
@@ -2877,7 +2877,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2921,34 +2921,34 @@
         <v>0.0969643383436487</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3439326658646624</v>
+        <v>0.2448931430703108</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2927412809917307</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3633260531436069</v>
+        <v>0.2995017648869266</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.04897892794210235</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04897892794210235</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3633260531436069</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="W22" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>1.816630265718035</v>
+        <v>2.278025460213813</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.816630265718035</v>
+        <v>2.278025460213813</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -2991,7 +2991,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3014,55 +3014,55 @@
         <v>1671</v>
       </c>
       <c r="G23" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4051585169263837</v>
+        <v>0.5639990501068629</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2804943578721118</v>
+        <v>0.2436475896461648</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3143471252015046</v>
+        <v>0.1923533602469722</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0969643383436487</v>
+        <v>0.09447693307342431</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2448931430703108</v>
+        <v>0.2985644244914996</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4556050920427626</v>
+        <v>0.3169153134554451</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2995017648869266</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="R23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1751107341706508</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1751107341706508</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4556050920427626</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="W23" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>2.278025460213813</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.278025460213813</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
@@ -3087,16 +3087,16 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3105,20 +3105,20 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45476.9375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3128,66 +3128,66 @@
         <v>1671</v>
       </c>
       <c r="G24" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="H24" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5639990501068629</v>
+        <v>0.5280322219860701</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2436475896461648</v>
+        <v>0.2609987840102575</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1923533602469722</v>
+        <v>0.2109689940036723</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09447693307342431</v>
+        <v>0.09469585001230074</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2985644244914996</v>
+        <v>0.3422502016557549</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3169153134554451</v>
+        <v>0.3415599378636597</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3845202620530553</v>
+        <v>0.3161898604805853</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1921669018060831</v>
+        <v>-0.1857820203303152</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1921669018060831</v>
+        <v>0.1857820203303152</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3845202620530553</v>
+        <v>0.6577497983442451</v>
       </c>
       <c r="W24" t="n">
-        <v>4.75</v>
+        <v>1.935504469987229</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>1.922601310265276</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.922601310265276</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AE24" t="n">
@@ -3219,20 +3219,20 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45477.89583333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3242,66 +3242,66 @@
         <v>1671</v>
       </c>
       <c r="G25" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I25" t="n">
-        <v>4.33</v>
+        <v>2.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5280322219860701</v>
+        <v>0.4329004329004328</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2609987840102575</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2109689940036723</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="M25" t="n">
-        <v>0.09469585001230074</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3422502016557549</v>
+        <v>0.1161871972015239</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3415599378636597</v>
+        <v>0.2590926084503565</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3161898604805853</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1857820203303152</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="T25" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1857820203303152</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6577497983442451</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="W25" t="n">
-        <v>1.935504469987229</v>
+        <v>2.8</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>3.288748991721225</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.288748991721225</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
@@ -3333,20 +3333,20 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45477.89583333334</v>
+        <v>45477.9375</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3356,66 +3356,66 @@
         <v>1671</v>
       </c>
       <c r="G26" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="H26" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4329004329004328</v>
+        <v>0.5949500412764382</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.2395456745139343</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.1655042842096274</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.0985708477968541</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1161871972015239</v>
+        <v>0.3708726163433075</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2590926084503565</v>
+        <v>0.3150255188123561</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.6247201943481197</v>
+        <v>0.3141018648443366</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.300044869672795</v>
+        <v>-0.2240774249331308</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>0.300044869672795</v>
+        <v>0.2240774249331308</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6247201943481197</v>
+        <v>0.6291273836566925</v>
       </c>
       <c r="W26" t="n">
-        <v>2.8</v>
+        <v>2.247311827956989</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>3.123600971740598</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.123600971740598</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
@@ -3429,12 +3429,12 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE26" t="n">
@@ -3447,20 +3447,20 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45477.9375</v>
+        <v>45477.97916666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3470,66 +3470,66 @@
         <v>1671</v>
       </c>
       <c r="G27" t="n">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5949500412764382</v>
+        <v>0.41797976447172</v>
       </c>
       <c r="K27" t="n">
-        <v>0.2395456745139343</v>
+        <v>0.2627301376679383</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1655042842096274</v>
+        <v>0.3192900978603417</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0985708477968541</v>
+        <v>0.08748196248196249</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3708726163433075</v>
+        <v>0.1630457610990916</v>
       </c>
       <c r="P27" t="n">
-        <v>0.3150255188123561</v>
+        <v>0.3785328609147655</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3141018648443366</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2240774249331308</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="T27" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2240774249331308</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6291273836566925</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="W27" t="n">
-        <v>2.247311827956989</v>
+        <v>2.88</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>3.145636918283463</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.145636918283463</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
@@ -3541,119 +3541,21 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45477.97916666666</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>167</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.41797976447172</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.2627301376679383</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.3192900978603417</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.08748196248196249</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.1630457610990916</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.3785328609147655</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.4584213779861428</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0.1391312801258011</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0.1391312801258011</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0.4584213779861428</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.292106889930714</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2.292106889930714</v>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF27"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,20 +597,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>G0IRHiWk</t>
+          <t>W0zNyInr</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45476.8125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -620,55 +620,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.5636978579481398</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2536640360766629</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.1826381059751973</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.09506172839506166</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.2968325553819417</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2825583427564414</v>
+        <v>0.2265005769057136</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1038652110113047</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.07425060353562463</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07425060353562463</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6135764462322538</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="W2" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>3.067882231161269</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.067882231161269</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -698,33 +698,33 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiHVGBod</t>
+          <t>QJcftbvR</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -734,55 +734,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.369093490164267</v>
+        <v>0.4343286698684485</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2689109714053944</v>
+        <v>0.2806431405303822</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.2850281896011694</v>
       </c>
       <c r="M3" t="n">
-        <v>0.06248653307476837</v>
+        <v>0.09638278388278376</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0706619627663416</v>
+        <v>0.1839455355924454</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2511722045198468</v>
+        <v>0.3280930314040816</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.316170294283473</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.316170294283473</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6781658327138117</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>3.390829163569058</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.390829163569058</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -816,29 +816,29 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4nbBt7Y9</t>
+          <t>p4vRzx2l</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -848,55 +848,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3129548762736535</v>
+        <v>0.3521126760563379</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2503639010189229</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4366812227074235</v>
+        <v>0.3661971830985915</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06511627906976747</v>
+        <v>0.09230769230769242</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1964722326397506</v>
+        <v>0.1546325039321441</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4125912331172771</v>
+        <v>0.3258389601561393</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3909365342429724</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1622273320983542</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1622273320983542</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4125912331172771</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="W4" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>2.062956165586385</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.062956165586385</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -921,38 +921,38 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>b9cFuRmG</t>
+          <t>88KCueOd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45472.85416666666</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -962,66 +962,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6359043646830759</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.211478587792986</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1526170475239382</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.09205799332820108</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4489400143010975</v>
+        <v>0.2962823561221066</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3040135939367658</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2470463917621368</v>
+        <v>0.2180305387363038</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1826389330673235</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1826389330673235</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5510599856989025</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="W5" t="n">
-        <v>2.571428571428571</v>
+        <v>4.33</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>2.755299928494512</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.755299928494512</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1040,33 +1040,33 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
         <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zZKrObIr</t>
+          <t>naJGvFw3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45476.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1076,55 +1076,55 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3619955384303387</v>
+        <v>0.4051585169263837</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2689109714053944</v>
+        <v>0.2804943578721118</v>
       </c>
       <c r="L6" t="n">
-        <v>0.369093490164267</v>
+        <v>0.3143471252015046</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06248653307476837</v>
+        <v>0.0969643383436487</v>
       </c>
       <c r="N6" t="n">
         <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1285853626482153</v>
+        <v>0.09582627098066902</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2521890736131565</v>
+        <v>0.2336393823796127</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2501320735743613</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6192255637386282</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="W6" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>3.096127818693141</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.096127818693141</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="n">
@@ -1167,20 +1167,20 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hAFmNIXl</t>
+          <t>vRwVZeHf</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45476.86458333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1190,66 +1190,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4051585169263837</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2804943578721118</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2074074074074074</v>
+        <v>0.3143471252015046</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0969643383436487</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2868517150384613</v>
+        <v>0.4043701639172806</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3390256513186948</v>
+        <v>0.2780547405980152</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.3175750954847041</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1667152262354365</v>
+        <v>-0.0007883530091030155</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1667152262354365</v>
+        <v>0.0007883530091030155</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3741226336428439</v>
+        <v>0.5956298360827194</v>
       </c>
       <c r="W7" t="n">
-        <v>4.5</v>
+        <v>1.532520325203252</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>1.870613168214219</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.870613168214219</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="n">
@@ -1281,20 +1281,20 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>QNDeLd21</t>
+          <t>IHxZYFW0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1304,55 +1304,55 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4953320415712524</v>
+        <v>0.4051585169263837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2489695261581821</v>
+        <v>0.2804943578721118</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2556984322705654</v>
+        <v>0.3143471252015046</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05698837443119609</v>
+        <v>0.0969643383436487</v>
       </c>
       <c r="N8" t="n">
         <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07899396123747764</v>
+        <v>0.3439326658646624</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2628148092904548</v>
+        <v>0.2927412809917307</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4024927972015022</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6581912294720677</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="W8" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>3.290956147360338</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.290956147360338</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1377,38 +1377,38 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W0EiMxme</t>
+          <t>UN8LwZh9</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45472.89583333334</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1418,89 +1418,89 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5256916996047432</v>
+        <v>0.4051585169263837</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2490118577075099</v>
+        <v>0.2804943578721118</v>
       </c>
       <c r="L9" t="n">
-        <v>0.225296442687747</v>
+        <v>0.3143471252015046</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05680868838763575</v>
+        <v>0.0969643383436487</v>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.2448931430703108</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4556050920427626</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.2995017648869266</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1751107341706508</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.1751107341706508</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.4556050920427626</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.278025460213813</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.278025460213813</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
         <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.2519603951479352</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.3332635017594314</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.4147761030926335</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1894796604048865</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1894796604048865</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.4147761030926335</v>
-      </c>
-      <c r="W9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.073880515463168</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.073880515463168</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE9" t="n">
-        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1509,20 +1509,20 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>xbHaKGH7</t>
+          <t>pv9VXZo7</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1532,55 +1532,55 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="I10" t="n">
-        <v>5.75</v>
+        <v>4.75</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6272727272727273</v>
+        <v>0.5639990501068629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2090909090909091</v>
+        <v>0.2436475896461648</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1636363636363637</v>
+        <v>0.1923533602469722</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06280193236714959</v>
+        <v>0.09447693307342431</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.650131948091704</v>
+        <v>0.2985644244914996</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2779189034356739</v>
+        <v>0.3169153134554451</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.07194914847262197</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02285922081897673</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="V10" t="n">
-        <v>0.650131948091704</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>4.75</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>3.25065974045852</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.25065974045852</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -1617,26 +1617,26 @@
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>v3erq0f8</t>
+          <t>OU7ZWg1D</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45476.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1646,66 +1646,66 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5082095387021109</v>
+        <v>0.5280322219860701</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2410737555381809</v>
+        <v>0.2609987840102575</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2507167057597081</v>
+        <v>0.2109689940036723</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06361746361746357</v>
+        <v>0.09469585001230074</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0.688836885905344</v>
+        <v>0.3422502016557549</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1566867042163429</v>
+        <v>0.3415599378636597</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1544764098783133</v>
+        <v>0.3161898604805853</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.180627347203233</v>
+        <v>-0.1857820203303152</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.180627347203233</v>
+        <v>0.1857820203303152</v>
       </c>
       <c r="V11" t="n">
-        <v>0.688836885905344</v>
+        <v>0.6577497983442451</v>
       </c>
       <c r="W11" t="n">
-        <v>1.85</v>
+        <v>1.935504469987229</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>3.44418442952672</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.44418442952672</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1731,26 +1731,26 @@
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>IgfnrK9E</t>
+          <t>xYeHewvE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45477.89583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1760,55 +1760,55 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3646038628301144</v>
+        <v>0.4329004329004328</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2562081198265668</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="L12" t="n">
-        <v>0.379188017343319</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05488565488565467</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2111363599934632</v>
+        <v>0.1161871972015239</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2528128853098374</v>
+        <v>0.2590926084503565</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1568627373533805</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5360507546966995</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>2.680253773483497</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.680253773483497</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1833,38 +1833,38 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>nTbjsvPK</t>
+          <t>jy0LfcgK</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45477.9375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1874,66 +1874,66 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5835764902042518</v>
+        <v>0.5949500412764382</v>
       </c>
       <c r="K13" t="n">
-        <v>0.236348478532722</v>
+        <v>0.2395456745139343</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1800750312630263</v>
+        <v>0.1655042842096274</v>
       </c>
       <c r="M13" t="n">
-        <v>0.05776014109347427</v>
+        <v>0.0985708477968541</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1101391702825879</v>
+        <v>0.3708726163433075</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3923018476563575</v>
+        <v>0.3150255188123561</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.3141018648443366</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3174839507980283</v>
+        <v>-0.2240774249331308</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3174839507980283</v>
+        <v>0.2240774249331308</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4975589820610545</v>
+        <v>0.6291273836566925</v>
       </c>
       <c r="W13" t="n">
-        <v>5.25</v>
+        <v>2.247311827956989</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>2.487794910305273</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.487794910305273</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1965,20 +1965,20 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>YyTMIXGq</t>
+          <t>YakQgH8Q</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45472.97916666666</v>
+        <v>45477.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1988,55 +1988,55 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5221774193548387</v>
+        <v>0.41797976447172</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2540322580645161</v>
+        <v>0.2627301376679383</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2237903225806452</v>
+        <v>0.3192900978603417</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06392106392106389</v>
+        <v>0.08748196248196249</v>
       </c>
       <c r="N14" t="n">
         <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3419055891466642</v>
+        <v>0.1630457610990916</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2647645273290432</v>
+        <v>0.3785328609147655</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1695395609436476</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3933298835242927</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>1.966649417621464</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.966649417621464</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2061,38 +2061,38 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>xlCTyDNL</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45476.8125</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2101,67 +2101,47 @@
       <c r="F15" t="n">
         <v>1671</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5636978579481398</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.2536640360766629</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1826381059751973</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.09506172839506166</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2968325553819417</v>
+        <v>0.223759155178852</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2265005769057136</v>
+        <v>0.3735870219714469</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4766668677123448</v>
+        <v>0.4026538228497012</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>0.2940287617371475</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.2940287617371475</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4766668677123448</v>
-      </c>
-      <c r="W15" t="n">
-        <v>5</v>
-      </c>
+        <v>0.5973461771502988</v>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>2.383334338561724</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.383334338561724</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2175,38 +2155,38 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>rRCPxg8F</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2215,67 +2195,47 @@
       <c r="F16" t="n">
         <v>1671</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.4343286698684485</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.2806431405303822</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.2850281896011694</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.09638278388278376</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1839455355924454</v>
+        <v>0.6553996133903959</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3280930314040816</v>
+        <v>0.2410638081451136</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4879614330034731</v>
+        <v>0.1035365784644905</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>0.2029332434023037</v>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.2029332434023037</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4879614330034731</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.2</v>
-      </c>
+        <v>0.3446003866096041</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>2.439807165017365</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.439807165017365</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
@@ -2289,38 +2249,38 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>z9yhkyHs</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2329,67 +2289,47 @@
       <c r="F17" t="n">
         <v>1671</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.3521126760563379</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.2816901408450704</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.3661971830985915</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.09230769230769242</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1546325039321441</v>
+        <v>0.2360330562038147</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3258389601561393</v>
+        <v>0.4495899136506157</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5195285359117165</v>
+        <v>0.3143770301455694</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.153331352813125</v>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.153331352813125</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5195285359117165</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.5504100863493844</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>2.597642679558583</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.597642679558583</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
@@ -2403,16 +2343,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -2421,20 +2361,20 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>4rtdleWm</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2443,67 +2383,47 @@
       <c r="F18" t="n">
         <v>1671</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I18" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.6359043646830759</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.211478587792986</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.1526170475239382</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.09205799332820108</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2962823561221066</v>
+        <v>0.4795172639227532</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4856871051415895</v>
+        <v>0.2875773278385532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2180305387363038</v>
+        <v>0.2329054082386934</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
-        <v>0.2742085173486035</v>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.2742085173486035</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4856871051415895</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.5204827360772468</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>2.428435525707947</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.428435525707947</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2517,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -2535,20 +2455,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2557,67 +2477,47 @@
       <c r="F19" t="n">
         <v>1671</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09582627098066902</v>
+        <v>0.3186060955835326</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2336393823796127</v>
+        <v>0.4299583669421621</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.6705343466397182</v>
+        <v>0.2514355374743054</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0.3561872214382136</v>
-      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0.3561872214382136</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6705343466397182</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.5700416330578379</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>3.352671733198591</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.352671733198591</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
@@ -2631,38 +2531,38 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45476.86458333334</v>
+        <v>45479.89583333334</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2671,67 +2571,47 @@
       <c r="F20" t="n">
         <v>1671</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043701639172806</v>
+        <v>0.3070182371591425</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2780547405980152</v>
+        <v>0.2545542891632127</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3175750954847041</v>
+        <v>0.4384274736776448</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
-        <v>-0.0007883530091030155</v>
-      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0.0007883530091030155</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5956298360827194</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.532520325203252</v>
-      </c>
+        <v>0.5615725263223552</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>2.978149180413597</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.978149180413597</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
@@ -2757,26 +2637,26 @@
         <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45479.9375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2785,67 +2665,47 @@
       <c r="F21" t="n">
         <v>1671</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3439326658646624</v>
+        <v>0.3237649678672507</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2927412809917307</v>
+        <v>0.3903995195351682</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3633260531436069</v>
+        <v>0.2858355125975812</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S21" t="n">
-        <v>0.04897892794210235</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.04897892794210235</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3633260531436069</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.6096004804648318</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>1.816630265718035</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.816630265718035</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
@@ -2859,38 +2719,38 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2899,67 +2759,47 @@
       <c r="F22" t="n">
         <v>1671</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2448931430703108</v>
+        <v>0.2238260684664798</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4556050920427626</v>
+        <v>0.4161708195251439</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2995017648869266</v>
+        <v>0.3600031120083761</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
-        <v>0.1751107341706508</v>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.1751107341706508</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4556050920427626</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.25</v>
-      </c>
+        <v>0.5838291804748561</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y22" t="n">
-        <v>2.278025460213813</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.278025460213813</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
@@ -2973,588 +2813,18 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>pv9VXZo7</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45476.89583333334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>167</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.5639990501068629</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.2436475896461648</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.1923533602469722</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.09447693307342431</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.2985644244914996</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.3169153134554451</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0.3845202620530553</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.1921669018060831</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0.1921669018060831</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0.3845202620530553</v>
-      </c>
-      <c r="W23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.922601310265276</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.922601310265276</v>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>OU7ZWg1D</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45476.9375</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>houston dynamo</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>167</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I24" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.5280322219860701</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.2609987840102575</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.2109689940036723</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.09469585001230074</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.3422502016557549</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.3415599378636597</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.3161898604805853</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>-0.1857820203303152</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.1857820203303152</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0.6577497983442451</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.935504469987229</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y24" t="n">
-        <v>3.288748991721225</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.288748991721225</v>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>xYeHewvE</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45477.89583333334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>167</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.4329004329004328</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.2424242424242424</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.3246753246753247</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.1000000000000001</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.1161871972015239</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.2590926084503565</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0.6247201943481197</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.300044869672795</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.300044869672795</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.6247201943481197</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y25" t="n">
-        <v>3.123600971740598</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.123600971740598</v>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>jy0LfcgK</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45477.9375</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>167</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.5949500412764382</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.2395456745139343</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0.1655042842096274</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.0985708477968541</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.3708726163433075</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.3150255188123561</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.3141018648443366</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.2240774249331308</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0.2240774249331308</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0.6291273836566925</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.247311827956989</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y26" t="n">
-        <v>3.145636918283463</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.145636918283463</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>YakQgH8Q</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45477.97916666666</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>167</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.41797976447172</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.2627301376679383</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0.3192900978603417</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.08748196248196249</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.1630457610990916</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.3785328609147655</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.4584213779861428</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.1391312801258011</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0.1391312801258011</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0.4584213779861428</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.292106889930714</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.292106889930714</v>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="86">
   <si>
     <t>id_match</t>
   </si>
@@ -263,9 +263,6 @@
   </si>
   <si>
     <t>jqf7smJ3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">orlando city </t>
   </si>
   <si>
     <t>dif_prob_mod_bm &gt; 0.0</t>
@@ -284,7 +281,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,13 +291,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -361,16 +352,16 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -727,7 +718,7 @@
     <col min="32" max="32" style="12" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -825,12 +816,12 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B2" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>33</v>
@@ -919,12 +910,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>39</v>
@@ -1013,12 +1004,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>43</v>
@@ -1107,12 +1098,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>47</v>
@@ -1201,12 +1192,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>50</v>
@@ -1295,12 +1286,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B7" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>54</v>
@@ -1389,12 +1380,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>58</v>
@@ -1483,12 +1474,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="5">
-        <v>25568.875526215277</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>61</v>
@@ -1577,12 +1568,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B10" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>64</v>
@@ -1671,12 +1662,12 @@
         <v>1</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B11" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>67</v>
@@ -1765,12 +1756,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B12" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>70</v>
@@ -1859,12 +1850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B13" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>73</v>
@@ -1953,12 +1944,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B14" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>77</v>
@@ -2047,12 +2038,12 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B15" s="5">
-        <v>25568.875526226853</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>80</v>
@@ -2141,18 +2132,18 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="20.25">
       <c r="A16" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B16" s="5">
-        <v>25568.875526284723</v>
+        <v>25568.875520833335</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="E16" s="7">
         <v>167</v>
@@ -2212,7 +2203,7 @@
         <v>3.75</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y16" s="8">
         <v>2.425578889313971</v>
@@ -2221,10 +2212,10 @@
         <v>2.425578889313971</v>
       </c>
       <c r="AA16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB16" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="AB16" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>36</v>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AF19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,20 +597,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W0zNyInr</t>
+          <t>xlCTyDNL</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45476.8125</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -619,67 +619,47 @@
       <c r="F2" t="n">
         <v>1671</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.5636978579481398</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.2536640360766629</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1826381059751973</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.09506172839506166</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2968325553819417</v>
+        <v>0.223759155178852</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2265005769057136</v>
+        <v>0.3735870219714469</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4766668677123448</v>
+        <v>0.4026538228497012</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0.2940287617371475</v>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.2940287617371475</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4766668677123448</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5</v>
-      </c>
+        <v>0.5973461771502988</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>2.383334338561724</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.383334338561724</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -693,38 +673,38 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QJcftbvR</t>
+          <t>rRCPxg8F</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -733,67 +713,47 @@
       <c r="F3" t="n">
         <v>1671</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.4343286698684485</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2806431405303822</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.2850281896011694</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.09638278388278376</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1839455355924454</v>
+        <v>0.6553996133903959</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3280930314040816</v>
+        <v>0.2410638081451136</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4879614330034731</v>
+        <v>0.1035365784644905</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.2029332434023037</v>
-      </c>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.2029332434023037</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4879614330034731</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.2</v>
-      </c>
+        <v>0.3446003866096041</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>2.439807165017365</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.439807165017365</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -807,38 +767,38 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>p4vRzx2l</t>
+          <t>z9yhkyHs</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -847,67 +807,47 @@
       <c r="F4" t="n">
         <v>1671</v>
       </c>
-      <c r="G4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.3521126760563379</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2816901408450704</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.3661971830985915</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.09230769230769242</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1546325039321441</v>
+        <v>0.2360330562038147</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3258389601561393</v>
+        <v>0.4495899136506157</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5195285359117165</v>
+        <v>0.3143770301455694</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.153331352813125</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.153331352813125</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5195285359117165</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.5504100863493844</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>2.597642679558583</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.597642679558583</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -921,16 +861,16 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
@@ -939,20 +879,20 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>88KCueOd</t>
+          <t>4rtdleWm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -961,67 +901,47 @@
       <c r="F5" t="n">
         <v>1671</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6359043646830759</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.211478587792986</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1526170475239382</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.09205799332820108</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2962823561221066</v>
+        <v>0.4795172639227532</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4856871051415895</v>
+        <v>0.2875773278385532</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2180305387363038</v>
+        <v>0.2329054082386934</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>0.2742085173486035</v>
-      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.2742085173486035</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4856871051415895</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.33</v>
-      </c>
+        <v>0.5204827360772468</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>2.428435525707947</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.428435525707947</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1035,7 +955,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1053,20 +973,20 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>naJGvFw3</t>
+          <t>rZv0mFof</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45476.85416666666</v>
+        <v>45479.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1075,67 +995,47 @@
       <c r="F6" t="n">
         <v>1671</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.09582627098066902</v>
+        <v>0.3186060955835326</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2336393823796127</v>
+        <v>0.4299583669421621</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6705343466397182</v>
+        <v>0.2514355374743054</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0.3561872214382136</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.3561872214382136</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6705343466397182</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.5700416330578379</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>3.352671733198591</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.352671733198591</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1149,38 +1049,38 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vRwVZeHf</t>
+          <t>QcU4nZ00</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45476.86458333334</v>
+        <v>45479.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1189,67 +1089,47 @@
       <c r="F7" t="n">
         <v>1671</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4043701639172806</v>
+        <v>0.3070182371591425</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2780547405980152</v>
+        <v>0.2545542891632127</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3175750954847041</v>
+        <v>0.4384274736776448</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>-0.0007883530091030155</v>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.0007883530091030155</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5956298360827194</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.532520325203252</v>
-      </c>
+        <v>0.5615725263223552</v>
+      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>2.978149180413597</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.978149180413597</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1275,26 +1155,26 @@
         <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>IHxZYFW0</t>
+          <t>xYX8ogG6</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45479.9375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1303,67 +1183,47 @@
       <c r="F8" t="n">
         <v>1671</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3439326658646624</v>
+        <v>0.3237649678672507</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2927412809917307</v>
+        <v>0.3903995195351682</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3633260531436069</v>
+        <v>0.2858355125975812</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.04897892794210235</v>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.04897892794210235</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3633260531436069</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.9</v>
-      </c>
+        <v>0.6096004804648318</v>
+      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>1.816630265718035</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.816630265718035</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1377,38 +1237,38 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>UN8LwZh9</t>
+          <t>WfXCpDVC</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45479.97916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1417,67 +1277,47 @@
       <c r="F9" t="n">
         <v>1671</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.4051585169263837</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2804943578721118</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3143471252015046</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.0969643383436487</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2448931430703108</v>
+        <v>0.2238260684664798</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4556050920427626</v>
+        <v>0.4161708195251439</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2995017648869266</v>
+        <v>0.3600031120083761</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.1751107341706508</v>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1751107341706508</v>
-      </c>
+        <v>-100</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4556050920427626</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.25</v>
-      </c>
+        <v>0.5838291804748561</v>
+      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>2.278025460213813</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.278025460213813</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1491,38 +1331,38 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pv9VXZo7</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45476.89583333334</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1531,67 +1371,47 @@
       <c r="F10" t="n">
         <v>1671</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5639990501068629</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2436475896461648</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.1923533602469722</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.09447693307342431</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2985644244914996</v>
+        <v>0.1120165223774064</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3169153134554451</v>
+        <v>0.2698353424998143</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3845202620530553</v>
+        <v>0.6181481351227792</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>0.1921669018060831</v>
-      </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.1921669018060831</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3845202620530553</v>
-      </c>
-      <c r="W10" t="n">
-        <v>4.75</v>
-      </c>
+        <v>0.3818518648772208</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>1.922601310265276</v>
+        <v>1.909259324386104</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.922601310265276</v>
+        <v>1.909259324386104</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1605,38 +1425,34 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OU7ZWg1D</t>
+          <t>QgE37zwQ</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45476.9375</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1645,67 +1461,47 @@
       <c r="F11" t="n">
         <v>1671</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5280322219860701</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.2609987840102575</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.2109689940036723</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.09469585001230074</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3422502016557549</v>
+        <v>0.2405801587546016</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3415599378636597</v>
+        <v>0.3523714869042734</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3161898604805853</v>
+        <v>0.407048354341125</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>-0.1857820203303152</v>
-      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1857820203303152</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6577497983442451</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.935504469987229</v>
-      </c>
+        <v>0.592951645658875</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>3.288748991721225</v>
+        <v>2.964758228294375</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.288748991721225</v>
+        <v>2.964758228294375</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1719,38 +1515,38 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>xYeHewvE</t>
+          <t>n3Fa8GNJ</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45477.89583333334</v>
+        <v>45480.89583333334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1759,67 +1555,47 @@
       <c r="F12" t="n">
         <v>1671</v>
       </c>
-      <c r="G12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.4329004329004328</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2424242424242424</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.3246753246753247</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.1000000000000001</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1161871972015239</v>
+        <v>0.198872053428177</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2590926084503565</v>
+        <v>0.3501070220679228</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6247201943481197</v>
+        <v>0.4510209245039001</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>0.300044869672795</v>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.300044869672795</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6247201943481197</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.8</v>
-      </c>
+        <v>0.5489790754960999</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>3.123600971740598</v>
+        <v>2.7448953774805</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.123600971740598</v>
+        <v>2.7448953774805</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1845,17 +1621,17 @@
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>jy0LfcgK</t>
+          <t>rZ0V2fos</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45477.9375</v>
+        <v>45480.9375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1864,7 +1640,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1873,67 +1649,47 @@
       <c r="F13" t="n">
         <v>1671</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.5949500412764382</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.2395456745139343</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1655042842096274</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0985708477968541</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3708726163433075</v>
+        <v>0.188470341582974</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3150255188123561</v>
+        <v>0.2394887306904805</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3141018648443366</v>
+        <v>0.5720409277265455</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>-0.2240774249331308</v>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.2240774249331308</v>
-      </c>
+        <v>-2</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6291273836566925</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.247311827956989</v>
-      </c>
+        <v>0.4279590722734545</v>
+      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>3.145636918283463</v>
+        <v>2.139795361367272</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.145636918283463</v>
+        <v>2.139795361367272</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1947,7 +1703,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -1959,17 +1715,17 @@
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>YakQgH8Q</t>
+          <t>dx5Z1E0m</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45477.97916666666</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,7 +1734,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1987,67 +1743,47 @@
       <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.41797976447172</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2627301376679383</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.3192900978603417</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.08748196248196249</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1630457610990916</v>
+        <v>0.4414859472229207</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3785328609147655</v>
+        <v>0.3348306941728106</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4584213779861428</v>
+        <v>0.2236833586042686</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
-        <v>0.1391312801258011</v>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.1391312801258011</v>
-      </c>
+        <v>-1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4584213779861428</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.88</v>
-      </c>
+        <v>0.5585140527770793</v>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>2.292106889930714</v>
+        <v>2.792570263885397</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.292106889930714</v>
+        <v>2.792570263885397</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2061,38 +1797,38 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>xlCTyDNL</t>
+          <t>v1fv1YFg</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45479.85416666666</v>
+        <v>45480.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2109,27 +1845,27 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.223759155178852</v>
+        <v>0.3763245744414552</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3735870219714469</v>
+        <v>0.2845306901402596</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4026538228497012</v>
+        <v>0.3391447354182852</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5973461771502988</v>
+        <v>0.6236754255585448</v>
       </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
@@ -2138,10 +1874,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>2.986730885751494</v>
+        <v>3.118377127792724</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.986730885751494</v>
+        <v>3.118377127792724</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
@@ -2155,45 +1891,45 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF15" t="n">
         <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>rRCPxg8F</t>
+          <t>SKZvN7pn</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45479.85416666666</v>
+        <v>45482.83333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>indy eleven</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>167</v>
       </c>
       <c r="F16" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -2202,41 +1938,27 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.6553996133903959</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.2410638081451136</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.1035365784644905</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>0.3446003866096041</v>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
-      <c r="Y16" t="n">
-        <v>1.723001933048021</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.723001933048021</v>
-      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>usa</t>
@@ -2244,50 +1966,50 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>z9yhkyHs</t>
+          <t>APpAklQ6</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45479.85416666666</v>
+        <v>45483</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>sacramento republic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>167</v>
       </c>
       <c r="F17" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -2296,18 +2018,10 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.2360330562038147</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.4495899136506157</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3143770301455694</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>1</v>
       </c>
@@ -2316,21 +2030,15 @@
         <v>-100</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.5504100863493844</v>
-      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
-      <c r="Y17" t="n">
-        <v>2.752050431746922</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.752050431746922</v>
-      </c>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>usa</t>
@@ -2338,21 +2046,21 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
         <v>1</v>
@@ -2361,27 +2069,27 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>4rtdleWm</t>
+          <t>d0ReJPqB</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45479.85416666666</v>
+        <v>45483.91666666666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>167</v>
       </c>
       <c r="F18" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -2391,27 +2099,27 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4795172639227532</v>
+        <v>0.182855882324076</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2875773278385532</v>
+        <v>0.332272585414535</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2329054082386934</v>
+        <v>0.4848715322613889</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5204827360772468</v>
+        <v>0.5151284677386111</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
@@ -2420,10 +2128,10 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>2.602413680386234</v>
+        <v>2.575642338693056</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.602413680386234</v>
+        <v>2.575642338693056</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
@@ -2432,50 +2140,50 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>rZv0mFof</t>
+          <t>0YXnLoFb</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45479.85416666666</v>
+        <v>45484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new mexico</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>167</v>
       </c>
       <c r="F19" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -2484,18 +2192,10 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.3186060955835326</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.4299583669421621</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.2514355374743054</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>1</v>
       </c>
@@ -2504,21 +2204,15 @@
         <v>-100</v>
       </c>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>0.5700416330578379</v>
-      </c>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
-      <c r="Y19" t="n">
-        <v>2.85020816528919</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.85020816528919</v>
-      </c>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
           <t>usa</t>
@@ -2526,305 +2220,23 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>mls</t>
+          <t>us open cup</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>QcU4nZ00</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45479.89583333334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>167</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.3070182371591425</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.2545542891632127</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.4384274736776448</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>0.5615725263223552</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.807862631611776</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.807862631611776</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>xYX8ogG6</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45479.9375</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>167</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.3237649678672507</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.3903995195351682</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.2858355125975812</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>0.6096004804648318</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y21" t="n">
-        <v>3.048002402324159</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.048002402324159</v>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>WfXCpDVC</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45479.97916666666</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>new england revolution</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>167</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.2238260684664798</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.4161708195251439</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.3600031120083761</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="n">
-        <v>0.5838291804748561</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.919145902374281</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.919145902374281</v>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/predicciones.xlsx
+++ b/p6_deployment/data/predicciones.xlsx
@@ -634,28 +634,28 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3193946784018565</v>
+        <v>0.3174877309452435</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1327931856650388</v>
+        <v>0.1352195093147789</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.07394357007552477</v>
+        <v>-0.07446294626865269</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5478121359331051</v>
+        <v>0.5472927597399772</v>
       </c>
       <c r="Y2" t="n">
         <v>1.53</v>
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.889293414211416</v>
+        <v>6.884337015187532</v>
       </c>
     </row>
     <row r="3">
@@ -732,28 +732,28 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2075059145687156</v>
+        <v>0.2100382114772122</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2996237109575965</v>
+        <v>0.2980519455785725</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1952030200217249</v>
+        <v>-0.1961635515511977</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4928703744736879</v>
+        <v>0.4919098429442151</v>
       </c>
       <c r="Y3" t="n">
         <v>1.36</v>
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.499224233569205</v>
+        <v>6.187681235770201</v>
       </c>
     </row>
     <row r="4">
@@ -830,28 +830,28 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3094895004568461</v>
+        <v>0.3099576327625041</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2437127070590602</v>
+        <v>0.2434906243134364</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3365738390178907</v>
+        <v>-0.336819888577925</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4467977924840937</v>
+        <v>0.4465517429240594</v>
       </c>
       <c r="Y4" t="n">
         <v>1.22</v>
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.172123430293599</v>
+        <v>5.617126553015594</v>
       </c>
     </row>
     <row r="5">
@@ -928,28 +928,28 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2278268765141783</v>
+        <v>0.2312737815347075</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3619384246905776</v>
+        <v>0.364304302167788</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07939031083750286</v>
+        <v>0.07357752833976383</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4102346987952438</v>
+        <v>0.4044219162975047</v>
       </c>
       <c r="Y5" t="n">
         <v>2.88</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.91253699516467</v>
+        <v>5.087179975563296</v>
       </c>
     </row>
     <row r="6">
@@ -1026,28 +1026,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3445222740792314</v>
+        <v>0.346874166327044</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1699860963163061</v>
+        <v>0.1670322764584181</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2238268683093066</v>
+        <v>-0.2232249406992314</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4854916296044625</v>
+        <v>0.4860935572145377</v>
       </c>
       <c r="Y6" t="n">
         <v>1.33</v>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.446837471862763</v>
+        <v>6.114518800442628</v>
       </c>
     </row>
     <row r="7">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.605577891638621</v>
+        <v>4.616442401246155</v>
       </c>
     </row>
     <row r="8">
@@ -1222,28 +1222,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3805482879075007</v>
+        <v>0.3743799427639963</v>
       </c>
       <c r="R8" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2230859571026854</v>
+        <v>0.2309863852711951</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1255324216564806</v>
+        <v>0.1238003386314753</v>
       </c>
       <c r="X8" t="n">
-        <v>0.396365754989814</v>
+        <v>0.3946336719648086</v>
       </c>
       <c r="Y8" t="n">
         <v>3.5</v>
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.81407186767594</v>
+        <v>4.964054698325397</v>
       </c>
     </row>
     <row r="9">
@@ -1296,52 +1296,52 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3852691218130311</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2776203966005666</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3371104815864023</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05942376950780304</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3106801764048837</v>
+        <v>0.3144227816646827</v>
       </c>
       <c r="R9" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3052092685201684</v>
+        <v>0.3013720182071305</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1064901584743814</v>
+        <v>0.1062129221359085</v>
       </c>
       <c r="X9" t="n">
-        <v>0.384110555074948</v>
+        <v>0.3842052001281865</v>
       </c>
       <c r="Y9" t="n">
         <v>3.4</v>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.72706381292092</v>
+        <v>4.832876067877577</v>
       </c>
     </row>
     <row r="10">
@@ -1418,28 +1418,28 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2820386913923193</v>
+        <v>0.2820683392247597</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3396646854508487</v>
+        <v>0.3380256032651838</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1305811565363245</v>
+        <v>-0.1289717221830999</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3782966231568318</v>
+        <v>0.3799060575100564</v>
       </c>
       <c r="Y10" t="n">
         <v>1.85</v>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.685786729708283</v>
+        <v>4.778797613279301</v>
       </c>
     </row>
     <row r="11">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
       <c r="AB11" t="n">
-        <v>3.686010949050913</v>
+        <v>6.53070372267968</v>
       </c>
     </row>
     <row r="12">
@@ -1596,49 +1596,49 @@
         <v>4.75</v>
       </c>
       <c r="K12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2061603080154008</v>
+        <v>0.2077442718852288</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1953097654882744</v>
+        <v>0.1968103628386378</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5985299264963249</v>
+        <v>0.5954453652761335</v>
       </c>
       <c r="O12" t="n">
-        <v>0.07790982833427651</v>
+        <v>0.06969121317093152</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3028390567587279</v>
+        <v>0.2992414176127644</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3365992230389832</v>
+        <v>0.3364340154000717</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.2379682062940361</v>
+        <v>-0.2311207982889693</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3605617202022888</v>
+        <v>0.3643245669871641</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.55987451137947</v>
+        <v>4.582799712613659</v>
       </c>
     </row>
     <row r="13">
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.434307874051561</v>
+        <v>6.084747855583996</v>
       </c>
     </row>
     <row r="19">
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.766953864951772</v>
+        <v>4.902360887174315</v>
       </c>
     </row>
     <row r="36">
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
       <c r="AB45" t="n">
-        <v>3.254462363758577</v>
+        <v>5.766105898245254</v>
       </c>
     </row>
     <row r="46">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="AA47" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
       <c r="AB47" t="n">
-        <v>4.271171166281338</v>
+        <v>7.567463532092283</v>
       </c>
     </row>
     <row r="48">
@@ -4550,28 +4550,28 @@
         <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.1729686475272086</v>
+        <v>0.1664549248772655</v>
       </c>
       <c r="R48" t="n">
-        <v>0.1505997669895271</v>
+        <v>0.1487827602374613</v>
       </c>
       <c r="S48" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="V48" t="n">
         <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>0.09637039221452426</v>
+        <v>0.1047011216165326</v>
       </c>
       <c r="X48" t="n">
-        <v>0.6764315854832647</v>
+        <v>0.6847623148852729</v>
       </c>
       <c r="Y48" t="n">
         <v>1.62</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="AA48" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
       <c r="AB48" t="n">
-        <v>20.29294756449794</v>
+        <v>12.13230199941425</v>
       </c>
     </row>
     <row r="49">
@@ -4648,28 +4648,28 @@
         <v>2</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.2317616976083876</v>
+        <v>0.2371626881820494</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1873067975146034</v>
+        <v>0.1955269582216931</v>
       </c>
       <c r="S49" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="V49" t="n">
         <v>2</v>
       </c>
       <c r="W49" t="n">
-        <v>0.1506355547212458</v>
+        <v>0.1370144034404941</v>
       </c>
       <c r="X49" t="n">
-        <v>0.580931504877009</v>
+        <v>0.5673103535962573</v>
       </c>
       <c r="Y49" t="n">
         <v>2.2</v>
@@ -4680,10 +4680,10 @@
         </is>
       </c>
       <c r="AA49" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
       <c r="AB49" t="n">
-        <v>17.42794514631027</v>
+        <v>10.05134246965305</v>
       </c>
     </row>
     <row r="50">
@@ -4746,28 +4746,28 @@
         <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.3533679002749218</v>
+        <v>0.354926915744822</v>
       </c>
       <c r="R50" t="n">
-        <v>0.2489795619064891</v>
+        <v>0.2495066794755585</v>
       </c>
       <c r="S50" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="V50" t="n">
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>0.0411338380632586</v>
+        <v>0.03904770502428889</v>
       </c>
       <c r="X50" t="n">
-        <v>0.3976525378185889</v>
+        <v>0.3955664047796192</v>
       </c>
       <c r="Y50" t="n">
         <v>2.63</v>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="AA50" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
       <c r="AB50" t="n">
-        <v>11.92957613455767</v>
+        <v>7.008462614378747</v>
       </c>
     </row>
     <row r="51">
@@ -4844,28 +4844,28 @@
         <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.1295641630952608</v>
+        <v>0.1427096599821709</v>
       </c>
       <c r="R51" t="n">
-        <v>0.1728765496975989</v>
+        <v>0.1812842175949421</v>
       </c>
       <c r="S51" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="V51" t="n">
         <v>2</v>
       </c>
       <c r="W51" t="n">
-        <v>0.04369317407792372</v>
+        <v>0.02214000929367066</v>
       </c>
       <c r="X51" t="n">
-        <v>0.6975592872071401</v>
+        <v>0.676006122422887</v>
       </c>
       <c r="Y51" t="n">
         <v>1.45</v>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="AA51" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
       <c r="AB51" t="n">
-        <v>20.9267786162142</v>
+        <v>11.97716383101715</v>
       </c>
     </row>
     <row r="52">
@@ -4942,28 +4942,28 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="R52" t="n">
-        <v>0.2753010456706311</v>
+        <v>0.275418703280472</v>
       </c>
       <c r="S52" t="n">
-        <v>0.1576425674115408</v>
+        <v>0.1510256328109897</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="V52" t="n">
         <v>1</v>
       </c>
       <c r="W52" t="n">
-        <v>-0.06270139854930001</v>
+        <v>-0.05620212155858972</v>
       </c>
       <c r="X52" t="n">
-        <v>0.5670563869178281</v>
+        <v>0.5735556639085384</v>
       </c>
       <c r="Y52" t="n">
         <v>1.5</v>
@@ -4974,10 +4974,10 @@
         </is>
       </c>
       <c r="AA52" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
       <c r="AB52" t="n">
-        <v>17.01169160753484</v>
+        <v>10.16199398937248</v>
       </c>
     </row>
     <row r="53">
@@ -5040,28 +5040,28 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="R53" t="n">
-        <v>0.2582212984756653</v>
+        <v>0.260593877861823</v>
       </c>
       <c r="S53" t="n">
-        <v>0.2850692333242246</v>
+        <v>0.2846952181133715</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="V53" t="n">
         <v>1</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.003613961660740239</v>
+        <v>-0.005612525836044324</v>
       </c>
       <c r="X53" t="n">
-        <v>0.4567094682001097</v>
+        <v>0.4547109040248056</v>
       </c>
       <c r="Y53" t="n">
         <v>2.05</v>
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="AA53" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
       <c r="AB53" t="n">
-        <v>13.70128404600329</v>
+        <v>8.056357498265502</v>
       </c>
     </row>
     <row r="54">
@@ -5138,28 +5138,28 @@
         <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.3661568152418682</v>
+        <v>0.3483132254346947</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2318042695397813</v>
+        <v>0.2281432612817216</v>
       </c>
       <c r="S54" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="V54" t="n">
         <v>2</v>
       </c>
       <c r="W54" t="n">
-        <v>-0.07145285809060742</v>
+        <v>-0.04994826002537434</v>
       </c>
       <c r="X54" t="n">
-        <v>0.4020389152183506</v>
+        <v>0.4235435132835836</v>
       </c>
       <c r="Y54" t="n">
         <v>2</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="AA54" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
       <c r="AB54" t="n">
-        <v>12.06116745655052</v>
+        <v>7.504148083719076</v>
       </c>
     </row>
     <row r="55">
@@ -5233,34 +5233,34 @@
         <v>0.05106209150326801</v>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.3787959845619371</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="R55" t="n">
-        <v>0.2353448661406139</v>
+        <v>0.2369855400499945</v>
       </c>
       <c r="S55" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3793676215468028</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W55" t="n">
-        <v>0.08854084381746435</v>
+        <v>-0.03920586272388638</v>
       </c>
       <c r="X55" t="n">
-        <v>0.3858591492974488</v>
+        <v>0.3836468384032026</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
@@ -5268,10 +5268,10 @@
         </is>
       </c>
       <c r="AA55" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
       <c r="AB55" t="n">
-        <v>11.57577447892346</v>
+        <v>6.79727725000165</v>
       </c>
     </row>
     <row r="56">
@@ -5334,28 +5334,28 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="R56" t="n">
-        <v>0.28390046926644</v>
+        <v>0.2827917961495244</v>
       </c>
       <c r="S56" t="n">
-        <v>0.2836653976507963</v>
+        <v>0.2805224764028122</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="V56" t="n">
         <v>1</v>
       </c>
       <c r="W56" t="n">
-        <v>-0.02788929677808633</v>
+        <v>-0.02363770241318652</v>
       </c>
       <c r="X56" t="n">
-        <v>0.4324341330827636</v>
+        <v>0.4366857274476634</v>
       </c>
       <c r="Y56" t="n">
         <v>2.05</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="AA56" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
       <c r="AB56" t="n">
-        <v>12.97302399248291</v>
+        <v>7.736995756135612</v>
       </c>
     </row>
     <row r="57">
@@ -5482,13 +5482,13 @@
         <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.09632788562397251</v>
+        <v>0.0971796147990323</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1182393982592243</v>
+        <v>0.1193467756926307</v>
       </c>
       <c r="S58" t="n">
-        <v>0.7854327161168032</v>
+        <v>0.7834736095083371</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
-        <v>0.2145672838831968</v>
+        <v>0.2165263904916629</v>
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr">
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="AA58" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.8110177206963003</v>
+        <v>1.450043520282718</v>
       </c>
     </row>
     <row r="59">
@@ -6072,13 +6072,13 @@
         <v>2</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.06117359204943089</v>
+        <v>0.05890705866981628</v>
       </c>
       <c r="R67" t="n">
-        <v>0.08600848854088683</v>
+        <v>0.0850825161689492</v>
       </c>
       <c r="S67" t="n">
-        <v>0.8528179194096823</v>
+        <v>0.8560104251612345</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="n">
-        <v>0.1471820805903177</v>
+        <v>0.1439895748387655</v>
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr">
@@ -6098,10 +6098,10 @@
         </is>
       </c>
       <c r="AA67" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.5563162909433954</v>
+        <v>0.9642757610705874</v>
       </c>
     </row>
     <row r="68">
@@ -6598,13 +6598,13 @@
         <v>2</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.1776197490202196</v>
+        <v>0.1794567954919975</v>
       </c>
       <c r="R75" t="n">
-        <v>0.1134975541628484</v>
+        <v>0.1125722033075784</v>
       </c>
       <c r="S75" t="n">
-        <v>0.7088826968169321</v>
+        <v>0.7079710012004241</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="n">
-        <v>0.2911173031830679</v>
+        <v>0.2920289987995759</v>
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr">
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="AA75" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.100360164000171</v>
+        <v>1.955672731081154</v>
       </c>
     </row>
     <row r="76">
@@ -7316,13 +7316,13 @@
         <v>2</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.03980787590673734</v>
+        <v>0.03866522508709244</v>
       </c>
       <c r="R86" t="n">
-        <v>0.07123388984010177</v>
+        <v>0.0701925108605358</v>
       </c>
       <c r="S86" t="n">
-        <v>0.8889582342531608</v>
+        <v>0.8911422640523718</v>
       </c>
       <c r="T86" t="n">
         <v>1</v>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
-        <v>0.1110417657468392</v>
+        <v>0.1088577359476282</v>
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr">
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="AA86" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.4197137519209032</v>
+        <v>0.7290033066411972</v>
       </c>
     </row>
     <row r="87">
@@ -7384,55 +7384,55 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K87" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5185185185185186</v>
+        <v>0.4926019487549621</v>
       </c>
       <c r="M87" t="n">
-        <v>0.2592592592592593</v>
+        <v>0.2674124864669794</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2399855647780585</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.06844033159822627</v>
       </c>
       <c r="P87" t="n">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="R87" t="n">
-        <v>0.03928553527936484</v>
+        <v>0.04088231273115332</v>
       </c>
       <c r="S87" t="n">
-        <v>0.1616678371451817</v>
+        <v>0.1760312514530925</v>
       </c>
       <c r="T87" t="n">
         <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="V87" t="n">
         <v>1</v>
       </c>
       <c r="W87" t="n">
-        <v>0.280528109056935</v>
+        <v>0.2904844870607921</v>
       </c>
       <c r="X87" t="n">
-        <v>0.7990466275754536</v>
+        <v>0.7830864358157542</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
@@ -7440,10 +7440,10 @@
         </is>
       </c>
       <c r="AA87" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
       <c r="AB87" t="n">
-        <v>3.020222668144887</v>
+        <v>5.24420792078758</v>
       </c>
     </row>
     <row r="88">
@@ -7482,52 +7482,52 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="J88" t="n">
         <v>3.8</v>
       </c>
       <c r="K88" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="L88" t="n">
-        <v>0.158004158004158</v>
+        <v>0.1649473486776882</v>
       </c>
       <c r="M88" t="n">
-        <v>0.2494802494802495</v>
+        <v>0.2495913828675545</v>
       </c>
       <c r="N88" t="n">
-        <v>0.5925155925155925</v>
+        <v>0.5854612684547574</v>
       </c>
       <c r="O88" t="n">
-        <v>0.05482456140350878</v>
+        <v>0.05435488883238682</v>
       </c>
       <c r="P88" t="n">
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.2322024601791497</v>
+        <v>0.2287387667007373</v>
       </c>
       <c r="R88" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="S88" t="n">
-        <v>0.2446752639291447</v>
+        <v>0.2353465342801532</v>
       </c>
       <c r="T88" t="n">
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="V88" t="n">
         <v>0</v>
       </c>
       <c r="W88" t="n">
-        <v>0.273642026411456</v>
+        <v>0.286323316151555</v>
       </c>
       <c r="X88" t="n">
-        <v>0.5231222758917055</v>
+        <v>0.5359146990191095</v>
       </c>
       <c r="Y88" t="n">
         <v>3.8</v>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="AA88" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
       <c r="AB88" t="n">
-        <v>3.530708773348613</v>
+        <v>6.408519536582851</v>
       </c>
     </row>
     <row r="89">
@@ -7604,28 +7604,28 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.2711379192563951</v>
+        <v>0.2725231151948335</v>
       </c>
       <c r="R89" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="S89" t="n">
-        <v>0.3330606025944221</v>
+        <v>0.3317922691381407</v>
       </c>
       <c r="T89" t="n">
         <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="V89" t="n">
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>0.1009831338966516</v>
+        <v>0.1008662714144943</v>
       </c>
       <c r="X89" t="n">
-        <v>0.3958014781491829</v>
+        <v>0.3956846156670256</v>
       </c>
       <c r="Y89" t="n">
         <v>3.2</v>
@@ -7636,10 +7636,10 @@
         </is>
       </c>
       <c r="AA89" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.671382611309341</v>
+        <v>4.731634706920012</v>
       </c>
     </row>
     <row r="90">
@@ -7702,28 +7702,28 @@
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.4372196027838811</v>
+        <v>0.4400086634656995</v>
       </c>
       <c r="R90" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="S90" t="n">
-        <v>0.06229188444374419</v>
+        <v>0.06570155745768574</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="V90" t="n">
         <v>0</v>
       </c>
       <c r="W90" t="n">
-        <v>0.2237053833631196</v>
+        <v>0.2175066496673598</v>
       </c>
       <c r="X90" t="n">
-        <v>0.5004885127723747</v>
+        <v>0.4942897790766149</v>
       </c>
       <c r="Y90" t="n">
         <v>3.4</v>
@@ -7734,10 +7734,10 @@
         </is>
       </c>
       <c r="AA90" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
       <c r="AB90" t="n">
-        <v>3.377946733377945</v>
+        <v>5.910764738760704</v>
       </c>
     </row>
     <row r="91">
@@ -7800,28 +7800,28 @@
         <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.3446007529713776</v>
+        <v>0.3447548041594359</v>
       </c>
       <c r="R91" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="S91" t="n">
-        <v>0.3027082363163736</v>
+        <v>0.3024915270262238</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>0.05857336365342514</v>
+        <v>0.05863602175551663</v>
       </c>
       <c r="X91" t="n">
-        <v>0.3526910107122487</v>
+        <v>0.3527536688143402</v>
       </c>
       <c r="Y91" t="n">
         <v>3.2</v>
@@ -7832,10 +7832,10 @@
         </is>
       </c>
       <c r="AA91" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.380417166675411</v>
+        <v>4.218262313639893</v>
       </c>
     </row>
     <row r="92">
@@ -7898,28 +7898,28 @@
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="R92" t="n">
-        <v>0.3773943291766953</v>
+        <v>0.3766028498451762</v>
       </c>
       <c r="S92" t="n">
-        <v>0.19024678256438</v>
+        <v>0.1961827095327438</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="V92" t="n">
         <v>1</v>
       </c>
       <c r="W92" t="n">
-        <v>-0.07893478087621114</v>
+        <v>-0.0840792285130561</v>
       </c>
       <c r="X92" t="n">
-        <v>0.4323588882589248</v>
+        <v>0.4272144406220799</v>
       </c>
       <c r="Y92" t="n">
         <v>1.85</v>
@@ -7930,10 +7930,10 @@
         </is>
       </c>
       <c r="AA92" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.918119511177259</v>
+        <v>5.108671387532308</v>
       </c>
     </row>
     <row r="93">
@@ -7996,28 +7996,28 @@
         <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.2317021112264667</v>
+        <v>0.2314049743946865</v>
       </c>
       <c r="R93" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="S93" t="n">
-        <v>0.2490088676518839</v>
+        <v>0.2512316805728451</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="V93" t="n">
         <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>0.2317692738862625</v>
+        <v>0.2298435977970813</v>
       </c>
       <c r="X93" t="n">
-        <v>0.5192890211216494</v>
+        <v>0.5173633450324683</v>
       </c>
       <c r="Y93" t="n">
         <v>3.3</v>
@@ -8028,10 +8028,10 @@
         </is>
       </c>
       <c r="AA93" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
       <c r="AB93" t="n">
-        <v>3.504836989884513</v>
+        <v>6.186680660599315</v>
       </c>
     </row>
     <row r="94">
@@ -8094,28 +8094,28 @@
         <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.2446428108738781</v>
+        <v>0.243982251206936</v>
       </c>
       <c r="R94" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="S94" t="n">
-        <v>0.2630634887461987</v>
+        <v>0.2613060377202377</v>
       </c>
       <c r="T94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="V94" t="n">
         <v>0</v>
       </c>
       <c r="W94" t="n">
-        <v>0.215697955699072</v>
+        <v>0.2181159663919753</v>
       </c>
       <c r="X94" t="n">
-        <v>0.492293700379923</v>
+        <v>0.4947117110728264</v>
       </c>
       <c r="Y94" t="n">
         <v>3.4</v>
@@ -8126,10 +8126,10 @@
         </is>
       </c>
       <c r="AA94" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
       <c r="AB94" t="n">
-        <v>3.322637492415771</v>
+        <v>5.915810242169697</v>
       </c>
     </row>
     <row r="95">
@@ -8189,34 +8189,34 @@
         <v>0.05900900900900896</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.4672142682244892</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="R95" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4645031770758087</v>
       </c>
       <c r="S95" t="n">
-        <v>0.06407475416544899</v>
+        <v>0.06664867022742459</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" t="n">
-        <v>0.2326412200600831</v>
+        <v>-0.1691782190599326</v>
       </c>
       <c r="X95" t="n">
-        <v>0.4687109776100618</v>
+        <v>0.4688481526967667</v>
       </c>
       <c r="Y95" t="n">
-        <v>4</v>
+        <v>1.48</v>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
@@ -8224,10 +8224,10 @@
         </is>
       </c>
       <c r="AA95" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
       <c r="AB95" t="n">
-        <v>3.163470639807426</v>
+        <v>5.606531322517188</v>
       </c>
     </row>
     <row r="96">
@@ -8290,28 +8290,28 @@
         <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.2653946255938225</v>
+        <v>0.2651006284586224</v>
       </c>
       <c r="R96" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="S96" t="n">
-        <v>0.3284392673664195</v>
+        <v>0.3281732089376114</v>
       </c>
       <c r="T96" t="n">
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="V96" t="n">
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>0.149916107039758</v>
+        <v>0.1504761626037661</v>
       </c>
       <c r="X96" t="n">
-        <v>0.406166107039758</v>
+        <v>0.406726162603766</v>
       </c>
       <c r="Y96" t="n">
         <v>3.7</v>
@@ -8322,10 +8322,10 @@
         </is>
       </c>
       <c r="AA96" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.74133659308937</v>
+        <v>4.8636705876072</v>
       </c>
     </row>
     <row r="97">
@@ -8388,28 +8388,28 @@
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4535486110547644</v>
+        <v>0.4566736230579956</v>
       </c>
       <c r="S97" t="n">
-        <v>0.05676912018698233</v>
+        <v>0.05435846129682308</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="V97" t="n">
         <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>-0.2215552845845635</v>
+        <v>-0.2222696376976354</v>
       </c>
       <c r="X97" t="n">
-        <v>0.4896822687582531</v>
+        <v>0.4889679156451812</v>
       </c>
       <c r="Y97" t="n">
         <v>1.33</v>
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="AA97" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
       <c r="AB97" t="n">
-        <v>3.305012158985048</v>
+        <v>5.847125383777921</v>
       </c>
     </row>
     <row r="98">
@@ -8461,13 +8461,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J98" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K98" t="n">
+        <v>4</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.5010684547933092</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.2696927271387518</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.229238818067939</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.09056573449051752</v>
+      </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -8479,7 +8493,9 @@
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
+      <c r="Y98" t="n">
+        <v>1.25557461406518</v>
+      </c>
       <c r="Z98" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -8523,13 +8539,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.2216320651496475</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.247988310735011</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.5303796241153415</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.08985084607100191</v>
+      </c>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -8541,7 +8571,9 @@
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
+      <c r="Y99" t="n">
+        <v>1.220136286201022</v>
+      </c>
       <c r="Z99" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -8553,20 +8585,20 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -8585,13 +8617,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J100" t="n">
+        <v>4</v>
+      </c>
+      <c r="K100" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.6227621063893677</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.2288650740980926</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.1483728195125398</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.09234666313851303</v>
+      </c>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -8603,7 +8649,9 @@
       </c>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
+      <c r="Y100" t="n">
+        <v>1.187159685863874</v>
+      </c>
       <c r="Z100" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -8615,20 +8663,20 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45508.65625</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -8647,13 +8695,27 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J101" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.2902468687989416</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.2997631595792349</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.4099899716218234</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.09375966319287654</v>
+      </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -8665,7 +8727,9 @@
       </c>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
+      <c r="Y101" t="n">
+        <v>1.305669144981413</v>
+      </c>
       <c r="Z101" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
@@ -8720,13 +8784,13 @@
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.4714480047822971</v>
+        <v>0.4694967552742121</v>
       </c>
       <c r="R102" t="n">
-        <v>0.4056032949254636</v>
+        <v>0.4042830898537844</v>
       </c>
       <c r="S102" t="n">
-        <v>0.1229487002922391</v>
+        <v>0.1262201548720035</v>
       </c>
       <c r="T102" t="n">
         <v>1</v>
@@ -8737,7 +8801,7 @@
       </c>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="n">
-        <v>0.5285519952177029</v>
+        <v>0.5305032447257878</v>
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr">
@@ -8746,10 +8810,10 @@
         </is>
       </c>
       <c r="AA102" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
       <c r="AB102" t="n">
-        <v>3.567355573809254</v>
+        <v>6.343808845453178</v>
       </c>
     </row>
     <row r="103">
@@ -8798,13 +8862,13 @@
         <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.474807650426295</v>
+        <v>0.4727240812949189</v>
       </c>
       <c r="R103" t="n">
-        <v>0.4097372930966371</v>
+        <v>0.4071627836349588</v>
       </c>
       <c r="S103" t="n">
-        <v>0.115455056477068</v>
+        <v>0.1201131350701222</v>
       </c>
       <c r="T103" t="n">
         <v>1</v>
@@ -8815,7 +8879,7 @@
       </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="n">
-        <v>0.525192349573705</v>
+        <v>0.5272759187050811</v>
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr">
@@ -8824,10 +8888,10 @@
         </is>
       </c>
       <c r="AA103" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
       <c r="AB103" t="n">
-        <v>3.544680320054506</v>
+        <v>6.305216170364257</v>
       </c>
     </row>
     <row r="104">
@@ -8876,13 +8940,13 @@
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.4744099064021176</v>
+        <v>0.4738402187299073</v>
       </c>
       <c r="R104" t="n">
-        <v>0.3974162014452964</v>
+        <v>0.3970833715775151</v>
       </c>
       <c r="S104" t="n">
-        <v>0.128173892152586</v>
+        <v>0.1290764096925773</v>
       </c>
       <c r="T104" t="n">
         <v>1</v>
@@ -8893,7 +8957,7 @@
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="n">
-        <v>0.5255900935978823</v>
+        <v>0.5261597812700927</v>
       </c>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr">
@@ -8902,10 +8966,10 @@
         </is>
       </c>
       <c r="AA104" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
       <c r="AB104" t="n">
-        <v>3.547364813490225</v>
+        <v>6.291869291521921</v>
       </c>
     </row>
     <row r="105">
@@ -8954,13 +9018,13 @@
         <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.3961073401413146</v>
+        <v>0.3997746834822209</v>
       </c>
       <c r="R105" t="n">
-        <v>0.3802938556685332</v>
+        <v>0.3808697754406668</v>
       </c>
       <c r="S105" t="n">
-        <v>0.223598804190152</v>
+        <v>0.2193555410771125</v>
       </c>
       <c r="T105" t="n">
         <v>1</v>
@@ -8971,7 +9035,7 @@
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="n">
-        <v>0.6038926598586853</v>
+        <v>0.6002253165177791</v>
       </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr">
@@ -8980,10 +9044,10 @@
         </is>
       </c>
       <c r="AA105" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
       <c r="AB105" t="n">
-        <v>4.075852263582984</v>
+        <v>7.177552088599557</v>
       </c>
     </row>
     <row r="106">
@@ -9032,13 +9096,13 @@
         <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.4357604694674418</v>
+        <v>0.4375459700908128</v>
       </c>
       <c r="R106" t="n">
-        <v>0.3721789459378736</v>
+        <v>0.3730150628421344</v>
       </c>
       <c r="S106" t="n">
-        <v>0.1920605845946844</v>
+        <v>0.1894389670670526</v>
       </c>
       <c r="T106" t="n">
         <v>1</v>
@@ -9049,7 +9113,7 @@
       </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="n">
-        <v>0.5642395305325583</v>
+        <v>0.5624540299091871</v>
       </c>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr">
@@ -9058,10 +9122,10 @@
         </is>
       </c>
       <c r="AA106" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
       <c r="AB106" t="n">
-        <v>3.808221428394718</v>
+        <v>6.725879408980817</v>
       </c>
     </row>
     <row r="107">
@@ -9110,13 +9174,13 @@
         <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.4748223715979583</v>
+        <v>0.4762256520660549</v>
       </c>
       <c r="R107" t="n">
-        <v>0.4821446094511964</v>
+        <v>0.4803533188099261</v>
       </c>
       <c r="S107" t="n">
-        <v>0.04303301895084536</v>
+        <v>0.0434210291240188</v>
       </c>
       <c r="T107" t="n">
         <v>1</v>
@@ -9127,7 +9191,7 @@
       </c>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="n">
-        <v>0.5178553905488036</v>
+        <v>0.519646681190074</v>
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr">
@@ -9136,10 +9200,10 @@
         </is>
       </c>
       <c r="AA107" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
       <c r="AB107" t="n">
-        <v>3.495160988164534</v>
+        <v>6.213985014074568</v>
       </c>
     </row>
     <row r="108">
@@ -9188,13 +9252,13 @@
         <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.3378760736066398</v>
+        <v>0.3405749389402209</v>
       </c>
       <c r="R108" t="n">
-        <v>0.35690813030224</v>
+        <v>0.3558480852076204</v>
       </c>
       <c r="S108" t="n">
-        <v>0.3052157960911198</v>
+        <v>0.3035769758521589</v>
       </c>
       <c r="T108" t="n">
         <v>1</v>
@@ -9205,7 +9269,7 @@
       </c>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="n">
-        <v>0.64309186969776</v>
+        <v>0.6441519147923795</v>
       </c>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr">
@@ -9214,10 +9278,10 @@
         </is>
       </c>
       <c r="AA108" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
       <c r="AB108" t="n">
-        <v>4.34041946032726</v>
+        <v>7.702830577384516</v>
       </c>
     </row>
     <row r="109">
@@ -9266,13 +9330,13 @@
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.406988013196621</v>
+        <v>0.403847330668933</v>
       </c>
       <c r="R109" t="n">
-        <v>0.3644240071799103</v>
+        <v>0.3641302640579551</v>
       </c>
       <c r="S109" t="n">
-        <v>0.2285879796234687</v>
+        <v>0.232022405273112</v>
       </c>
       <c r="T109" t="n">
         <v>1</v>
@@ -9283,7 +9347,7 @@
       </c>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="n">
-        <v>0.593011986803379</v>
+        <v>0.596152669331067</v>
       </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr">
@@ -9292,10 +9356,10 @@
         </is>
       </c>
       <c r="AA109" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
       <c r="AB109" t="n">
-        <v>4.002415345319804</v>
+        <v>7.128850981670743</v>
       </c>
     </row>
     <row r="110">
@@ -9344,13 +9408,13 @@
         <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.3694937315310033</v>
+        <v>0.3742469639595186</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3732029792473935</v>
+        <v>0.3749425523620097</v>
       </c>
       <c r="S110" t="n">
-        <v>0.2573032892216031</v>
+        <v>0.2508104836784718</v>
       </c>
       <c r="T110" t="n">
         <v>1</v>
@@ -9361,7 +9425,7 @@
       </c>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="n">
-        <v>0.6267970207526066</v>
+        <v>0.6250574476379902</v>
       </c>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr">
@@ -9370,10 +9434,10 @@
         </is>
       </c>
       <c r="AA110" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
       <c r="AB110" t="n">
-        <v>4.230440648905065</v>
+        <v>7.474497101882698</v>
       </c>
     </row>
     <row r="111">
@@ -9422,13 +9486,13 @@
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.4733371806917877</v>
+        <v>0.4739942378041332</v>
       </c>
       <c r="R111" t="n">
-        <v>0.4239851741582934</v>
+        <v>0.422798329895286</v>
       </c>
       <c r="S111" t="n">
-        <v>0.1026776451499188</v>
+        <v>0.1032074323005807</v>
       </c>
       <c r="T111" t="n">
         <v>1</v>
@@ -9439,7 +9503,7 @@
       </c>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="n">
-        <v>0.5266628193082123</v>
+        <v>0.5260057621958667</v>
       </c>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr">
@@ -9448,10 +9512,10 @@
         </is>
       </c>
       <c r="AA111" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
       <c r="AB111" t="n">
-        <v>3.554604960299884</v>
+        <v>6.290027516612613</v>
       </c>
     </row>
     <row r="112">
@@ -9500,13 +9564,13 @@
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.4238880895081383</v>
+        <v>0.4214803559717588</v>
       </c>
       <c r="R112" t="n">
-        <v>0.3826738469226045</v>
+        <v>0.3823090013622199</v>
       </c>
       <c r="S112" t="n">
-        <v>0.1934380635692574</v>
+        <v>0.196210642666021</v>
       </c>
       <c r="T112" t="n">
         <v>1</v>
@@ -9517,7 +9581,7 @@
       </c>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="n">
-        <v>0.5761119104918617</v>
+        <v>0.5785196440282412</v>
       </c>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr">
@@ -9526,10 +9590,10 @@
         </is>
       </c>
       <c r="AA112" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
       <c r="AB112" t="n">
-        <v>3.88835167330044</v>
+        <v>6.917993568449856</v>
       </c>
     </row>
     <row r="113">
@@ -9578,13 +9642,13 @@
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.4544331171342493</v>
+        <v>0.4455732802592645</v>
       </c>
       <c r="R113" t="n">
-        <v>0.3913317838444145</v>
+        <v>0.3852067815535028</v>
       </c>
       <c r="S113" t="n">
-        <v>0.1542350990213361</v>
+        <v>0.1692199381872326</v>
       </c>
       <c r="T113" t="n">
         <v>1</v>
@@ -9595,7 +9659,7 @@
       </c>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="n">
-        <v>0.5455668828657507</v>
+        <v>0.5544267197407355</v>
       </c>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr">
@@ -9604,10 +9668,10 @@
         </is>
       </c>
       <c r="AA113" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
       <c r="AB113" t="n">
-        <v>3.682194141893745</v>
+        <v>6.629888061598689</v>
       </c>
     </row>
     <row r="114">
@@ -9670,28 +9734,28 @@
         <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>0.3380679964157302</v>
+        <v>0.3388659580677731</v>
       </c>
       <c r="R114" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="S114" t="n">
-        <v>0.2879097657470336</v>
+        <v>0.2864394269506713</v>
       </c>
       <c r="T114" t="n">
         <v>1</v>
       </c>
       <c r="U114" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0.08333192751424695</v>
+        <v>0.08400430465856634</v>
       </c>
       <c r="X114" t="n">
-        <v>0.3740222378372361</v>
+        <v>0.3746946149815555</v>
       </c>
       <c r="Y114" t="n">
         <v>3.2</v>
@@ -9702,10 +9766,10 @@
         </is>
       </c>
       <c r="AA114" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.524388001463713</v>
+        <v>4.480634259065295</v>
       </c>
     </row>
     <row r="115">
@@ -9848,28 +9912,28 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="R116" t="n">
-        <v>0.3715543510497629</v>
+        <v>0.3703923812577244</v>
       </c>
       <c r="S116" t="n">
-        <v>0.2493869548668708</v>
+        <v>0.2524479614880006</v>
       </c>
       <c r="T116" t="n">
         <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="V116" t="n">
         <v>1</v>
       </c>
       <c r="W116" t="n">
-        <v>0.00735858848674531</v>
+        <v>0.00545955165765416</v>
       </c>
       <c r="X116" t="n">
-        <v>0.3790586940833662</v>
+        <v>0.3771596572542751</v>
       </c>
       <c r="Y116" t="n">
         <v>2.5</v>
@@ -9880,10 +9944,10 @@
         </is>
       </c>
       <c r="AA116" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
       <c r="AB116" t="n">
-        <v>2.55838055172261</v>
+        <v>4.510111471748842</v>
       </c>
     </row>
     <row r="117">
@@ -9946,28 +10010,28 @@
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="R117" t="n">
-        <v>0.3950426087473192</v>
+        <v>0.3894999314195416</v>
       </c>
       <c r="S117" t="n">
-        <v>0.146649704299382</v>
+        <v>0.1593977160970436</v>
       </c>
       <c r="T117" t="n">
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="V117" t="n">
         <v>1</v>
       </c>
       <c r="W117" t="n">
-        <v>-0.04557375270795772</v>
+        <v>-0.05277908717784108</v>
       </c>
       <c r="X117" t="n">
-        <v>0.4583076869532984</v>
+        <v>0.451102352483415</v>
       </c>
       <c r="Y117" t="n">
         <v>1.85</v>
@@ -9978,10 +10042,10 @@
         </is>
       </c>
       <c r="AA117" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
       <c r="AB117" t="n">
-        <v>3.09325571819867</v>
+        <v>5.394325336065033</v>
       </c>
     </row>
     <row r="118">
@@ -10044,28 +10108,28 @@
         <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.3614264383835507</v>
+        <v>0.3613841827993978</v>
       </c>
       <c r="R118" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="S118" t="n">
-        <v>0.2641950155242111</v>
+        <v>0.265575233477619</v>
       </c>
       <c r="T118" t="n">
         <v>1</v>
       </c>
       <c r="U118" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0.0718963729883717</v>
+        <v>0.07055841061911661</v>
       </c>
       <c r="X118" t="n">
-        <v>0.3743785460922382</v>
+        <v>0.3730405837229831</v>
       </c>
       <c r="Y118" t="n">
         <v>3.1</v>
@@ -10076,10 +10140,10 @@
         </is>
       </c>
       <c r="AA118" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.526792832494484</v>
+        <v>4.460855194124398</v>
       </c>
     </row>
     <row r="119">
@@ -10142,28 +10206,28 @@
         <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.3082132045474411</v>
+        <v>0.310221098231573</v>
       </c>
       <c r="R119" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="S119" t="n">
-        <v>0.3321025659439781</v>
+        <v>0.3318168848056527</v>
       </c>
       <c r="T119" t="n">
         <v>1</v>
       </c>
       <c r="U119" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>0.06929352201122096</v>
+        <v>0.06757130946541395</v>
       </c>
       <c r="X119" t="n">
-        <v>0.359684229508581</v>
+        <v>0.357962016962774</v>
       </c>
       <c r="Y119" t="n">
         <v>3.2</v>
@@ -10174,10 +10238,10 @@
         </is>
       </c>
       <c r="AA119" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.427616492905725</v>
+        <v>4.280544241946123</v>
       </c>
     </row>
     <row r="120">
@@ -10318,28 +10382,28 @@
         <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.3272688283754523</v>
+        <v>0.3271006089805857</v>
       </c>
       <c r="R121" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="S121" t="n">
-        <v>0.2980829384824198</v>
+        <v>0.2966877125278745</v>
       </c>
       <c r="T121" t="n">
         <v>1</v>
       </c>
       <c r="U121" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="V121" t="n">
         <v>0</v>
       </c>
       <c r="W121" t="n">
-        <v>0.0851745489316012</v>
+        <v>0.08673799428101381</v>
       </c>
       <c r="X121" t="n">
-        <v>0.3746482331421275</v>
+        <v>0.3762116784915401</v>
       </c>
       <c r="Y121" t="n">
         <v>3.2</v>
@@ -10350,10 +10414,10 @@
         </is>
       </c>
       <c r="AA121" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.528613031092374</v>
+        <v>4.498775450489541</v>
       </c>
     </row>
     <row r="122">
@@ -10413,34 +10477,34 @@
         <v>0.07613636363636367</v>
       </c>
       <c r="P122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3792582472531151</v>
       </c>
       <c r="R122" t="n">
-        <v>0.3799057602844827</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="S122" t="n">
-        <v>0.2257445937585379</v>
+        <v>0.2402791170121459</v>
       </c>
       <c r="T122" t="n">
         <v>1</v>
       </c>
       <c r="U122" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="V122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W122" t="n">
-        <v>0.02264954036035843</v>
+        <v>0.09007192823737875</v>
       </c>
       <c r="X122" t="n">
-        <v>0.3943496459569794</v>
+        <v>0.3804626357347388</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
@@ -10448,10 +10512,10 @@
         </is>
       </c>
       <c r="AA122" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.661583761413864</v>
+        <v>4.549608806230817</v>
       </c>
     </row>
     <row r="123">
@@ -10591,45 +10655,45 @@
         <v>0.06108374384236459</v>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>0.3674867332397739</v>
+        <v>0.3543207301500569</v>
       </c>
       <c r="R124" t="n">
-        <v>0.3843011769385412</v>
+        <v>0.3309504969275024</v>
       </c>
       <c r="S124" t="n">
-        <v>0.2482120898216849</v>
+        <v>0.3147287729224407</v>
       </c>
       <c r="T124" t="n">
         <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>0.1599124428005034</v>
+        <v>-0.2956328445946042</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W124" t="n">
-        <v>0.1599124428005034</v>
+        <v>0.2956328445946042</v>
       </c>
       <c r="X124" t="n">
-        <v>0.3843011769385412</v>
+        <v>0.6456792698499432</v>
       </c>
       <c r="Y124" t="n">
-        <v>4.2</v>
+        <v>2.692307692307693</v>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA124" t="n">
-        <v>7.863766199583208</v>
+        <v>9.885606821282982</v>
       </c>
       <c r="AB124" t="n">
-        <v>7.863766199583208</v>
+        <v>9.885606821282982</v>
       </c>
     </row>
     <row r="125">
@@ -10668,66 +10732,66 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="J125" t="n">
         <v>3.4</v>
       </c>
       <c r="K125" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="L125" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.3781597573306371</v>
       </c>
       <c r="M125" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2780586450960567</v>
       </c>
       <c r="N125" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.3437815975733064</v>
       </c>
       <c r="O125" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05775401069518704</v>
       </c>
       <c r="P125" t="n">
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>0.2977685999675609</v>
+        <v>0.3450016956237524</v>
       </c>
       <c r="R125" t="n">
-        <v>0.3540569072701464</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="S125" t="n">
-        <v>0.3481744927622927</v>
+        <v>0.2835960499940407</v>
       </c>
       <c r="T125" t="n">
         <v>1</v>
       </c>
       <c r="U125" t="n">
-        <v>0.07570639180622885</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="V125" t="n">
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>0.07570639180622885</v>
+        <v>0.09334360928615032</v>
       </c>
       <c r="X125" t="n">
-        <v>0.3540569072701464</v>
+        <v>0.371402254382207</v>
       </c>
       <c r="Y125" t="n">
         <v>3.4</v>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA125" t="n">
-        <v>7.244892566553878</v>
+        <v>5.686316458965599</v>
       </c>
       <c r="AB125" t="n">
-        <v>7.244892566553878</v>
+        <v>5.686316458965599</v>
       </c>
     </row>
     <row r="126">
@@ -10790,42 +10854,42 @@
         <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>0.3644976060688948</v>
+        <v>0.2917897629546954</v>
       </c>
       <c r="R126" t="n">
-        <v>0.3876858851927056</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="S126" t="n">
-        <v>0.2478165087383996</v>
+        <v>0.3523444024590837</v>
       </c>
       <c r="T126" t="n">
         <v>1</v>
       </c>
       <c r="U126" t="n">
-        <v>0.1017416791841219</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="V126" t="n">
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>0.1017416791841219</v>
+        <v>0.06992162857763712</v>
       </c>
       <c r="X126" t="n">
-        <v>0.3876858851927056</v>
+        <v>0.3558658345862208</v>
       </c>
       <c r="Y126" t="n">
         <v>3.3</v>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA126" t="n">
-        <v>7.933025821884092</v>
+        <v>5.448447683111589</v>
       </c>
       <c r="AB126" t="n">
-        <v>7.933025821884092</v>
+        <v>5.448447683111589</v>
       </c>
     </row>
     <row r="127">
@@ -10888,42 +10952,42 @@
         <v>2</v>
       </c>
       <c r="Q127" t="n">
-        <v>0.2490802893171681</v>
+        <v>0.1663911399929355</v>
       </c>
       <c r="R127" t="n">
-        <v>0.3653293906011599</v>
+        <v>0.3464497059716086</v>
       </c>
       <c r="S127" t="n">
-        <v>0.3855903200816719</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="T127" t="n">
         <v>1</v>
       </c>
       <c r="U127" t="n">
-        <v>0.02347897733322735</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="V127" t="n">
         <v>2</v>
       </c>
       <c r="W127" t="n">
-        <v>0.02347897733322735</v>
+        <v>0.1250478112870113</v>
       </c>
       <c r="X127" t="n">
-        <v>0.3855903200816719</v>
+        <v>0.4871591540354559</v>
       </c>
       <c r="Y127" t="n">
         <v>2.63</v>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA127" t="n">
-        <v>7.890145302442416</v>
+        <v>7.458600703260249</v>
       </c>
       <c r="AB127" t="n">
-        <v>7.890145302442416</v>
+        <v>7.458600703260249</v>
       </c>
     </row>
     <row r="128">
@@ -10982,29 +11046,47 @@
       <c r="O128" t="n">
         <v>0.05842972440212746</v>
       </c>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.4014381059865235</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3129428747972791</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.2856190192161973</v>
+      </c>
       <c r="T128" t="n">
         <v>1</v>
       </c>
-      <c r="U128" t="inlineStr"/>
+      <c r="U128" t="n">
+        <v>-0.1643079056797918</v>
+      </c>
       <c r="V128" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W128" t="inlineStr"/>
-      <c r="X128" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.1643079056797918</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.5985618940134765</v>
+      </c>
       <c r="Y128" t="n">
-        <v>1.294137466307278</v>
+        <v>2.175675675675676</v>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr"/>
-      <c r="AB128" t="inlineStr"/>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA128" t="n">
+        <v>9.164221028491188</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>9.164221028491188</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -11066,42 +11148,42 @@
         <v>2</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.1911693611669979</v>
+        <v>0.08782328920802665</v>
       </c>
       <c r="R129" t="n">
-        <v>0.3333557197207141</v>
+        <v>0.3046577231035404</v>
       </c>
       <c r="S129" t="n">
-        <v>0.475474919112288</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="T129" t="n">
         <v>1</v>
       </c>
       <c r="U129" t="n">
-        <v>-0.06523654333830486</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="V129" t="n">
         <v>2</v>
       </c>
       <c r="W129" t="n">
-        <v>-0.06523654333830486</v>
+        <v>0.06680752523784006</v>
       </c>
       <c r="X129" t="n">
-        <v>0.475474919112288</v>
+        <v>0.6075189876884329</v>
       </c>
       <c r="Y129" t="n">
         <v>1.75</v>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA129" t="n">
-        <v>9.729409697495484</v>
+        <v>9.301357700623464</v>
       </c>
       <c r="AB129" t="n">
-        <v>9.729409697495484</v>
+        <v>9.301357700623464</v>
       </c>
     </row>
     <row r="130">
@@ -11164,42 +11246,42 @@
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>0.4260256512288893</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="R130" t="n">
-        <v>0.3704826390791036</v>
+        <v>0.2831583750474474</v>
       </c>
       <c r="S130" t="n">
-        <v>0.2034917096920073</v>
+        <v>0.1639463079895984</v>
       </c>
       <c r="T130" t="n">
         <v>1</v>
       </c>
       <c r="U130" t="n">
-        <v>-0.1847649833147144</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="V130" t="n">
         <v>1</v>
       </c>
       <c r="W130" t="n">
-        <v>-0.1847649833147144</v>
+        <v>-0.05789531758064959</v>
       </c>
       <c r="X130" t="n">
-        <v>0.4260256512288893</v>
+        <v>0.5528953169629541</v>
       </c>
       <c r="Y130" t="n">
         <v>1.55</v>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA130" t="n">
-        <v>8.717553620255851</v>
+        <v>8.465047543023386</v>
       </c>
       <c r="AB130" t="n">
-        <v>8.717553620255851</v>
+        <v>8.465047543023386</v>
       </c>
     </row>
     <row r="131">
@@ -11262,42 +11344,42 @@
         <v>2</v>
       </c>
       <c r="Q131" t="n">
-        <v>0.137404684861135</v>
+        <v>0.08103257282901304</v>
       </c>
       <c r="R131" t="n">
-        <v>0.3356936919426209</v>
+        <v>0.2903271265316048</v>
       </c>
       <c r="S131" t="n">
-        <v>0.5269016231962442</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="T131" t="n">
         <v>1</v>
       </c>
       <c r="U131" t="n">
-        <v>-0.07123405779805936</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="V131" t="n">
         <v>2</v>
       </c>
       <c r="W131" t="n">
-        <v>-0.07123405779805936</v>
+        <v>0.03050461964507867</v>
       </c>
       <c r="X131" t="n">
-        <v>0.5269016231962442</v>
+        <v>0.6286403006393823</v>
       </c>
       <c r="Y131" t="n">
         <v>1.6</v>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA131" t="n">
-        <v>10.78172908031137</v>
+        <v>9.624733415366299</v>
       </c>
       <c r="AB131" t="n">
-        <v>10.78172908031137</v>
+        <v>9.624733415366299</v>
       </c>
     </row>
     <row r="132">
@@ -11356,29 +11438,47 @@
       <c r="O132" t="n">
         <v>0.051747311827957</v>
       </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+      <c r="P132" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3609999082839134</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3275469899490511</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3114531017670354</v>
+      </c>
       <c r="T132" t="n">
         <v>1</v>
       </c>
-      <c r="U132" t="inlineStr"/>
+      <c r="U132" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
       <c r="V132" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W132" t="inlineStr"/>
-      <c r="X132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W132" t="n">
+        <v>-0.03516622590139018</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3609999082839134</v>
+      </c>
       <c r="Y132" t="n">
-        <v>1.371428571428572</v>
+        <v>2.4</v>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
+        </is>
+      </c>
+      <c r="AA132" t="n">
+        <v>5.52705239653018</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>5.52705239653018</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -11416,66 +11516,66 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J133" t="n">
         <v>3.4</v>
       </c>
       <c r="K133" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="L133" t="n">
-        <v>0.3308443879577409</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M133" t="n">
-        <v>0.2802446580347923</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N133" t="n">
-        <v>0.3889109540074668</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="O133" t="n">
-        <v>0.04950313458716815</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="P133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.2360303609118284</v>
+        <v>0.2799751019411993</v>
       </c>
       <c r="R133" t="n">
-        <v>0.3436490407035404</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="S133" t="n">
-        <v>0.4203205983846311</v>
+        <v>0.3551977642422137</v>
       </c>
       <c r="T133" t="n">
         <v>1</v>
       </c>
       <c r="U133" t="n">
-        <v>0.03140964437716431</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="V133" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W133" t="n">
-        <v>0.03140964437716431</v>
+        <v>0.0862042354979321</v>
       </c>
       <c r="X133" t="n">
-        <v>0.4203205983846311</v>
+        <v>0.364827133816587</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.1</t>
         </is>
       </c>
       <c r="AA133" t="n">
-        <v>8.600813926453956</v>
+        <v>5.585648743972431</v>
       </c>
       <c r="AB133" t="n">
-        <v>8.600813926453956</v>
+        <v>5.585648743972431</v>
       </c>
     </row>
     <row r="134">
@@ -11524,13 +11624,13 @@
         <v>2</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.3380006120789301</v>
+        <v>0.1838937751487623</v>
       </c>
       <c r="R134" t="n">
-        <v>0.2429502572775514</v>
+        <v>0.2459078968870776</v>
       </c>
       <c r="S134" t="n">
-        <v>0.4190491306435185</v>
+        <v>0.57019832796416</v>
       </c>
       <c r="T134" t="n">
         <v>1</v>
@@ -11541,19 +11641,19 @@
       </c>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="n">
-        <v>0.5809508693564815</v>
+        <v>0.42980167203584</v>
       </c>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA134" t="n">
-        <v>11.88771225333662</v>
+        <v>6.580434806066749</v>
       </c>
       <c r="AB134" t="n">
-        <v>11.88771225333662</v>
+        <v>6.580434806066749</v>
       </c>
     </row>
     <row r="135">
@@ -11602,13 +11702,13 @@
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.3970849127278552</v>
+        <v>0.7540168523407008</v>
       </c>
       <c r="R135" t="n">
-        <v>0.2458736909589887</v>
+        <v>0.131951511035547</v>
       </c>
       <c r="S135" t="n">
-        <v>0.3570413963131561</v>
+        <v>0.1140316366237523</v>
       </c>
       <c r="T135" t="n">
         <v>1</v>
@@ -11619,19 +11719,19 @@
       </c>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="n">
-        <v>0.6029150872721448</v>
+        <v>0.2459831476592992</v>
       </c>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.1</t>
         </is>
       </c>
       <c r="AA135" t="n">
-        <v>12.33715525484243</v>
+        <v>3.766099975590909</v>
       </c>
       <c r="AB135" t="n">
-        <v>12.33715525484243</v>
+        <v>3.766099975590909</v>
       </c>
     </row>
   </sheetData>
